--- a/data/carbon/Aveiro2025_Biomass_C_cores.xlsx
+++ b/data/carbon/Aveiro2025_Biomass_C_cores.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" hidePivotFieldList="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\REWRITE\Field_data\seagrass_carbon_2025\data\carbon\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\REWRITE\Field_data\Nantes_cloud\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -159,7 +159,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2078" uniqueCount="538">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2091" uniqueCount="557">
   <si>
     <t>type</t>
   </si>
@@ -1740,9 +1740,6 @@
     <t>-</t>
   </si>
   <si>
-    <t>NG_27_A</t>
-  </si>
-  <si>
     <t>NR_41_A</t>
   </si>
   <si>
@@ -1752,18 +1749,12 @@
     <t>NR_49_A</t>
   </si>
   <si>
-    <t>NR_51_A</t>
-  </si>
-  <si>
     <t>NR_52_A</t>
   </si>
   <si>
     <t>NG_27_B</t>
   </si>
   <si>
-    <t>NR_41_B</t>
-  </si>
-  <si>
     <t>NR_43_B</t>
   </si>
   <si>
@@ -1788,9 +1779,6 @@
     <t>NG_13_A</t>
   </si>
   <si>
-    <t>NG_15_A</t>
-  </si>
-  <si>
     <t>NG_16_A</t>
   </si>
   <si>
@@ -1803,21 +1791,9 @@
     <t>NG_12_B</t>
   </si>
   <si>
-    <t>NG_13_B</t>
-  </si>
-  <si>
-    <t>NG_15_B</t>
-  </si>
-  <si>
-    <t>NG_16_B</t>
-  </si>
-  <si>
     <t>NG_18_A</t>
   </si>
   <si>
-    <t>NG_19_A</t>
-  </si>
-  <si>
     <t>NG_20_A</t>
   </si>
   <si>
@@ -1830,9 +1806,6 @@
     <t>NG_26_A</t>
   </si>
   <si>
-    <t>NG_18_B</t>
-  </si>
-  <si>
     <t>NG_19_B</t>
   </si>
   <si>
@@ -1863,9 +1836,6 @@
     <t>RR_39_A</t>
   </si>
   <si>
-    <t>RR_41_A</t>
-  </si>
-  <si>
     <t>RR_45_A</t>
   </si>
   <si>
@@ -1881,9 +1851,6 @@
     <t>RR_38_B</t>
   </si>
   <si>
-    <t>RR_39_B</t>
-  </si>
-  <si>
     <t>RR_41B</t>
   </si>
   <si>
@@ -1914,19 +1881,109 @@
     <t>DryMassTotal</t>
   </si>
   <si>
+    <t>CarbonTC</t>
+  </si>
+  <si>
     <t>DryMassIC</t>
   </si>
   <si>
+    <t>CarbonIC</t>
+  </si>
+  <si>
     <t>CoreType</t>
   </si>
   <si>
     <t>Habitat</t>
   </si>
   <si>
-    <t>MeasuredTC</t>
-  </si>
-  <si>
-    <t>MeasuredIC</t>
+    <t>RG_4_A</t>
+  </si>
+  <si>
+    <t>RG_5_A</t>
+  </si>
+  <si>
+    <t>RG_9_A/RG_17_A</t>
+  </si>
+  <si>
+    <t>RG_12_A</t>
+  </si>
+  <si>
+    <t>RG_14_A</t>
+  </si>
+  <si>
+    <t>RG_4_B</t>
+  </si>
+  <si>
+    <t>RG_5_B</t>
+  </si>
+  <si>
+    <t>RG_9_B/RG_17_B</t>
+  </si>
+  <si>
+    <t>RG_12_B</t>
+  </si>
+  <si>
+    <t>RG_14_B</t>
+  </si>
+  <si>
+    <t>RG_13_A</t>
+  </si>
+  <si>
+    <t>RG_15_A</t>
+  </si>
+  <si>
+    <t>RG_16_A</t>
+  </si>
+  <si>
+    <t>RG_24_A</t>
+  </si>
+  <si>
+    <t>RG_13_B</t>
+  </si>
+  <si>
+    <t>RG_15_B</t>
+  </si>
+  <si>
+    <t>RG_16_B</t>
+  </si>
+  <si>
+    <t>RG_24_B</t>
+  </si>
+  <si>
+    <t>NG_27_A *</t>
+  </si>
+  <si>
+    <t>NR_51_A *</t>
+  </si>
+  <si>
+    <t>NR_41_B *</t>
+  </si>
+  <si>
+    <t>NG_15_A *</t>
+  </si>
+  <si>
+    <t>NG_13_B *</t>
+  </si>
+  <si>
+    <t>NG_15_B *</t>
+  </si>
+  <si>
+    <t>NG_16_B *</t>
+  </si>
+  <si>
+    <t>NG_19_A *</t>
+  </si>
+  <si>
+    <t>NG_18_B *</t>
+  </si>
+  <si>
+    <t>RR_41_A *</t>
+  </si>
+  <si>
+    <t>RR_39_B *</t>
+  </si>
+  <si>
+    <t>* Samples not well homogenised</t>
   </si>
 </sst>
 </file>
@@ -2437,7 +2494,7 @@
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="24" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="89">
+  <cellXfs count="90">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -2697,6 +2754,9 @@
     <xf numFmtId="0" fontId="20" fillId="9" borderId="4" xfId="9" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="0" xfId="6" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="16">
     <cellStyle name="Heading" xfId="1"/>
@@ -2844,7 +2904,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" refreshedBy="barille-l" refreshedDate="46070.722848495374" createdVersion="8" refreshedVersion="6" minRefreshableVersion="3" recordCount="179">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" refreshedBy="barille-l" refreshedDate="46069.625101851852" createdVersion="8" refreshedVersion="6" minRefreshableVersion="3" recordCount="179">
   <cacheSource type="worksheet">
     <worksheetSource ref="B1:E1048576" sheet="seagrass biomass"/>
   </cacheSource>
@@ -3031,7 +3091,7 @@
     <s v="6A"/>
     <x v="5"/>
     <x v="0"/>
-    <n v="0"/>
+    <n v="17"/>
   </r>
   <r>
     <s v="6B"/>
@@ -3883,7 +3943,7 @@
     <s v="134AN"/>
     <x v="76"/>
     <x v="0"/>
-    <n v="0"/>
+    <n v="12"/>
   </r>
   <r>
     <s v="134BN"/>
@@ -4889,37 +4949,37 @@
   <sheetData>
     <row r="1" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="30" t="s">
-        <v>534</v>
+        <v>525</v>
       </c>
       <c r="B1" s="30" t="s">
-        <v>527</v>
+        <v>516</v>
       </c>
       <c r="C1" s="30" t="s">
         <v>456</v>
       </c>
       <c r="D1" s="30" t="s">
-        <v>525</v>
+        <v>514</v>
       </c>
       <c r="E1" s="30" t="s">
+        <v>515</v>
+      </c>
+      <c r="F1" s="30" t="s">
         <v>526</v>
       </c>
-      <c r="F1" s="30" t="s">
-        <v>535</v>
-      </c>
       <c r="G1" s="31" t="s">
-        <v>532</v>
+        <v>521</v>
       </c>
       <c r="H1" s="31" t="s">
-        <v>531</v>
+        <v>520</v>
       </c>
       <c r="I1" s="31" t="s">
-        <v>536</v>
+        <v>522</v>
       </c>
       <c r="J1" s="31" t="s">
-        <v>533</v>
+        <v>523</v>
       </c>
       <c r="K1" s="31" t="s">
-        <v>537</v>
+        <v>524</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -4930,7 +4990,7 @@
         <v>455</v>
       </c>
       <c r="C2" s="30" t="s">
-        <v>528</v>
+        <v>517</v>
       </c>
       <c r="D2" t="s">
         <v>264</v>
@@ -4948,19 +5008,19 @@
         <v>780</v>
       </c>
       <c r="H2" s="66">
-        <f>IF($F2 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E2&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
+        <f>IF($F2 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E2&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
         <v>78.52</v>
       </c>
       <c r="I2" s="66">
-        <f>IF($F2 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E2&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
+        <f>IF($F2 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E2&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
         <v>24.32</v>
       </c>
       <c r="J2" s="66">
-        <f>IF($F2 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E2&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
+        <f>IF($F2 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E2&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
         <v>211.87</v>
       </c>
       <c r="K2" s="66">
-        <f>IF($F2 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E2&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
+        <f>IF($F2 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E2&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
         <v>2.3180000000000001</v>
       </c>
     </row>
@@ -4972,7 +5032,7 @@
         <v>453</v>
       </c>
       <c r="C3" s="30" t="s">
-        <v>528</v>
+        <v>517</v>
       </c>
       <c r="D3" t="s">
         <v>264</v>
@@ -4990,19 +5050,19 @@
         <v>557</v>
       </c>
       <c r="H3" s="66">
-        <f>IF($F3 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E3&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
+        <f>IF($F3 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E3&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
         <v>70.52</v>
       </c>
       <c r="I3" s="66">
-        <f>IF($F3 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E3&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
+        <f>IF($F3 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E3&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
         <v>17.850000000000001</v>
       </c>
       <c r="J3" s="66">
-        <f>IF($F3 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E3&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
+        <f>IF($F3 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E3&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
         <v>189.89</v>
       </c>
       <c r="K3" s="66">
-        <f>IF($F3 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E3&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
+        <f>IF($F3 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E3&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
         <v>1.5349999999999999</v>
       </c>
     </row>
@@ -5014,7 +5074,7 @@
         <v>455</v>
       </c>
       <c r="C4" s="30" t="s">
-        <v>528</v>
+        <v>517</v>
       </c>
       <c r="D4" t="s">
         <v>266</v>
@@ -5032,19 +5092,19 @@
         <v>1415</v>
       </c>
       <c r="H4" s="66" t="str">
-        <f>IF($F4 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E4&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
+        <f>IF($F4 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E4&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="I4" s="66" t="str">
-        <f>IF($F4 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E4&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
+        <f>IF($F4 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E4&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="J4" s="66" t="str">
-        <f>IF($F4 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E4&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
+        <f>IF($F4 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E4&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="K4" s="66" t="str">
-        <f>IF($F4 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E4&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
+        <f>IF($F4 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E4&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
         <v>NA</v>
       </c>
     </row>
@@ -5056,7 +5116,7 @@
         <v>453</v>
       </c>
       <c r="C5" s="30" t="s">
-        <v>528</v>
+        <v>517</v>
       </c>
       <c r="D5" t="s">
         <v>266</v>
@@ -5074,19 +5134,19 @@
         <v>833</v>
       </c>
       <c r="H5" s="66" t="str">
-        <f>IF($F5 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E5&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
+        <f>IF($F5 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E5&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="I5" s="66" t="str">
-        <f>IF($F5 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E5&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
+        <f>IF($F5 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E5&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="J5" s="66" t="str">
-        <f>IF($F5 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E5&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
+        <f>IF($F5 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E5&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="K5" s="66" t="str">
-        <f>IF($F5 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E5&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
+        <f>IF($F5 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E5&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
         <v>NA</v>
       </c>
     </row>
@@ -5098,7 +5158,7 @@
         <v>455</v>
       </c>
       <c r="C6" s="30" t="s">
-        <v>528</v>
+        <v>517</v>
       </c>
       <c r="D6" t="s">
         <v>268</v>
@@ -5116,19 +5176,19 @@
         <v>1552</v>
       </c>
       <c r="H6" s="66" t="str">
-        <f>IF($F6 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E6&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
+        <f>IF($F6 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E6&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="I6" s="66" t="str">
-        <f>IF($F6 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E6&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
+        <f>IF($F6 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E6&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="J6" s="66" t="str">
-        <f>IF($F6 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E6&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
+        <f>IF($F6 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E6&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="K6" s="66" t="str">
-        <f>IF($F6 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E6&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
+        <f>IF($F6 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E6&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
         <v>NA</v>
       </c>
     </row>
@@ -5140,7 +5200,7 @@
         <v>453</v>
       </c>
       <c r="C7" s="30" t="s">
-        <v>528</v>
+        <v>517</v>
       </c>
       <c r="D7" t="s">
         <v>268</v>
@@ -5158,19 +5218,19 @@
         <v>561</v>
       </c>
       <c r="H7" s="66" t="str">
-        <f>IF($F7 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E7&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
+        <f>IF($F7 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E7&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="I7" s="66" t="str">
-        <f>IF($F7 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E7&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
+        <f>IF($F7 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E7&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="J7" s="66" t="str">
-        <f>IF($F7 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E7&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
+        <f>IF($F7 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E7&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="K7" s="66" t="str">
-        <f>IF($F7 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E7&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
+        <f>IF($F7 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E7&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
         <v>NA</v>
       </c>
     </row>
@@ -5182,7 +5242,7 @@
         <v>455</v>
       </c>
       <c r="C8" s="30" t="s">
-        <v>528</v>
+        <v>517</v>
       </c>
       <c r="D8" t="s">
         <v>270</v>
@@ -5200,19 +5260,19 @@
         <v>2799</v>
       </c>
       <c r="H8" s="66">
-        <f>IF($F8 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E8&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
+        <f>IF($F8 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E8&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
         <v>71.180000000000007</v>
       </c>
       <c r="I8" s="66">
-        <f>IF($F8 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E8&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
+        <f>IF($F8 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E8&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
         <v>20.43</v>
       </c>
       <c r="J8" s="66">
-        <f>IF($F8 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E8&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
+        <f>IF($F8 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E8&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
         <v>230.9</v>
       </c>
       <c r="K8" s="66">
-        <f>IF($F8 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E8&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
+        <f>IF($F8 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E8&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
         <v>1.3680000000000001</v>
       </c>
     </row>
@@ -5224,7 +5284,7 @@
         <v>453</v>
       </c>
       <c r="C9" s="30" t="s">
-        <v>528</v>
+        <v>517</v>
       </c>
       <c r="D9" t="s">
         <v>270</v>
@@ -5242,19 +5302,19 @@
         <v>1299</v>
       </c>
       <c r="H9" s="66">
-        <f>IF($F9 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E9&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
+        <f>IF($F9 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E9&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
         <v>78.010000000000005</v>
       </c>
       <c r="I9" s="66">
-        <f>IF($F9 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E9&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
+        <f>IF($F9 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E9&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
         <v>20.02</v>
       </c>
       <c r="J9" s="66">
-        <f>IF($F9 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E9&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
+        <f>IF($F9 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E9&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
         <v>266.81</v>
       </c>
       <c r="K9" s="66">
-        <f>IF($F9 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E9&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
+        <f>IF($F9 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E9&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
         <v>1.075</v>
       </c>
     </row>
@@ -5266,7 +5326,7 @@
         <v>455</v>
       </c>
       <c r="C10" s="30" t="s">
-        <v>528</v>
+        <v>517</v>
       </c>
       <c r="D10" t="s">
         <v>286</v>
@@ -5284,19 +5344,19 @@
         <v>NA</v>
       </c>
       <c r="H10" s="66" t="str">
-        <f>IF($F10 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E10&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
+        <f>IF($F10 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E10&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="I10" s="66" t="str">
-        <f>IF($F10 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E10&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
+        <f>IF($F10 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E10&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="J10" s="66" t="str">
-        <f>IF($F10 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E10&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
+        <f>IF($F10 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E10&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="K10" s="66" t="str">
-        <f>IF($F10 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E10&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
+        <f>IF($F10 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E10&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
         <v>NA</v>
       </c>
     </row>
@@ -5308,7 +5368,7 @@
         <v>453</v>
       </c>
       <c r="C11" s="30" t="s">
-        <v>528</v>
+        <v>517</v>
       </c>
       <c r="D11" t="s">
         <v>286</v>
@@ -5326,19 +5386,19 @@
         <v>NA</v>
       </c>
       <c r="H11" s="66" t="str">
-        <f>IF($F11 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E11&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
+        <f>IF($F11 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E11&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="I11" s="66" t="str">
-        <f>IF($F11 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E11&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
+        <f>IF($F11 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E11&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="J11" s="66" t="str">
-        <f>IF($F11 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E11&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
+        <f>IF($F11 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E11&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="K11" s="66" t="str">
-        <f>IF($F11 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E11&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
+        <f>IF($F11 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E11&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
         <v>NA</v>
       </c>
     </row>
@@ -5350,7 +5410,7 @@
         <v>455</v>
       </c>
       <c r="C12" s="30" t="s">
-        <v>528</v>
+        <v>517</v>
       </c>
       <c r="D12" t="s">
         <v>260</v>
@@ -5368,19 +5428,19 @@
         <v>1476</v>
       </c>
       <c r="H12" s="66" t="str">
-        <f>IF($F12 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E12&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
+        <f>IF($F12 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E12&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="I12" s="66" t="str">
-        <f>IF($F12 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E12&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
+        <f>IF($F12 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E12&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="J12" s="66" t="str">
-        <f>IF($F12 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E12&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
+        <f>IF($F12 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E12&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="K12" s="66" t="str">
-        <f>IF($F12 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E12&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
+        <f>IF($F12 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E12&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
         <v>NA</v>
       </c>
     </row>
@@ -5392,7 +5452,7 @@
         <v>453</v>
       </c>
       <c r="C13" s="30" t="s">
-        <v>528</v>
+        <v>517</v>
       </c>
       <c r="D13" t="s">
         <v>260</v>
@@ -5410,19 +5470,19 @@
         <v>1194</v>
       </c>
       <c r="H13" s="66" t="str">
-        <f>IF($F13 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E13&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
+        <f>IF($F13 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E13&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="I13" s="66" t="str">
-        <f>IF($F13 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E13&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
+        <f>IF($F13 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E13&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="J13" s="66" t="str">
-        <f>IF($F13 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E13&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
+        <f>IF($F13 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E13&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="K13" s="66" t="str">
-        <f>IF($F13 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E13&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
+        <f>IF($F13 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E13&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
         <v>NA</v>
       </c>
     </row>
@@ -5434,7 +5494,7 @@
         <v>455</v>
       </c>
       <c r="C14" s="30" t="s">
-        <v>528</v>
+        <v>517</v>
       </c>
       <c r="D14" t="s">
         <v>256</v>
@@ -5452,19 +5512,19 @@
         <v>0</v>
       </c>
       <c r="H14" s="66">
-        <f>IF($F14 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E14&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
+        <f>IF($F14 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E14&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
         <v>0</v>
       </c>
       <c r="I14" s="66">
-        <f>IF($F14 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E14&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
+        <f>IF($F14 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E14&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
         <v>0</v>
       </c>
       <c r="J14" s="66">
-        <f>IF($F14 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E14&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
+        <f>IF($F14 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E14&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
         <v>0</v>
       </c>
       <c r="K14" s="66">
-        <f>IF($F14 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E14&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
+        <f>IF($F14 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E14&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
         <v>0</v>
       </c>
     </row>
@@ -5476,7 +5536,7 @@
         <v>453</v>
       </c>
       <c r="C15" s="30" t="s">
-        <v>528</v>
+        <v>517</v>
       </c>
       <c r="D15" t="s">
         <v>256</v>
@@ -5494,19 +5554,19 @@
         <v>0</v>
       </c>
       <c r="H15" s="66">
-        <f>IF($F15 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E15&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
+        <f>IF($F15 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E15&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
         <v>0</v>
       </c>
       <c r="I15" s="66">
-        <f>IF($F15 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E15&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
+        <f>IF($F15 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E15&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
         <v>0</v>
       </c>
       <c r="J15" s="66">
-        <f>IF($F15 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E15&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
+        <f>IF($F15 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E15&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
         <v>0</v>
       </c>
       <c r="K15" s="66">
-        <f>IF($F15 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E15&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
+        <f>IF($F15 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E15&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
         <v>0</v>
       </c>
     </row>
@@ -5518,7 +5578,7 @@
         <v>455</v>
       </c>
       <c r="C16" s="30" t="s">
-        <v>528</v>
+        <v>517</v>
       </c>
       <c r="D16" t="s">
         <v>248</v>
@@ -5536,19 +5596,19 @@
         <v>821</v>
       </c>
       <c r="H16" s="66">
-        <f>IF($F16 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E16&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
+        <f>IF($F16 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E16&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
         <v>74.400000000000006</v>
       </c>
       <c r="I16" s="66">
-        <f>IF($F16 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E16&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
+        <f>IF($F16 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E16&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
         <v>21.16</v>
       </c>
       <c r="J16" s="66">
-        <f>IF($F16 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E16&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
+        <f>IF($F16 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E16&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
         <v>200.54</v>
       </c>
       <c r="K16" s="66">
-        <f>IF($F16 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E16&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
+        <f>IF($F16 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E16&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
         <v>1.54</v>
       </c>
     </row>
@@ -5560,7 +5620,7 @@
         <v>453</v>
       </c>
       <c r="C17" s="30" t="s">
-        <v>528</v>
+        <v>517</v>
       </c>
       <c r="D17" t="s">
         <v>248</v>
@@ -5578,19 +5638,19 @@
         <v>561</v>
       </c>
       <c r="H17" s="66">
-        <f>IF($F17 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E17&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
+        <f>IF($F17 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E17&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
         <v>76.260000000000005</v>
       </c>
       <c r="I17" s="66">
-        <f>IF($F17 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E17&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
+        <f>IF($F17 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E17&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
         <v>19.3</v>
       </c>
       <c r="J17" s="66">
-        <f>IF($F17 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E17&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
+        <f>IF($F17 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E17&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
         <v>203.5</v>
       </c>
       <c r="K17" s="66">
-        <f>IF($F17 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E17&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
+        <f>IF($F17 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E17&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
         <v>1.37</v>
       </c>
     </row>
@@ -5602,7 +5662,7 @@
         <v>455</v>
       </c>
       <c r="C18" s="30" t="s">
-        <v>528</v>
+        <v>517</v>
       </c>
       <c r="D18" t="s">
         <v>232</v>
@@ -5620,19 +5680,19 @@
         <v>2057</v>
       </c>
       <c r="H18" s="66">
-        <f>IF($F18 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E18&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
+        <f>IF($F18 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E18&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
         <v>72.2</v>
       </c>
       <c r="I18" s="66">
-        <f>IF($F18 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E18&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
+        <f>IF($F18 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E18&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
         <v>20.67</v>
       </c>
       <c r="J18" s="66">
-        <f>IF($F18 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E18&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
+        <f>IF($F18 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E18&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
         <v>199.92</v>
       </c>
       <c r="K18" s="66">
-        <f>IF($F18 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E18&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
+        <f>IF($F18 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E18&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
         <v>1.3069999999999999</v>
       </c>
     </row>
@@ -5644,7 +5704,7 @@
         <v>453</v>
       </c>
       <c r="C19" s="30" t="s">
-        <v>528</v>
+        <v>517</v>
       </c>
       <c r="D19" t="s">
         <v>232</v>
@@ -5662,19 +5722,19 @@
         <v>1686</v>
       </c>
       <c r="H19" s="66">
-        <f>IF($F19 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E19&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
+        <f>IF($F19 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E19&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
         <v>77.64</v>
       </c>
       <c r="I19" s="66">
-        <f>IF($F19 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E19&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
+        <f>IF($F19 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E19&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
         <v>20.94</v>
       </c>
       <c r="J19" s="66">
-        <f>IF($F19 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E19&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
+        <f>IF($F19 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E19&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
         <v>216.88</v>
       </c>
       <c r="K19" s="66">
-        <f>IF($F19 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E19&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
+        <f>IF($F19 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E19&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
         <v>1.151</v>
       </c>
     </row>
@@ -5686,7 +5746,7 @@
         <v>455</v>
       </c>
       <c r="C20" s="30" t="s">
-        <v>528</v>
+        <v>517</v>
       </c>
       <c r="D20" t="s">
         <v>236</v>
@@ -5704,19 +5764,19 @@
         <v>2434</v>
       </c>
       <c r="H20" s="66" t="str">
-        <f>IF($F20 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E20&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
+        <f>IF($F20 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E20&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="I20" s="66" t="str">
-        <f>IF($F20 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E20&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
+        <f>IF($F20 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E20&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="J20" s="66" t="str">
-        <f>IF($F20 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E20&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
+        <f>IF($F20 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E20&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="K20" s="66" t="str">
-        <f>IF($F20 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E20&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
+        <f>IF($F20 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E20&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
         <v>NA</v>
       </c>
     </row>
@@ -5728,7 +5788,7 @@
         <v>453</v>
       </c>
       <c r="C21" s="30" t="s">
-        <v>528</v>
+        <v>517</v>
       </c>
       <c r="D21" t="s">
         <v>236</v>
@@ -5746,19 +5806,19 @@
         <v>1076</v>
       </c>
       <c r="H21" s="66" t="str">
-        <f>IF($F21 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E21&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
+        <f>IF($F21 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E21&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="I21" s="66" t="str">
-        <f>IF($F21 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E21&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
+        <f>IF($F21 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E21&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="J21" s="66" t="str">
-        <f>IF($F21 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E21&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
+        <f>IF($F21 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E21&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="K21" s="66" t="str">
-        <f>IF($F21 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E21&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
+        <f>IF($F21 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E21&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
         <v>NA</v>
       </c>
     </row>
@@ -5770,7 +5830,7 @@
         <v>455</v>
       </c>
       <c r="C22" s="30" t="s">
-        <v>528</v>
+        <v>517</v>
       </c>
       <c r="D22" t="s">
         <v>238</v>
@@ -5788,19 +5848,19 @@
         <v>1517</v>
       </c>
       <c r="H22" s="66">
-        <f>IF($F22 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E22&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
+        <f>IF($F22 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E22&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
         <v>70.680000000000007</v>
       </c>
       <c r="I22" s="66">
-        <f>IF($F22 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E22&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
+        <f>IF($F22 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E22&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
         <v>21.47</v>
       </c>
       <c r="J22" s="66">
-        <f>IF($F22 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E22&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
+        <f>IF($F22 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E22&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
         <v>233.34</v>
       </c>
       <c r="K22" s="66">
-        <f>IF($F22 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E22&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
+        <f>IF($F22 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E22&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
         <v>1.577</v>
       </c>
     </row>
@@ -5812,7 +5872,7 @@
         <v>453</v>
       </c>
       <c r="C23" s="30" t="s">
-        <v>528</v>
+        <v>517</v>
       </c>
       <c r="D23" t="s">
         <v>238</v>
@@ -5830,19 +5890,19 @@
         <v>811</v>
       </c>
       <c r="H23" s="66">
-        <f>IF($F23 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E23&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
+        <f>IF($F23 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E23&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
         <v>72.239999999999995</v>
       </c>
       <c r="I23" s="66">
-        <f>IF($F23 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E23&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
+        <f>IF($F23 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E23&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
         <v>20.89</v>
       </c>
       <c r="J23" s="66">
-        <f>IF($F23 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E23&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
+        <f>IF($F23 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E23&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
         <v>228.67</v>
       </c>
       <c r="K23" s="66">
-        <f>IF($F23 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E23&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
+        <f>IF($F23 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E23&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
         <v>0.82050000000000001</v>
       </c>
     </row>
@@ -5854,7 +5914,7 @@
         <v>455</v>
       </c>
       <c r="C24" s="30" t="s">
-        <v>528</v>
+        <v>517</v>
       </c>
       <c r="D24" t="s">
         <v>245</v>
@@ -5872,19 +5932,19 @@
         <v>1040</v>
       </c>
       <c r="H24" s="66">
-        <f>IF($F24 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E24&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
+        <f>IF($F24 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E24&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
         <v>71.760000000000005</v>
       </c>
       <c r="I24" s="66">
-        <f>IF($F24 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E24&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
+        <f>IF($F24 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E24&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
         <v>21.87</v>
       </c>
       <c r="J24" s="66">
-        <f>IF($F24 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E24&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
+        <f>IF($F24 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E24&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
         <v>214.43</v>
       </c>
       <c r="K24" s="66">
-        <f>IF($F24 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E24&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
+        <f>IF($F24 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E24&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
         <v>1.206</v>
       </c>
     </row>
@@ -5896,7 +5956,7 @@
         <v>453</v>
       </c>
       <c r="C25" s="30" t="s">
-        <v>528</v>
+        <v>517</v>
       </c>
       <c r="D25" t="s">
         <v>245</v>
@@ -5914,19 +5974,19 @@
         <v>1642</v>
       </c>
       <c r="H25" s="66">
-        <f>IF($F25 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E25&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
+        <f>IF($F25 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E25&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
         <v>70.900000000000006</v>
       </c>
       <c r="I25" s="66">
-        <f>IF($F25 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E25&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
+        <f>IF($F25 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E25&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
         <v>20.03</v>
       </c>
       <c r="J25" s="66">
-        <f>IF($F25 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E25&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
+        <f>IF($F25 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E25&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
         <v>247.39</v>
       </c>
       <c r="K25" s="66">
-        <f>IF($F25 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E25&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
+        <f>IF($F25 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E25&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
         <v>1.2529999999999999</v>
       </c>
     </row>
@@ -5938,7 +5998,7 @@
         <v>455</v>
       </c>
       <c r="C26" s="30" t="s">
-        <v>528</v>
+        <v>517</v>
       </c>
       <c r="D26" t="s">
         <v>180</v>
@@ -5956,19 +6016,19 @@
         <v>1103</v>
       </c>
       <c r="H26" s="66" t="str">
-        <f>IF($F26 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E26&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
+        <f>IF($F26 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E26&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="I26" s="66" t="str">
-        <f>IF($F26 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E26&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
+        <f>IF($F26 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E26&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="J26" s="66" t="str">
-        <f>IF($F26 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E26&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
+        <f>IF($F26 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E26&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="K26" s="66" t="str">
-        <f>IF($F26 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E26&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
+        <f>IF($F26 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E26&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
         <v>NA</v>
       </c>
     </row>
@@ -5980,7 +6040,7 @@
         <v>453</v>
       </c>
       <c r="C27" s="30" t="s">
-        <v>528</v>
+        <v>517</v>
       </c>
       <c r="D27" t="s">
         <v>180</v>
@@ -5998,19 +6058,19 @@
         <v>813</v>
       </c>
       <c r="H27" s="66" t="str">
-        <f>IF($F27 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E27&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
+        <f>IF($F27 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E27&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="I27" s="66" t="str">
-        <f>IF($F27 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E27&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
+        <f>IF($F27 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E27&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="J27" s="66" t="str">
-        <f>IF($F27 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E27&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
+        <f>IF($F27 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E27&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="K27" s="66" t="str">
-        <f>IF($F27 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E27&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
+        <f>IF($F27 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E27&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
         <v>NA</v>
       </c>
     </row>
@@ -6022,7 +6082,7 @@
         <v>455</v>
       </c>
       <c r="C28" s="30" t="s">
-        <v>528</v>
+        <v>517</v>
       </c>
       <c r="D28" t="s">
         <v>208</v>
@@ -6040,19 +6100,19 @@
         <v>1378</v>
       </c>
       <c r="H28" s="66">
-        <f>IF($F28 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E28&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
+        <f>IF($F28 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E28&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
         <v>72.83</v>
       </c>
       <c r="I28" s="66">
-        <f>IF($F28 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E28&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
+        <f>IF($F28 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E28&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
         <v>22.67</v>
       </c>
       <c r="J28" s="66">
-        <f>IF($F28 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E28&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
+        <f>IF($F28 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E28&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
         <v>204.77</v>
       </c>
       <c r="K28" s="66">
-        <f>IF($F28 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E28&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
+        <f>IF($F28 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E28&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
         <v>1.03</v>
       </c>
     </row>
@@ -6064,7 +6124,7 @@
         <v>453</v>
       </c>
       <c r="C29" s="30" t="s">
-        <v>528</v>
+        <v>517</v>
       </c>
       <c r="D29" t="s">
         <v>208</v>
@@ -6082,19 +6142,19 @@
         <v>929</v>
       </c>
       <c r="H29" s="66">
-        <f>IF($F29 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E29&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
+        <f>IF($F29 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E29&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
         <v>72.86</v>
       </c>
       <c r="I29" s="66">
-        <f>IF($F29 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E29&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
+        <f>IF($F29 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E29&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
         <v>30.09</v>
       </c>
       <c r="J29" s="66">
-        <f>IF($F29 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E29&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
+        <f>IF($F29 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E29&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
         <v>209.51</v>
       </c>
       <c r="K29" s="66">
-        <f>IF($F29 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E29&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
+        <f>IF($F29 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E29&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
         <v>1.1819999999999999</v>
       </c>
     </row>
@@ -6106,7 +6166,7 @@
         <v>455</v>
       </c>
       <c r="C30" s="30" t="s">
-        <v>528</v>
+        <v>517</v>
       </c>
       <c r="D30" t="s">
         <v>201</v>
@@ -6124,19 +6184,19 @@
         <v>3531</v>
       </c>
       <c r="H30" s="66">
-        <f>IF($F30 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E30&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
+        <f>IF($F30 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E30&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
         <v>70.86</v>
       </c>
       <c r="I30" s="66">
-        <f>IF($F30 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E30&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
+        <f>IF($F30 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E30&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
         <v>19.559999999999999</v>
       </c>
       <c r="J30" s="66">
-        <f>IF($F30 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E30&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
+        <f>IF($F30 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E30&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
         <v>211.49</v>
       </c>
       <c r="K30" s="66">
-        <f>IF($F30 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E30&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
+        <f>IF($F30 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E30&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
         <v>1.1819999999999999</v>
       </c>
     </row>
@@ -6148,7 +6208,7 @@
         <v>453</v>
       </c>
       <c r="C31" s="30" t="s">
-        <v>528</v>
+        <v>517</v>
       </c>
       <c r="D31" t="s">
         <v>201</v>
@@ -6166,19 +6226,19 @@
         <v>2364</v>
       </c>
       <c r="H31" s="66">
-        <f>IF($F31 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E31&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
+        <f>IF($F31 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E31&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
         <v>77.36</v>
       </c>
       <c r="I31" s="66">
-        <f>IF($F31 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E31&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
+        <f>IF($F31 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E31&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
         <v>20.83</v>
       </c>
       <c r="J31" s="66">
-        <f>IF($F31 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E31&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
+        <f>IF($F31 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E31&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
         <v>219.9</v>
       </c>
       <c r="K31" s="66">
-        <f>IF($F31 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E31&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
+        <f>IF($F31 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E31&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
         <v>1.2549999999999999</v>
       </c>
     </row>
@@ -6190,7 +6250,7 @@
         <v>455</v>
       </c>
       <c r="C32" s="30" t="s">
-        <v>528</v>
+        <v>517</v>
       </c>
       <c r="D32" t="s">
         <v>198</v>
@@ -6208,19 +6268,19 @@
         <v>3975.8</v>
       </c>
       <c r="H32" s="66">
-        <f>IF($F32 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E32&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
+        <f>IF($F32 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E32&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
         <v>71.849999999999994</v>
       </c>
       <c r="I32" s="66">
-        <f>IF($F32 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E32&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
+        <f>IF($F32 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E32&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
         <v>19.86</v>
       </c>
       <c r="J32" s="66">
-        <f>IF($F32 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E32&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
+        <f>IF($F32 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E32&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
         <v>217.72</v>
       </c>
       <c r="K32" s="66">
-        <f>IF($F32 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E32&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
+        <f>IF($F32 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E32&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
         <v>2.1139999999999999</v>
       </c>
     </row>
@@ -6232,7 +6292,7 @@
         <v>453</v>
       </c>
       <c r="C33" s="30" t="s">
-        <v>528</v>
+        <v>517</v>
       </c>
       <c r="D33" t="s">
         <v>198</v>
@@ -6250,19 +6310,19 @@
         <v>2080</v>
       </c>
       <c r="H33" s="66">
-        <f>IF($F33 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E33&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
+        <f>IF($F33 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E33&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
         <v>72.73</v>
       </c>
       <c r="I33" s="66">
-        <f>IF($F33 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E33&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
+        <f>IF($F33 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E33&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
         <v>19.579999999999998</v>
       </c>
       <c r="J33" s="66">
-        <f>IF($F33 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E33&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
+        <f>IF($F33 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E33&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
         <v>220.57</v>
       </c>
       <c r="K33" s="66">
-        <f>IF($F33 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E33&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
+        <f>IF($F33 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E33&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
         <v>1.1759999999999999</v>
       </c>
     </row>
@@ -6274,7 +6334,7 @@
         <v>455</v>
       </c>
       <c r="C34" s="30" t="s">
-        <v>528</v>
+        <v>517</v>
       </c>
       <c r="D34" t="s">
         <v>177</v>
@@ -6292,19 +6352,19 @@
         <v>857</v>
       </c>
       <c r="H34" s="66" t="str">
-        <f>IF($F34 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E34&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
+        <f>IF($F34 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E34&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="I34" s="66" t="str">
-        <f>IF($F34 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E34&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
+        <f>IF($F34 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E34&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="J34" s="66" t="str">
-        <f>IF($F34 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E34&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
+        <f>IF($F34 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E34&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="K34" s="66" t="str">
-        <f>IF($F34 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E34&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
+        <f>IF($F34 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E34&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
         <v>NA</v>
       </c>
     </row>
@@ -6316,7 +6376,7 @@
         <v>453</v>
       </c>
       <c r="C35" s="30" t="s">
-        <v>528</v>
+        <v>517</v>
       </c>
       <c r="D35" t="s">
         <v>177</v>
@@ -6334,19 +6394,19 @@
         <v>705</v>
       </c>
       <c r="H35" s="66" t="str">
-        <f>IF($F35 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E35&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
+        <f>IF($F35 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E35&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="I35" s="66" t="str">
-        <f>IF($F35 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E35&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
+        <f>IF($F35 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E35&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="J35" s="66" t="str">
-        <f>IF($F35 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E35&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
+        <f>IF($F35 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E35&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="K35" s="66" t="str">
-        <f>IF($F35 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E35&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
+        <f>IF($F35 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E35&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
         <v>NA</v>
       </c>
     </row>
@@ -6358,7 +6418,7 @@
         <v>455</v>
       </c>
       <c r="C36" s="30" t="s">
-        <v>528</v>
+        <v>517</v>
       </c>
       <c r="D36" t="s">
         <v>184</v>
@@ -6376,19 +6436,19 @@
         <v>992</v>
       </c>
       <c r="H36" s="66">
-        <f>IF($F36 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E36&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
+        <f>IF($F36 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E36&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
         <v>70.849999999999994</v>
       </c>
       <c r="I36" s="66">
-        <f>IF($F36 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E36&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
+        <f>IF($F36 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E36&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
         <v>19.239999999999998</v>
       </c>
       <c r="J36" s="66">
-        <f>IF($F36 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E36&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
+        <f>IF($F36 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E36&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
         <v>205.08</v>
       </c>
       <c r="K36" s="66">
-        <f>IF($F36 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E36&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
+        <f>IF($F36 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E36&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
         <v>0.92620000000000002</v>
       </c>
     </row>
@@ -6400,7 +6460,7 @@
         <v>453</v>
       </c>
       <c r="C37" s="30" t="s">
-        <v>528</v>
+        <v>517</v>
       </c>
       <c r="D37" t="s">
         <v>184</v>
@@ -6418,19 +6478,19 @@
         <v>377</v>
       </c>
       <c r="H37" s="66">
-        <f>IF($F37 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E37&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
+        <f>IF($F37 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E37&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
         <v>71.72</v>
       </c>
       <c r="I37" s="66">
-        <f>IF($F37 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E37&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
+        <f>IF($F37 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E37&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
         <v>20.43</v>
       </c>
       <c r="J37" s="66">
-        <f>IF($F37 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E37&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
+        <f>IF($F37 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E37&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
         <v>227.49</v>
       </c>
       <c r="K37" s="66">
-        <f>IF($F37 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E37&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
+        <f>IF($F37 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E37&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
         <v>1.4910000000000001</v>
       </c>
     </row>
@@ -6442,7 +6502,7 @@
         <v>455</v>
       </c>
       <c r="C38" s="30" t="s">
-        <v>528</v>
+        <v>517</v>
       </c>
       <c r="D38" t="s">
         <v>188</v>
@@ -6460,19 +6520,19 @@
         <v>1483</v>
       </c>
       <c r="H38" s="66" t="str">
-        <f>IF($F38 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E38&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
+        <f>IF($F38 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E38&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="I38" s="66" t="str">
-        <f>IF($F38 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E38&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
+        <f>IF($F38 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E38&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="J38" s="66" t="str">
-        <f>IF($F38 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E38&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
+        <f>IF($F38 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E38&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="K38" s="66" t="str">
-        <f>IF($F38 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E38&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
+        <f>IF($F38 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E38&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
         <v>NA</v>
       </c>
     </row>
@@ -6484,7 +6544,7 @@
         <v>453</v>
       </c>
       <c r="C39" s="30" t="s">
-        <v>528</v>
+        <v>517</v>
       </c>
       <c r="D39" t="s">
         <v>188</v>
@@ -6502,19 +6562,19 @@
         <v>770</v>
       </c>
       <c r="H39" s="66" t="str">
-        <f>IF($F39 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E39&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
+        <f>IF($F39 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E39&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="I39" s="66" t="str">
-        <f>IF($F39 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E39&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
+        <f>IF($F39 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E39&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="J39" s="66" t="str">
-        <f>IF($F39 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E39&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
+        <f>IF($F39 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E39&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="K39" s="66" t="str">
-        <f>IF($F39 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E39&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
+        <f>IF($F39 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E39&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
         <v>NA</v>
       </c>
     </row>
@@ -6526,7 +6586,7 @@
         <v>455</v>
       </c>
       <c r="C40" s="30" t="s">
-        <v>528</v>
+        <v>517</v>
       </c>
       <c r="D40" t="s">
         <v>192</v>
@@ -6544,19 +6604,19 @@
         <v>1876</v>
       </c>
       <c r="H40" s="66" t="str">
-        <f>IF($F40 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E40&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
+        <f>IF($F40 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E40&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="I40" s="66" t="str">
-        <f>IF($F40 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E40&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
+        <f>IF($F40 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E40&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="J40" s="66" t="str">
-        <f>IF($F40 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E40&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
+        <f>IF($F40 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E40&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="K40" s="66" t="str">
-        <f>IF($F40 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E40&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
+        <f>IF($F40 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E40&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
         <v>NA</v>
       </c>
     </row>
@@ -6568,7 +6628,7 @@
         <v>453</v>
       </c>
       <c r="C41" s="30" t="s">
-        <v>528</v>
+        <v>517</v>
       </c>
       <c r="D41" t="s">
         <v>192</v>
@@ -6586,19 +6646,19 @@
         <v>608</v>
       </c>
       <c r="H41" s="66" t="str">
-        <f>IF($F41 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E41&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
+        <f>IF($F41 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E41&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="I41" s="66" t="str">
-        <f>IF($F41 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E41&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
+        <f>IF($F41 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E41&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="J41" s="66" t="str">
-        <f>IF($F41 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E41&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
+        <f>IF($F41 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E41&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="K41" s="66" t="str">
-        <f>IF($F41 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E41&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
+        <f>IF($F41 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E41&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
         <v>NA</v>
       </c>
     </row>
@@ -6610,7 +6670,7 @@
         <v>455</v>
       </c>
       <c r="C42" s="30" t="s">
-        <v>528</v>
+        <v>517</v>
       </c>
       <c r="D42" t="s">
         <v>212</v>
@@ -6628,19 +6688,19 @@
         <v>754</v>
       </c>
       <c r="H42" s="66">
-        <f>IF($F42 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E42&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
+        <f>IF($F42 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E42&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
         <v>73.849999999999994</v>
       </c>
       <c r="I42" s="66">
-        <f>IF($F42 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E42&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
+        <f>IF($F42 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E42&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
         <v>21.15</v>
       </c>
       <c r="J42" s="66">
-        <f>IF($F42 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E42&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
+        <f>IF($F42 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E42&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
         <v>232.37</v>
       </c>
       <c r="K42" s="66">
-        <f>IF($F42 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E42&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
+        <f>IF($F42 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E42&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
         <v>1.306</v>
       </c>
     </row>
@@ -6652,7 +6712,7 @@
         <v>453</v>
       </c>
       <c r="C43" s="30" t="s">
-        <v>528</v>
+        <v>517</v>
       </c>
       <c r="D43" t="s">
         <v>212</v>
@@ -6670,19 +6730,19 @@
         <v>582</v>
       </c>
       <c r="H43" s="66">
-        <f>IF($F43 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E43&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
+        <f>IF($F43 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E43&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
         <v>74.63</v>
       </c>
       <c r="I43" s="66">
-        <f>IF($F43 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E43&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
+        <f>IF($F43 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E43&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
         <v>21.16</v>
       </c>
       <c r="J43" s="66">
-        <f>IF($F43 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E43&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
+        <f>IF($F43 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E43&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
         <v>209.72</v>
       </c>
       <c r="K43" s="66">
-        <f>IF($F43 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E43&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
+        <f>IF($F43 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E43&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
         <v>1.3520000000000001</v>
       </c>
     </row>
@@ -6694,7 +6754,7 @@
         <v>455</v>
       </c>
       <c r="C44" s="30" t="s">
-        <v>528</v>
+        <v>517</v>
       </c>
       <c r="D44" t="s">
         <v>169</v>
@@ -6712,19 +6772,19 @@
         <v>3538</v>
       </c>
       <c r="H44" s="66">
-        <f>IF($F44 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E44&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
+        <f>IF($F44 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E44&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
         <v>74.42</v>
       </c>
       <c r="I44" s="66">
-        <f>IF($F44 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E44&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
+        <f>IF($F44 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E44&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
         <v>20.22</v>
       </c>
       <c r="J44" s="66">
-        <f>IF($F44 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E44&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
+        <f>IF($F44 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E44&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
         <v>240.09</v>
       </c>
       <c r="K44" s="66">
-        <f>IF($F44 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E44&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
+        <f>IF($F44 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E44&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
         <v>0.91800000000000004</v>
       </c>
     </row>
@@ -6736,7 +6796,7 @@
         <v>453</v>
       </c>
       <c r="C45" s="30" t="s">
-        <v>528</v>
+        <v>517</v>
       </c>
       <c r="D45" t="s">
         <v>169</v>
@@ -6754,19 +6814,19 @@
         <v>2263</v>
       </c>
       <c r="H45" s="66">
-        <f>IF($F45 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E45&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
+        <f>IF($F45 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E45&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
         <v>70.69</v>
       </c>
       <c r="I45" s="66">
-        <f>IF($F45 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E45&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
+        <f>IF($F45 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E45&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
         <v>17.940000000000001</v>
       </c>
       <c r="J45" s="66">
-        <f>IF($F45 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E45&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
+        <f>IF($F45 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E45&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
         <v>205.56</v>
       </c>
       <c r="K45" s="66">
-        <f>IF($F45 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E45&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
+        <f>IF($F45 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E45&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
         <v>0.72870000000000001</v>
       </c>
     </row>
@@ -6778,7 +6838,7 @@
         <v>455</v>
       </c>
       <c r="C46" s="30" t="s">
-        <v>528</v>
+        <v>517</v>
       </c>
       <c r="D46" t="s">
         <v>166</v>
@@ -6796,19 +6856,19 @@
         <v>2566</v>
       </c>
       <c r="H46" s="66">
-        <f>IF($F46 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E46&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
+        <f>IF($F46 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E46&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
         <v>78.55</v>
       </c>
       <c r="I46" s="66">
-        <f>IF($F46 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E46&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
+        <f>IF($F46 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E46&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
         <v>23.34</v>
       </c>
       <c r="J46" s="66">
-        <f>IF($F46 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E46&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
+        <f>IF($F46 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E46&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
         <v>187.41</v>
       </c>
       <c r="K46" s="66">
-        <f>IF($F46 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E46&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
+        <f>IF($F46 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E46&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
         <v>1.7370000000000001</v>
       </c>
     </row>
@@ -6820,7 +6880,7 @@
         <v>453</v>
       </c>
       <c r="C47" s="30" t="s">
-        <v>528</v>
+        <v>517</v>
       </c>
       <c r="D47" t="s">
         <v>166</v>
@@ -6838,19 +6898,19 @@
         <v>1512</v>
       </c>
       <c r="H47" s="66">
-        <f>IF($F47 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E47&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
+        <f>IF($F47 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E47&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
         <v>77.400000000000006</v>
       </c>
       <c r="I47" s="66">
-        <f>IF($F47 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E47&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
+        <f>IF($F47 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E47&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
         <v>19.61</v>
       </c>
       <c r="J47" s="66">
-        <f>IF($F47 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E47&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
+        <f>IF($F47 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E47&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
         <v>247.92</v>
       </c>
       <c r="K47" s="66">
-        <f>IF($F47 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E47&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
+        <f>IF($F47 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E47&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
         <v>1.0900000000000001</v>
       </c>
     </row>
@@ -6862,7 +6922,7 @@
         <v>455</v>
       </c>
       <c r="C48" s="30" t="s">
-        <v>528</v>
+        <v>517</v>
       </c>
       <c r="D48" t="s">
         <v>159</v>
@@ -6880,19 +6940,19 @@
         <v>717</v>
       </c>
       <c r="H48" s="66" t="str">
-        <f>IF($F48 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E48&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
+        <f>IF($F48 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E48&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="I48" s="66" t="str">
-        <f>IF($F48 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E48&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
+        <f>IF($F48 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E48&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="J48" s="66" t="str">
-        <f>IF($F48 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E48&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
+        <f>IF($F48 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E48&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="K48" s="66" t="str">
-        <f>IF($F48 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E48&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
+        <f>IF($F48 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E48&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
         <v>NA</v>
       </c>
     </row>
@@ -6904,7 +6964,7 @@
         <v>453</v>
       </c>
       <c r="C49" s="30" t="s">
-        <v>528</v>
+        <v>517</v>
       </c>
       <c r="D49" t="s">
         <v>159</v>
@@ -6922,19 +6982,19 @@
         <v>835</v>
       </c>
       <c r="H49" s="66" t="str">
-        <f>IF($F49 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E49&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
+        <f>IF($F49 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E49&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="I49" s="66" t="str">
-        <f>IF($F49 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E49&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
+        <f>IF($F49 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E49&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="J49" s="66" t="str">
-        <f>IF($F49 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E49&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
+        <f>IF($F49 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E49&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="K49" s="66" t="str">
-        <f>IF($F49 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E49&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
+        <f>IF($F49 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E49&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
         <v>NA</v>
       </c>
     </row>
@@ -6946,7 +7006,7 @@
         <v>455</v>
       </c>
       <c r="C50" s="30" t="s">
-        <v>528</v>
+        <v>517</v>
       </c>
       <c r="D50" t="s">
         <v>215</v>
@@ -6964,19 +7024,19 @@
         <v>12</v>
       </c>
       <c r="H50" s="66">
-        <f>IF($F50 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E50&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
+        <f>IF($F50 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E50&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
         <v>0</v>
       </c>
       <c r="I50" s="66">
-        <f>IF($F50 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E50&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
+        <f>IF($F50 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E50&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
         <v>0</v>
       </c>
       <c r="J50" s="66">
-        <f>IF($F50 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E50&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
+        <f>IF($F50 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E50&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
         <v>0</v>
       </c>
       <c r="K50" s="66">
-        <f>IF($F50 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E50&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
+        <f>IF($F50 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E50&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
         <v>0</v>
       </c>
     </row>
@@ -6988,7 +7048,7 @@
         <v>453</v>
       </c>
       <c r="C51" s="30" t="s">
-        <v>528</v>
+        <v>517</v>
       </c>
       <c r="D51" t="s">
         <v>215</v>
@@ -7006,19 +7066,19 @@
         <v>118</v>
       </c>
       <c r="H51" s="66">
-        <f>IF($F51 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E51&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
+        <f>IF($F51 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E51&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
         <v>0</v>
       </c>
       <c r="I51" s="66">
-        <f>IF($F51 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E51&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
+        <f>IF($F51 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E51&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
         <v>0</v>
       </c>
       <c r="J51" s="66">
-        <f>IF($F51 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E51&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
+        <f>IF($F51 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E51&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
         <v>0</v>
       </c>
       <c r="K51" s="66">
-        <f>IF($F51 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E51&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
+        <f>IF($F51 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E51&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
         <v>0</v>
       </c>
     </row>
@@ -7030,7 +7090,7 @@
         <v>455</v>
       </c>
       <c r="C52" s="30" t="s">
-        <v>528</v>
+        <v>517</v>
       </c>
       <c r="D52" t="s">
         <v>218</v>
@@ -7048,19 +7108,19 @@
         <v>0</v>
       </c>
       <c r="H52" s="66">
-        <f>IF($F52 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E52&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
+        <f>IF($F52 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E52&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
         <v>0</v>
       </c>
       <c r="I52" s="66">
-        <f>IF($F52 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E52&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
+        <f>IF($F52 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E52&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
         <v>0</v>
       </c>
       <c r="J52" s="66">
-        <f>IF($F52 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E52&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
+        <f>IF($F52 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E52&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
         <v>0</v>
       </c>
       <c r="K52" s="66">
-        <f>IF($F52 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E52&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
+        <f>IF($F52 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E52&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
         <v>0</v>
       </c>
     </row>
@@ -7072,7 +7132,7 @@
         <v>453</v>
       </c>
       <c r="C53" s="30" t="s">
-        <v>528</v>
+        <v>517</v>
       </c>
       <c r="D53" t="s">
         <v>218</v>
@@ -7090,19 +7150,19 @@
         <v>0</v>
       </c>
       <c r="H53" s="66">
-        <f>IF($F53 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E53&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
+        <f>IF($F53 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E53&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
         <v>0</v>
       </c>
       <c r="I53" s="66">
-        <f>IF($F53 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E53&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
+        <f>IF($F53 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E53&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
         <v>0</v>
       </c>
       <c r="J53" s="66">
-        <f>IF($F53 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E53&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
+        <f>IF($F53 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E53&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
         <v>0</v>
       </c>
       <c r="K53" s="66">
-        <f>IF($F53 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E53&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
+        <f>IF($F53 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E53&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
         <v>0</v>
       </c>
     </row>
@@ -7114,7 +7174,7 @@
         <v>455</v>
       </c>
       <c r="C54" s="30" t="s">
-        <v>528</v>
+        <v>517</v>
       </c>
       <c r="D54" t="s">
         <v>224</v>
@@ -7132,19 +7192,19 @@
         <v>0</v>
       </c>
       <c r="H54" s="66">
-        <f>IF($F54 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E54&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
+        <f>IF($F54 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E54&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
         <v>0</v>
       </c>
       <c r="I54" s="66">
-        <f>IF($F54 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E54&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
+        <f>IF($F54 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E54&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
         <v>0</v>
       </c>
       <c r="J54" s="66">
-        <f>IF($F54 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E54&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
+        <f>IF($F54 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E54&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
         <v>0</v>
       </c>
       <c r="K54" s="66">
-        <f>IF($F54 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E54&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
+        <f>IF($F54 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E54&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
         <v>0</v>
       </c>
     </row>
@@ -7156,7 +7216,7 @@
         <v>453</v>
       </c>
       <c r="C55" s="30" t="s">
-        <v>528</v>
+        <v>517</v>
       </c>
       <c r="D55" t="s">
         <v>224</v>
@@ -7174,19 +7234,19 @@
         <v>0</v>
       </c>
       <c r="H55" s="66">
-        <f>IF($F55 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E55&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
+        <f>IF($F55 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E55&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
         <v>0</v>
       </c>
       <c r="I55" s="66">
-        <f>IF($F55 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E55&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
+        <f>IF($F55 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E55&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
         <v>0</v>
       </c>
       <c r="J55" s="66">
-        <f>IF($F55 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E55&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
+        <f>IF($F55 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E55&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
         <v>0</v>
       </c>
       <c r="K55" s="66">
-        <f>IF($F55 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E55&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
+        <f>IF($F55 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E55&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
         <v>0</v>
       </c>
     </row>
@@ -7198,7 +7258,7 @@
         <v>455</v>
       </c>
       <c r="C56" s="30" t="s">
-        <v>528</v>
+        <v>517</v>
       </c>
       <c r="D56" t="s">
         <v>194</v>
@@ -7216,19 +7276,19 @@
         <v>0</v>
       </c>
       <c r="H56" s="66">
-        <f>IF($F56 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E56&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
+        <f>IF($F56 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E56&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
         <v>0</v>
       </c>
       <c r="I56" s="66">
-        <f>IF($F56 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E56&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
+        <f>IF($F56 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E56&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
         <v>0</v>
       </c>
       <c r="J56" s="66">
-        <f>IF($F56 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E56&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
+        <f>IF($F56 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E56&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
         <v>0</v>
       </c>
       <c r="K56" s="66">
-        <f>IF($F56 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E56&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
+        <f>IF($F56 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E56&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
         <v>0</v>
       </c>
     </row>
@@ -7240,7 +7300,7 @@
         <v>453</v>
       </c>
       <c r="C57" s="30" t="s">
-        <v>528</v>
+        <v>517</v>
       </c>
       <c r="D57" t="s">
         <v>194</v>
@@ -7258,19 +7318,19 @@
         <v>0</v>
       </c>
       <c r="H57" s="66">
-        <f>IF($F57 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E57&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
+        <f>IF($F57 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E57&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
         <v>0</v>
       </c>
       <c r="I57" s="66">
-        <f>IF($F57 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E57&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
+        <f>IF($F57 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E57&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
         <v>0</v>
       </c>
       <c r="J57" s="66">
-        <f>IF($F57 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E57&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
+        <f>IF($F57 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E57&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
         <v>0</v>
       </c>
       <c r="K57" s="66">
-        <f>IF($F57 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E57&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
+        <f>IF($F57 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E57&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
         <v>0</v>
       </c>
     </row>
@@ -7282,7 +7342,7 @@
         <v>455</v>
       </c>
       <c r="C58" s="30" t="s">
-        <v>528</v>
+        <v>517</v>
       </c>
       <c r="D58" t="s">
         <v>262</v>
@@ -7300,19 +7360,19 @@
         <v>1220</v>
       </c>
       <c r="H58" s="66" t="str">
-        <f>IF($F58 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E58&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
+        <f>IF($F58 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E58&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="I58" s="66" t="str">
-        <f>IF($F58 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E58&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
+        <f>IF($F58 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E58&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="J58" s="66" t="str">
-        <f>IF($F58 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E58&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
+        <f>IF($F58 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E58&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="K58" s="66" t="str">
-        <f>IF($F58 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E58&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
+        <f>IF($F58 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E58&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
         <v>NA</v>
       </c>
     </row>
@@ -7324,7 +7384,7 @@
         <v>453</v>
       </c>
       <c r="C59" s="30" t="s">
-        <v>528</v>
+        <v>517</v>
       </c>
       <c r="D59" t="s">
         <v>262</v>
@@ -7342,19 +7402,19 @@
         <v>2529</v>
       </c>
       <c r="H59" s="66" t="str">
-        <f>IF($F59 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E59&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
+        <f>IF($F59 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E59&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="I59" s="66" t="str">
-        <f>IF($F59 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E59&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
+        <f>IF($F59 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E59&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="J59" s="66" t="str">
-        <f>IF($F59 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E59&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
+        <f>IF($F59 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E59&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="K59" s="66" t="str">
-        <f>IF($F59 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E59&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
+        <f>IF($F59 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E59&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
         <v>NA</v>
       </c>
     </row>
@@ -7366,7 +7426,7 @@
         <v>455</v>
       </c>
       <c r="C60" s="30" t="s">
-        <v>528</v>
+        <v>517</v>
       </c>
       <c r="D60" t="s">
         <v>254</v>
@@ -7381,22 +7441,22 @@
       </c>
       <c r="G60" s="53">
         <f>IFERROR(INDEX(raw!$J$2:$K$86,MATCH(data!D60,raw!$B$2:$B$100,0),MATCH(data!B60,raw!$J$1:$K$1,0)), "NA")</f>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H60" s="66" t="str">
-        <f>IF($F60 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E60&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
+        <f>IF($F60 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E60&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="I60" s="66" t="str">
-        <f>IF($F60 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E60&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
+        <f>IF($F60 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E60&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="J60" s="66" t="str">
-        <f>IF($F60 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E60&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
+        <f>IF($F60 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E60&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="K60" s="66" t="str">
-        <f>IF($F60 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E60&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
+        <f>IF($F60 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E60&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
         <v>NA</v>
       </c>
     </row>
@@ -7408,7 +7468,7 @@
         <v>453</v>
       </c>
       <c r="C61" s="30" t="s">
-        <v>528</v>
+        <v>517</v>
       </c>
       <c r="D61" t="s">
         <v>254</v>
@@ -7426,19 +7486,19 @@
         <v>0</v>
       </c>
       <c r="H61" s="66" t="str">
-        <f>IF($F61 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E61&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
+        <f>IF($F61 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E61&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="I61" s="66" t="str">
-        <f>IF($F61 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E61&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
+        <f>IF($F61 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E61&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="J61" s="66" t="str">
-        <f>IF($F61 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E61&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
+        <f>IF($F61 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E61&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="K61" s="66" t="str">
-        <f>IF($F61 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E61&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
+        <f>IF($F61 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E61&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
         <v>NA</v>
       </c>
     </row>
@@ -7450,7 +7510,7 @@
         <v>455</v>
       </c>
       <c r="C62" s="30" t="s">
-        <v>528</v>
+        <v>517</v>
       </c>
       <c r="D62" t="s">
         <v>287</v>
@@ -7468,19 +7528,19 @@
         <v>NA</v>
       </c>
       <c r="H62" s="66" t="str">
-        <f>IF($F62 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E62&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
+        <f>IF($F62 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E62&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="I62" s="66" t="str">
-        <f>IF($F62 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E62&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
+        <f>IF($F62 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E62&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="J62" s="66" t="str">
-        <f>IF($F62 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E62&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
+        <f>IF($F62 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E62&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="K62" s="66" t="str">
-        <f>IF($F62 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E62&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
+        <f>IF($F62 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E62&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
         <v>NA</v>
       </c>
     </row>
@@ -7492,7 +7552,7 @@
         <v>453</v>
       </c>
       <c r="C63" s="30" t="s">
-        <v>528</v>
+        <v>517</v>
       </c>
       <c r="D63" t="s">
         <v>287</v>
@@ -7510,19 +7570,19 @@
         <v>NA</v>
       </c>
       <c r="H63" s="66" t="str">
-        <f>IF($F63 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E63&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
+        <f>IF($F63 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E63&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="I63" s="66" t="str">
-        <f>IF($F63 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E63&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
+        <f>IF($F63 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E63&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="J63" s="66" t="str">
-        <f>IF($F63 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E63&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
+        <f>IF($F63 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E63&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="K63" s="66" t="str">
-        <f>IF($F63 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E63&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
+        <f>IF($F63 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E63&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
         <v>NA</v>
       </c>
     </row>
@@ -7534,7 +7594,7 @@
         <v>455</v>
       </c>
       <c r="C64" s="30" t="s">
-        <v>528</v>
+        <v>517</v>
       </c>
       <c r="D64" t="s">
         <v>234</v>
@@ -7552,19 +7612,19 @@
         <v>926</v>
       </c>
       <c r="H64" s="66" t="str">
-        <f>IF($F64 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E64&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
+        <f>IF($F64 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E64&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="I64" s="66" t="str">
-        <f>IF($F64 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E64&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
+        <f>IF($F64 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E64&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="J64" s="66" t="str">
-        <f>IF($F64 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E64&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
+        <f>IF($F64 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E64&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="K64" s="66" t="str">
-        <f>IF($F64 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E64&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
+        <f>IF($F64 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E64&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
         <v>NA</v>
       </c>
     </row>
@@ -7576,7 +7636,7 @@
         <v>453</v>
       </c>
       <c r="C65" s="30" t="s">
-        <v>528</v>
+        <v>517</v>
       </c>
       <c r="D65" t="s">
         <v>234</v>
@@ -7594,19 +7654,19 @@
         <v>1187</v>
       </c>
       <c r="H65" s="66" t="str">
-        <f>IF($F65 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E65&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
+        <f>IF($F65 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E65&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="I65" s="66" t="str">
-        <f>IF($F65 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E65&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
+        <f>IF($F65 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E65&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="J65" s="66" t="str">
-        <f>IF($F65 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E65&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
+        <f>IF($F65 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E65&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="K65" s="66" t="str">
-        <f>IF($F65 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E65&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
+        <f>IF($F65 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E65&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
         <v>NA</v>
       </c>
     </row>
@@ -7618,7 +7678,7 @@
         <v>455</v>
       </c>
       <c r="C66" s="30" t="s">
-        <v>528</v>
+        <v>517</v>
       </c>
       <c r="D66" t="s">
         <v>258</v>
@@ -7636,19 +7696,19 @@
         <v>1396</v>
       </c>
       <c r="H66" s="66" t="str">
-        <f>IF($F66 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E66&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
+        <f>IF($F66 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E66&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="I66" s="66" t="str">
-        <f>IF($F66 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E66&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
+        <f>IF($F66 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E66&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="J66" s="66" t="str">
-        <f>IF($F66 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E66&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
+        <f>IF($F66 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E66&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="K66" s="66" t="str">
-        <f>IF($F66 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E66&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
+        <f>IF($F66 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E66&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
         <v>NA</v>
       </c>
     </row>
@@ -7660,7 +7720,7 @@
         <v>453</v>
       </c>
       <c r="C67" s="30" t="s">
-        <v>528</v>
+        <v>517</v>
       </c>
       <c r="D67" t="s">
         <v>258</v>
@@ -7678,19 +7738,19 @@
         <v>916</v>
       </c>
       <c r="H67" s="66" t="str">
-        <f>IF($F67 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E67&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
+        <f>IF($F67 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E67&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="I67" s="66" t="str">
-        <f>IF($F67 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E67&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
+        <f>IF($F67 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E67&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="J67" s="66" t="str">
-        <f>IF($F67 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E67&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
+        <f>IF($F67 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E67&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="K67" s="66" t="str">
-        <f>IF($F67 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E67&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
+        <f>IF($F67 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E67&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
         <v>NA</v>
       </c>
     </row>
@@ -7702,7 +7762,7 @@
         <v>455</v>
       </c>
       <c r="C68" s="30" t="s">
-        <v>528</v>
+        <v>517</v>
       </c>
       <c r="D68" t="s">
         <v>252</v>
@@ -7720,19 +7780,19 @@
         <v>951</v>
       </c>
       <c r="H68" s="66">
-        <f>IF($F68 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E68&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
+        <f>IF($F68 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E68&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
         <v>79.540000000000006</v>
       </c>
       <c r="I68" s="66">
-        <f>IF($F68 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E68&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
+        <f>IF($F68 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E68&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
         <v>21.31</v>
       </c>
       <c r="J68" s="66">
-        <f>IF($F68 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E68&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
+        <f>IF($F68 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E68&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
         <v>321.11</v>
       </c>
       <c r="K68" s="66">
-        <f>IF($F68 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E68&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
+        <f>IF($F68 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E68&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
         <v>1.528</v>
       </c>
     </row>
@@ -7744,7 +7804,7 @@
         <v>453</v>
       </c>
       <c r="C69" s="30" t="s">
-        <v>528</v>
+        <v>517</v>
       </c>
       <c r="D69" t="s">
         <v>252</v>
@@ -7762,19 +7822,19 @@
         <v>573.5</v>
       </c>
       <c r="H69" s="66">
-        <f>IF($F69 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E69&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
+        <f>IF($F69 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E69&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
         <v>78.98</v>
       </c>
       <c r="I69" s="66">
-        <f>IF($F69 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E69&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
+        <f>IF($F69 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E69&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
         <v>19.09</v>
       </c>
       <c r="J69" s="66">
-        <f>IF($F69 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E69&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
+        <f>IF($F69 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E69&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
         <v>226.35</v>
       </c>
       <c r="K69" s="66">
-        <f>IF($F69 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E69&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
+        <f>IF($F69 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E69&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
         <v>0.87939999999999996</v>
       </c>
     </row>
@@ -7786,7 +7846,7 @@
         <v>455</v>
       </c>
       <c r="C70" s="30" t="s">
-        <v>528</v>
+        <v>517</v>
       </c>
       <c r="D70" t="s">
         <v>229</v>
@@ -7804,19 +7864,19 @@
         <v>1891</v>
       </c>
       <c r="H70" s="66" t="str">
-        <f>IF($F70 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E70&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
+        <f>IF($F70 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E70&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="I70" s="66" t="str">
-        <f>IF($F70 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E70&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
+        <f>IF($F70 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E70&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="J70" s="66" t="str">
-        <f>IF($F70 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E70&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
+        <f>IF($F70 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E70&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="K70" s="66" t="str">
-        <f>IF($F70 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E70&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
+        <f>IF($F70 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E70&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
         <v>NA</v>
       </c>
     </row>
@@ -7828,7 +7888,7 @@
         <v>453</v>
       </c>
       <c r="C71" s="30" t="s">
-        <v>528</v>
+        <v>517</v>
       </c>
       <c r="D71" t="s">
         <v>229</v>
@@ -7846,19 +7906,19 @@
         <v>891</v>
       </c>
       <c r="H71" s="66" t="str">
-        <f>IF($F71 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E71&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
+        <f>IF($F71 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E71&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="I71" s="66" t="str">
-        <f>IF($F71 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E71&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
+        <f>IF($F71 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E71&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="J71" s="66" t="str">
-        <f>IF($F71 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E71&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
+        <f>IF($F71 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E71&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="K71" s="66" t="str">
-        <f>IF($F71 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E71&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
+        <f>IF($F71 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E71&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
         <v>NA</v>
       </c>
     </row>
@@ -7870,7 +7930,7 @@
         <v>455</v>
       </c>
       <c r="C72" s="30" t="s">
-        <v>528</v>
+        <v>517</v>
       </c>
       <c r="D72" t="s">
         <v>204</v>
@@ -7888,19 +7948,19 @@
         <v>750</v>
       </c>
       <c r="H72" s="66">
-        <f>IF($F72 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E72&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
+        <f>IF($F72 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E72&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
         <v>76</v>
       </c>
       <c r="I72" s="66">
-        <f>IF($F72 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E72&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
+        <f>IF($F72 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E72&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
         <v>22.26</v>
       </c>
       <c r="J72" s="66">
-        <f>IF($F72 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E72&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
+        <f>IF($F72 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E72&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
         <v>270.07</v>
       </c>
       <c r="K72" s="66">
-        <f>IF($F72 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E72&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
+        <f>IF($F72 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E72&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
         <v>2.4089999999999998</v>
       </c>
     </row>
@@ -7912,7 +7972,7 @@
         <v>453</v>
       </c>
       <c r="C73" s="30" t="s">
-        <v>528</v>
+        <v>517</v>
       </c>
       <c r="D73" t="s">
         <v>204</v>
@@ -7930,19 +7990,19 @@
         <v>345</v>
       </c>
       <c r="H73" s="66">
-        <f>IF($F73 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E73&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
+        <f>IF($F73 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E73&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
         <v>70.209999999999994</v>
       </c>
       <c r="I73" s="66">
-        <f>IF($F73 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E73&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
+        <f>IF($F73 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E73&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
         <v>18.68</v>
       </c>
       <c r="J73" s="66">
-        <f>IF($F73 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E73&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
+        <f>IF($F73 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E73&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
         <v>244.33</v>
       </c>
       <c r="K73" s="66">
-        <f>IF($F73 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E73&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
+        <f>IF($F73 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E73&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
         <v>1.339</v>
       </c>
     </row>
@@ -7954,7 +8014,7 @@
         <v>455</v>
       </c>
       <c r="C74" s="30" t="s">
-        <v>528</v>
+        <v>517</v>
       </c>
       <c r="D74" t="s">
         <v>242</v>
@@ -7972,19 +8032,19 @@
         <v>0</v>
       </c>
       <c r="H74" s="66">
-        <f>IF($F74 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E74&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
+        <f>IF($F74 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E74&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
         <v>0</v>
       </c>
       <c r="I74" s="66">
-        <f>IF($F74 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E74&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
+        <f>IF($F74 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E74&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
         <v>0</v>
       </c>
       <c r="J74" s="66">
-        <f>IF($F74 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E74&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
+        <f>IF($F74 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E74&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
         <v>0</v>
       </c>
       <c r="K74" s="66">
-        <f>IF($F74 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E74&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
+        <f>IF($F74 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E74&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
         <v>0</v>
       </c>
     </row>
@@ -7996,7 +8056,7 @@
         <v>453</v>
       </c>
       <c r="C75" s="30" t="s">
-        <v>528</v>
+        <v>517</v>
       </c>
       <c r="D75" t="s">
         <v>242</v>
@@ -8014,19 +8074,19 @@
         <v>125</v>
       </c>
       <c r="H75" s="66">
-        <f>IF($F75 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E75&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
+        <f>IF($F75 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E75&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
         <v>0</v>
       </c>
       <c r="I75" s="66">
-        <f>IF($F75 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E75&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
+        <f>IF($F75 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E75&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
         <v>0</v>
       </c>
       <c r="J75" s="66">
-        <f>IF($F75 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E75&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
+        <f>IF($F75 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E75&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
         <v>0</v>
       </c>
       <c r="K75" s="66">
-        <f>IF($F75 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E75&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
+        <f>IF($F75 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E75&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
         <v>0</v>
       </c>
     </row>
@@ -8038,7 +8098,7 @@
         <v>455</v>
       </c>
       <c r="C76" s="30" t="s">
-        <v>528</v>
+        <v>517</v>
       </c>
       <c r="D76" t="s">
         <v>182</v>
@@ -8056,19 +8116,19 @@
         <v>1230</v>
       </c>
       <c r="H76" s="66" t="str">
-        <f>IF($F76 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E76&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
+        <f>IF($F76 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E76&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="I76" s="66" t="str">
-        <f>IF($F76 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E76&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
+        <f>IF($F76 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E76&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="J76" s="66" t="str">
-        <f>IF($F76 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E76&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
+        <f>IF($F76 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E76&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="K76" s="66" t="str">
-        <f>IF($F76 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E76&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
+        <f>IF($F76 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E76&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
         <v>NA</v>
       </c>
     </row>
@@ -8080,7 +8140,7 @@
         <v>453</v>
       </c>
       <c r="C77" s="30" t="s">
-        <v>528</v>
+        <v>517</v>
       </c>
       <c r="D77" t="s">
         <v>182</v>
@@ -8098,19 +8158,19 @@
         <v>990</v>
       </c>
       <c r="H77" s="66" t="str">
-        <f>IF($F77 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E77&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
+        <f>IF($F77 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E77&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="I77" s="66" t="str">
-        <f>IF($F77 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E77&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
+        <f>IF($F77 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E77&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="J77" s="66" t="str">
-        <f>IF($F77 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E77&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
+        <f>IF($F77 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E77&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="K77" s="66" t="str">
-        <f>IF($F77 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E77&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
+        <f>IF($F77 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E77&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
         <v>NA</v>
       </c>
     </row>
@@ -8122,7 +8182,7 @@
         <v>455</v>
       </c>
       <c r="C78" s="30" t="s">
-        <v>528</v>
+        <v>517</v>
       </c>
       <c r="D78" t="s">
         <v>186</v>
@@ -8140,19 +8200,19 @@
         <v>1076</v>
       </c>
       <c r="H78" s="66" t="str">
-        <f>IF($F78 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E78&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
+        <f>IF($F78 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E78&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="I78" s="66" t="str">
-        <f>IF($F78 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E78&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
+        <f>IF($F78 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E78&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="J78" s="66" t="str">
-        <f>IF($F78 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E78&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
+        <f>IF($F78 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E78&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="K78" s="66" t="str">
-        <f>IF($F78 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E78&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
+        <f>IF($F78 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E78&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
         <v>NA</v>
       </c>
     </row>
@@ -8164,7 +8224,7 @@
         <v>453</v>
       </c>
       <c r="C79" s="30" t="s">
-        <v>528</v>
+        <v>517</v>
       </c>
       <c r="D79" t="s">
         <v>186</v>
@@ -8182,19 +8242,19 @@
         <v>803</v>
       </c>
       <c r="H79" s="66" t="str">
-        <f>IF($F79 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E79&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
+        <f>IF($F79 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E79&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="I79" s="66" t="str">
-        <f>IF($F79 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E79&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
+        <f>IF($F79 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E79&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="J79" s="66" t="str">
-        <f>IF($F79 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E79&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
+        <f>IF($F79 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E79&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="K79" s="66" t="str">
-        <f>IF($F79 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E79&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
+        <f>IF($F79 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E79&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
         <v>NA</v>
       </c>
     </row>
@@ -8206,7 +8266,7 @@
         <v>455</v>
       </c>
       <c r="C80" s="30" t="s">
-        <v>528</v>
+        <v>517</v>
       </c>
       <c r="D80" t="s">
         <v>190</v>
@@ -8224,19 +8284,19 @@
         <v>718</v>
       </c>
       <c r="H80" s="66" t="str">
-        <f>IF($F80 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E80&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
+        <f>IF($F80 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E80&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="I80" s="66" t="str">
-        <f>IF($F80 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E80&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
+        <f>IF($F80 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E80&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="J80" s="66" t="str">
-        <f>IF($F80 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E80&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
+        <f>IF($F80 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E80&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="K80" s="66" t="str">
-        <f>IF($F80 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E80&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
+        <f>IF($F80 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E80&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
         <v>NA</v>
       </c>
     </row>
@@ -8248,7 +8308,7 @@
         <v>453</v>
       </c>
       <c r="C81" s="30" t="s">
-        <v>528</v>
+        <v>517</v>
       </c>
       <c r="D81" t="s">
         <v>190</v>
@@ -8266,19 +8326,19 @@
         <v>512</v>
       </c>
       <c r="H81" s="66" t="str">
-        <f>IF($F81 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E81&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
+        <f>IF($F81 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E81&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="I81" s="66" t="str">
-        <f>IF($F81 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E81&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
+        <f>IF($F81 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E81&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="J81" s="66" t="str">
-        <f>IF($F81 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E81&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
+        <f>IF($F81 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E81&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="K81" s="66" t="str">
-        <f>IF($F81 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E81&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
+        <f>IF($F81 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E81&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
         <v>NA</v>
       </c>
     </row>
@@ -8290,7 +8350,7 @@
         <v>455</v>
       </c>
       <c r="C82" s="30" t="s">
-        <v>528</v>
+        <v>517</v>
       </c>
       <c r="D82" t="s">
         <v>175</v>
@@ -8308,19 +8368,19 @@
         <v>3113</v>
       </c>
       <c r="H82" s="66" t="str">
-        <f>IF($F82 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E82&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
+        <f>IF($F82 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E82&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="I82" s="66" t="str">
-        <f>IF($F82 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E82&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
+        <f>IF($F82 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E82&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="J82" s="66" t="str">
-        <f>IF($F82 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E82&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
+        <f>IF($F82 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E82&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="K82" s="66" t="str">
-        <f>IF($F82 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E82&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
+        <f>IF($F82 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E82&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
         <v>NA</v>
       </c>
     </row>
@@ -8332,7 +8392,7 @@
         <v>453</v>
       </c>
       <c r="C83" s="30" t="s">
-        <v>528</v>
+        <v>517</v>
       </c>
       <c r="D83" t="s">
         <v>175</v>
@@ -8350,19 +8410,19 @@
         <v>899</v>
       </c>
       <c r="H83" s="66" t="str">
-        <f>IF($F83 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E83&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
+        <f>IF($F83 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E83&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="I83" s="66" t="str">
-        <f>IF($F83 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E83&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
+        <f>IF($F83 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E83&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="J83" s="66" t="str">
-        <f>IF($F83 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E83&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
+        <f>IF($F83 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E83&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="K83" s="66" t="str">
-        <f>IF($F83 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E83&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
+        <f>IF($F83 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E83&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
         <v>NA</v>
       </c>
     </row>
@@ -8374,7 +8434,7 @@
         <v>455</v>
       </c>
       <c r="C84" s="30" t="s">
-        <v>528</v>
+        <v>517</v>
       </c>
       <c r="D84" t="s">
         <v>227</v>
@@ -8392,19 +8452,19 @@
         <v>2564</v>
       </c>
       <c r="H84" s="66">
-        <f>IF($F84 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E84&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
+        <f>IF($F84 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E84&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
         <v>78.48</v>
       </c>
       <c r="I84" s="66">
-        <f>IF($F84 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E84&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
+        <f>IF($F84 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E84&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
         <v>22.57</v>
       </c>
       <c r="J84" s="66">
-        <f>IF($F84 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E84&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
+        <f>IF($F84 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E84&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
         <v>282.14999999999998</v>
       </c>
       <c r="K84" s="66">
-        <f>IF($F84 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E84&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
+        <f>IF($F84 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E84&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
         <v>1.135</v>
       </c>
     </row>
@@ -8416,7 +8476,7 @@
         <v>453</v>
       </c>
       <c r="C85" s="30" t="s">
-        <v>528</v>
+        <v>517</v>
       </c>
       <c r="D85" t="s">
         <v>227</v>
@@ -8434,19 +8494,19 @@
         <v>2102</v>
       </c>
       <c r="H85" s="66">
-        <f>IF($F85 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E85&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
+        <f>IF($F85 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E85&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
         <v>75.290000000000006</v>
       </c>
       <c r="I85" s="66">
-        <f>IF($F85 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E85&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
+        <f>IF($F85 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E85&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
         <v>21.18</v>
       </c>
       <c r="J85" s="66">
-        <f>IF($F85 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E85&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
+        <f>IF($F85 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E85&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
         <v>200.61</v>
       </c>
       <c r="K85" s="66">
-        <f>IF($F85 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E85&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
+        <f>IF($F85 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E85&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
         <v>0.9385</v>
       </c>
     </row>
@@ -8458,7 +8518,7 @@
         <v>455</v>
       </c>
       <c r="C86" s="30" t="s">
-        <v>528</v>
+        <v>517</v>
       </c>
       <c r="D86" t="s">
         <v>288</v>
@@ -8476,19 +8536,19 @@
         <v>NA</v>
       </c>
       <c r="H86" s="66" t="str">
-        <f>IF($F86 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E86&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
+        <f>IF($F86 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E86&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="I86" s="66" t="str">
-        <f>IF($F86 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E86&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
+        <f>IF($F86 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E86&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="J86" s="66" t="str">
-        <f>IF($F86 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E86&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
+        <f>IF($F86 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E86&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="K86" s="66" t="str">
-        <f>IF($F86 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E86&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
+        <f>IF($F86 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E86&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
         <v>NA</v>
       </c>
     </row>
@@ -8500,7 +8560,7 @@
         <v>453</v>
       </c>
       <c r="C87" s="30" t="s">
-        <v>528</v>
+        <v>517</v>
       </c>
       <c r="D87" t="s">
         <v>288</v>
@@ -8518,19 +8578,19 @@
         <v>NA</v>
       </c>
       <c r="H87" s="66" t="str">
-        <f>IF($F87 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E87&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
+        <f>IF($F87 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E87&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="I87" s="66" t="str">
-        <f>IF($F87 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E87&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
+        <f>IF($F87 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E87&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="J87" s="66" t="str">
-        <f>IF($F87 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E87&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
+        <f>IF($F87 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E87&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="K87" s="66" t="str">
-        <f>IF($F87 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E87&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
+        <f>IF($F87 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E87&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
         <v>NA</v>
       </c>
     </row>
@@ -8542,7 +8602,7 @@
         <v>455</v>
       </c>
       <c r="C88" s="30" t="s">
-        <v>528</v>
+        <v>517</v>
       </c>
       <c r="D88" t="s">
         <v>172</v>
@@ -8560,19 +8620,19 @@
         <v>1780</v>
       </c>
       <c r="H88" s="66">
-        <f>IF($F88 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E88&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
+        <f>IF($F88 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E88&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
         <v>73.34</v>
       </c>
       <c r="I88" s="66">
-        <f>IF($F88 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E88&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
+        <f>IF($F88 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E88&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
         <v>21.97</v>
       </c>
       <c r="J88" s="66">
-        <f>IF($F88 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E88&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
+        <f>IF($F88 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E88&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
         <v>205.03</v>
       </c>
       <c r="K88" s="66">
-        <f>IF($F88 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E88&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
+        <f>IF($F88 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E88&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
         <v>1.839</v>
       </c>
     </row>
@@ -8584,7 +8644,7 @@
         <v>453</v>
       </c>
       <c r="C89" s="30" t="s">
-        <v>528</v>
+        <v>517</v>
       </c>
       <c r="D89" t="s">
         <v>172</v>
@@ -8602,19 +8662,19 @@
         <v>1728</v>
       </c>
       <c r="H89" s="66">
-        <f>IF($F89 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E89&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
+        <f>IF($F89 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E89&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
         <v>72.7</v>
       </c>
       <c r="I89" s="66">
-        <f>IF($F89 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E89&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
+        <f>IF($F89 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E89&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
         <v>19.46</v>
       </c>
       <c r="J89" s="66">
-        <f>IF($F89 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E89&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
+        <f>IF($F89 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E89&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
         <v>158.75</v>
       </c>
       <c r="K89" s="66">
-        <f>IF($F89 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E89&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
+        <f>IF($F89 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E89&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
         <v>0.66890000000000005</v>
       </c>
     </row>
@@ -8626,7 +8686,7 @@
         <v>455</v>
       </c>
       <c r="C90" s="30" t="s">
-        <v>528</v>
+        <v>517</v>
       </c>
       <c r="D90" t="s">
         <v>221</v>
@@ -8644,19 +8704,19 @@
         <v>2650</v>
       </c>
       <c r="H90" s="66">
-        <f>IF($F90 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E90&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
+        <f>IF($F90 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E90&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
         <v>71.319999999999993</v>
       </c>
       <c r="I90" s="66">
-        <f>IF($F90 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E90&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
+        <f>IF($F90 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E90&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
         <v>20.49</v>
       </c>
       <c r="J90" s="66">
-        <f>IF($F90 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E90&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
+        <f>IF($F90 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E90&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
         <v>251.3</v>
       </c>
       <c r="K90" s="66">
-        <f>IF($F90 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E90&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
+        <f>IF($F90 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E90&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
         <v>1.516</v>
       </c>
     </row>
@@ -8668,7 +8728,7 @@
         <v>453</v>
       </c>
       <c r="C91" s="30" t="s">
-        <v>528</v>
+        <v>517</v>
       </c>
       <c r="D91" t="s">
         <v>221</v>
@@ -8686,19 +8746,19 @@
         <v>1147</v>
       </c>
       <c r="H91" s="66">
-        <f>IF($F91 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E91&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
+        <f>IF($F91 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E91&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
         <v>71.37</v>
       </c>
       <c r="I91" s="66">
-        <f>IF($F91 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E91&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
+        <f>IF($F91 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E91&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
         <v>19.260000000000002</v>
       </c>
       <c r="J91" s="66">
-        <f>IF($F91 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E91&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
+        <f>IF($F91 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E91&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
         <v>265.77</v>
       </c>
       <c r="K91" s="66">
-        <f>IF($F91 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E91&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
+        <f>IF($F91 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E91&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
         <v>1.7589999999999999</v>
       </c>
     </row>
@@ -8710,7 +8770,7 @@
         <v>455</v>
       </c>
       <c r="C92" s="30" t="s">
-        <v>528</v>
+        <v>517</v>
       </c>
       <c r="D92" t="s">
         <v>163</v>
@@ -8728,19 +8788,19 @@
         <v>1514</v>
       </c>
       <c r="H92" s="66" t="str">
-        <f>IF($F92 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E92&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
+        <f>IF($F92 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E92&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="I92" s="66" t="str">
-        <f>IF($F92 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E92&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
+        <f>IF($F92 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E92&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="J92" s="66" t="str">
-        <f>IF($F92 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E92&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
+        <f>IF($F92 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E92&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="K92" s="66" t="str">
-        <f>IF($F92 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E92&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
+        <f>IF($F92 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E92&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
         <v>NA</v>
       </c>
     </row>
@@ -8752,7 +8812,7 @@
         <v>453</v>
       </c>
       <c r="C93" s="30" t="s">
-        <v>528</v>
+        <v>517</v>
       </c>
       <c r="D93" t="s">
         <v>163</v>
@@ -8770,19 +8830,19 @@
         <v>556</v>
       </c>
       <c r="H93" s="66" t="str">
-        <f>IF($F93 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E93&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
+        <f>IF($F93 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E93&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="I93" s="66" t="str">
-        <f>IF($F93 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E93&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
+        <f>IF($F93 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E93&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="J93" s="66" t="str">
-        <f>IF($F93 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E93&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
+        <f>IF($F93 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E93&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="K93" s="66" t="str">
-        <f>IF($F93 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E93&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
+        <f>IF($F93 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E93&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
         <v>NA</v>
       </c>
     </row>
@@ -8794,7 +8854,7 @@
         <v>455</v>
       </c>
       <c r="C94" s="30" t="s">
-        <v>529</v>
+        <v>518</v>
       </c>
       <c r="D94" t="s">
         <v>32</v>
@@ -8812,19 +8872,19 @@
         <v>2222</v>
       </c>
       <c r="H94" s="66" t="str">
-        <f>IF($F94 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E94&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
+        <f>IF($F94 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E94&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="I94" s="66" t="str">
-        <f>IF($F94 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E94&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
+        <f>IF($F94 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E94&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="J94" s="66" t="str">
-        <f>IF($F94 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E94&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
+        <f>IF($F94 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E94&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="K94" s="66" t="str">
-        <f>IF($F94 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E94&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
+        <f>IF($F94 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E94&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
         <v>NA</v>
       </c>
     </row>
@@ -8836,7 +8896,7 @@
         <v>453</v>
       </c>
       <c r="C95" s="30" t="s">
-        <v>529</v>
+        <v>518</v>
       </c>
       <c r="D95" t="s">
         <v>32</v>
@@ -8854,19 +8914,19 @@
         <v>939</v>
       </c>
       <c r="H95" s="66" t="str">
-        <f>IF($F95 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E95&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
+        <f>IF($F95 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E95&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="I95" s="66" t="str">
-        <f>IF($F95 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E95&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
+        <f>IF($F95 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E95&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="J95" s="66" t="str">
-        <f>IF($F95 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E95&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
+        <f>IF($F95 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E95&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="K95" s="66" t="str">
-        <f>IF($F95 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E95&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
+        <f>IF($F95 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E95&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
         <v>NA</v>
       </c>
     </row>
@@ -8878,7 +8938,7 @@
         <v>455</v>
       </c>
       <c r="C96" s="30" t="s">
-        <v>529</v>
+        <v>518</v>
       </c>
       <c r="D96" t="s">
         <v>35</v>
@@ -8893,22 +8953,22 @@
       </c>
       <c r="G96" s="53">
         <f>IFERROR(INDEX(raw!$J$2:$K$86,MATCH(data!D96,raw!$B$2:$B$100,0),MATCH(data!B96,raw!$J$1:$K$1,0)), "NA")</f>
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="H96" s="66">
-        <f>IF($F96 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E96&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
+        <f>IF($F96 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E96&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
         <v>0</v>
       </c>
       <c r="I96" s="66">
-        <f>IF($F96 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E96&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
+        <f>IF($F96 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E96&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
         <v>0</v>
       </c>
       <c r="J96" s="66">
-        <f>IF($F96 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E96&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
+        <f>IF($F96 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E96&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
         <v>0</v>
       </c>
       <c r="K96" s="66">
-        <f>IF($F96 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E96&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
+        <f>IF($F96 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E96&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
         <v>0</v>
       </c>
     </row>
@@ -8920,7 +8980,7 @@
         <v>453</v>
       </c>
       <c r="C97" s="30" t="s">
-        <v>529</v>
+        <v>518</v>
       </c>
       <c r="D97" t="s">
         <v>35</v>
@@ -8938,19 +8998,19 @@
         <v>0</v>
       </c>
       <c r="H97" s="66">
-        <f>IF($F97 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E97&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
+        <f>IF($F97 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E97&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
         <v>0</v>
       </c>
       <c r="I97" s="66">
-        <f>IF($F97 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E97&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
+        <f>IF($F97 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E97&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
         <v>0</v>
       </c>
       <c r="J97" s="66">
-        <f>IF($F97 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E97&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
+        <f>IF($F97 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E97&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
         <v>0</v>
       </c>
       <c r="K97" s="66">
-        <f>IF($F97 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E97&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
+        <f>IF($F97 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E97&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
         <v>0</v>
       </c>
     </row>
@@ -8962,7 +9022,7 @@
         <v>455</v>
       </c>
       <c r="C98" s="30" t="s">
-        <v>529</v>
+        <v>518</v>
       </c>
       <c r="D98" t="s">
         <v>65</v>
@@ -8980,19 +9040,19 @@
         <v>871</v>
       </c>
       <c r="H98" s="66">
-        <f>IF($F98 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E98&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
+        <f>IF($F98 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E98&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
         <v>74.73</v>
       </c>
       <c r="I98" s="66">
-        <f>IF($F98 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E98&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
+        <f>IF($F98 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E98&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
         <v>23.49</v>
       </c>
       <c r="J98" s="66">
-        <f>IF($F98 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E98&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
+        <f>IF($F98 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E98&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
         <v>211.46</v>
       </c>
       <c r="K98" s="66">
-        <f>IF($F98 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E98&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
+        <f>IF($F98 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E98&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
         <v>2.052</v>
       </c>
     </row>
@@ -9004,7 +9064,7 @@
         <v>453</v>
       </c>
       <c r="C99" s="30" t="s">
-        <v>529</v>
+        <v>518</v>
       </c>
       <c r="D99" t="s">
         <v>65</v>
@@ -9022,19 +9082,19 @@
         <v>401</v>
       </c>
       <c r="H99" s="66">
-        <f>IF($F99 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E99&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
+        <f>IF($F99 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E99&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
         <v>71.97</v>
       </c>
       <c r="I99" s="66">
-        <f>IF($F99 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E99&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
+        <f>IF($F99 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E99&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
         <v>15.46</v>
       </c>
       <c r="J99" s="66">
-        <f>IF($F99 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E99&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
+        <f>IF($F99 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E99&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
         <v>205.3</v>
       </c>
       <c r="K99" s="66">
-        <f>IF($F99 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E99&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
+        <f>IF($F99 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E99&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
         <v>2.879</v>
       </c>
     </row>
@@ -9046,7 +9106,7 @@
         <v>455</v>
       </c>
       <c r="C100" s="30" t="s">
-        <v>529</v>
+        <v>518</v>
       </c>
       <c r="D100" t="s">
         <v>69</v>
@@ -9063,21 +9123,21 @@
         <f>IFERROR(INDEX(raw!$J$2:$K$86,MATCH(data!D100,raw!$B$2:$B$100,0),MATCH(data!B100,raw!$J$1:$K$1,0)), "NA")</f>
         <v>994</v>
       </c>
-      <c r="H100" s="66" t="str">
-        <f>IF($F100 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E100&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
-        <v>NA</v>
-      </c>
-      <c r="I100" s="66" t="str">
-        <f>IF($F100 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E100&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
-        <v>NA</v>
-      </c>
-      <c r="J100" s="66" t="str">
-        <f>IF($F100 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E100&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
-        <v>NA</v>
-      </c>
-      <c r="K100" s="66" t="str">
-        <f>IF($F100 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E100&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
-        <v>NA</v>
+      <c r="H100" s="66">
+        <f>IF($F100 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E100&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
+        <v>70.150000000000006</v>
+      </c>
+      <c r="I100" s="66">
+        <f>IF($F100 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E100&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
+        <v>22.38</v>
+      </c>
+      <c r="J100" s="66">
+        <f>IF($F100 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E100&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
+        <v>226.21</v>
+      </c>
+      <c r="K100" s="66">
+        <f>IF($F100 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E100&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
+        <v>1.8839999999999999</v>
       </c>
     </row>
     <row r="101" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -9088,7 +9148,7 @@
         <v>453</v>
       </c>
       <c r="C101" s="30" t="s">
-        <v>529</v>
+        <v>518</v>
       </c>
       <c r="D101" t="s">
         <v>69</v>
@@ -9105,21 +9165,21 @@
         <f>IFERROR(INDEX(raw!$J$2:$K$86,MATCH(data!D101,raw!$B$2:$B$100,0),MATCH(data!B101,raw!$J$1:$K$1,0)), "NA")</f>
         <v>343</v>
       </c>
-      <c r="H101" s="66" t="str">
-        <f>IF($F101 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E101&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
-        <v>NA</v>
-      </c>
-      <c r="I101" s="66" t="str">
-        <f>IF($F101 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E101&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
-        <v>NA</v>
-      </c>
-      <c r="J101" s="66" t="str">
-        <f>IF($F101 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E101&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
-        <v>NA</v>
-      </c>
-      <c r="K101" s="66" t="str">
-        <f>IF($F101 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E101&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
-        <v>NA</v>
+      <c r="H101" s="66">
+        <f>IF($F101 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E101&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
+        <v>70.91</v>
+      </c>
+      <c r="I101" s="66">
+        <f>IF($F101 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E101&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
+        <v>16.93</v>
+      </c>
+      <c r="J101" s="66">
+        <f>IF($F101 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E101&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
+        <v>234.58</v>
+      </c>
+      <c r="K101" s="66">
+        <f>IF($F101 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E101&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
+        <v>0.74280000000000002</v>
       </c>
     </row>
     <row r="102" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -9130,7 +9190,7 @@
         <v>455</v>
       </c>
       <c r="C102" s="30" t="s">
-        <v>529</v>
+        <v>518</v>
       </c>
       <c r="D102" t="s">
         <v>97</v>
@@ -9147,21 +9207,21 @@
         <f>IFERROR(INDEX(raw!$J$2:$K$86,MATCH(data!D102,raw!$B$2:$B$100,0),MATCH(data!B102,raw!$J$1:$K$1,0)), "NA")</f>
         <v>2171</v>
       </c>
-      <c r="H102" s="66" t="str">
-        <f>IF($F102 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E102&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
-        <v>NA</v>
-      </c>
-      <c r="I102" s="66" t="str">
-        <f>IF($F102 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E102&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
-        <v>NA</v>
-      </c>
-      <c r="J102" s="66" t="str">
-        <f>IF($F102 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E102&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
-        <v>NA</v>
-      </c>
-      <c r="K102" s="66" t="str">
-        <f>IF($F102 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E102&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
-        <v>NA</v>
+      <c r="H102" s="66">
+        <f>IF($F102 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E102&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
+        <v>75.31</v>
+      </c>
+      <c r="I102" s="66">
+        <f>IF($F102 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E102&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
+        <v>22.2</v>
+      </c>
+      <c r="J102" s="66">
+        <f>IF($F102 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E102&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
+        <v>200.58</v>
+      </c>
+      <c r="K102" s="66">
+        <f>IF($F102 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E102&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
+        <v>1.0369999999999999</v>
       </c>
     </row>
     <row r="103" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -9172,7 +9232,7 @@
         <v>453</v>
       </c>
       <c r="C103" s="30" t="s">
-        <v>529</v>
+        <v>518</v>
       </c>
       <c r="D103" t="s">
         <v>97</v>
@@ -9189,21 +9249,21 @@
         <f>IFERROR(INDEX(raw!$J$2:$K$86,MATCH(data!D103,raw!$B$2:$B$100,0),MATCH(data!B103,raw!$J$1:$K$1,0)), "NA")</f>
         <v>933</v>
       </c>
-      <c r="H103" s="66" t="str">
-        <f>IF($F103 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E103&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
-        <v>NA</v>
-      </c>
-      <c r="I103" s="66" t="str">
-        <f>IF($F103 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E103&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
-        <v>NA</v>
-      </c>
-      <c r="J103" s="66" t="str">
-        <f>IF($F103 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E103&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
-        <v>NA</v>
-      </c>
-      <c r="K103" s="66" t="str">
-        <f>IF($F103 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E103&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
-        <v>NA</v>
+      <c r="H103" s="66">
+        <f>IF($F103 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E103&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
+        <v>79.260000000000005</v>
+      </c>
+      <c r="I103" s="66">
+        <f>IF($F103 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E103&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
+        <v>21.04</v>
+      </c>
+      <c r="J103" s="66">
+        <f>IF($F103 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E103&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
+        <v>202.92</v>
+      </c>
+      <c r="K103" s="66">
+        <f>IF($F103 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E103&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
+        <v>0.46689999999999998</v>
       </c>
     </row>
     <row r="104" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -9214,7 +9274,7 @@
         <v>455</v>
       </c>
       <c r="C104" s="30" t="s">
-        <v>529</v>
+        <v>518</v>
       </c>
       <c r="D104" t="s">
         <v>101</v>
@@ -9232,19 +9292,19 @@
         <v>0</v>
       </c>
       <c r="H104" s="66">
-        <f>IF($F104 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E104&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
+        <f>IF($F104 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E104&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
         <v>0</v>
       </c>
       <c r="I104" s="66">
-        <f>IF($F104 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E104&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
+        <f>IF($F104 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E104&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
         <v>0</v>
       </c>
       <c r="J104" s="66">
-        <f>IF($F104 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E104&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
+        <f>IF($F104 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E104&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
         <v>0</v>
       </c>
       <c r="K104" s="66">
-        <f>IF($F104 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E104&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
+        <f>IF($F104 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E104&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
         <v>0</v>
       </c>
     </row>
@@ -9256,7 +9316,7 @@
         <v>453</v>
       </c>
       <c r="C105" s="30" t="s">
-        <v>529</v>
+        <v>518</v>
       </c>
       <c r="D105" t="s">
         <v>101</v>
@@ -9274,19 +9334,19 @@
         <v>0</v>
       </c>
       <c r="H105" s="66">
-        <f>IF($F105 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E105&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
+        <f>IF($F105 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E105&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
         <v>0</v>
       </c>
       <c r="I105" s="66">
-        <f>IF($F105 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E105&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
+        <f>IF($F105 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E105&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
         <v>0</v>
       </c>
       <c r="J105" s="66">
-        <f>IF($F105 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E105&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
+        <f>IF($F105 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E105&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
         <v>0</v>
       </c>
       <c r="K105" s="66">
-        <f>IF($F105 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E105&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
+        <f>IF($F105 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E105&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
         <v>0</v>
       </c>
     </row>
@@ -9298,7 +9358,7 @@
         <v>455</v>
       </c>
       <c r="C106" s="30" t="s">
-        <v>529</v>
+        <v>518</v>
       </c>
       <c r="D106" t="s">
         <v>146</v>
@@ -9316,19 +9376,19 @@
         <v>0</v>
       </c>
       <c r="H106" s="66">
-        <f>IF($F106 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E106&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
+        <f>IF($F106 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E106&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
         <v>0</v>
       </c>
       <c r="I106" s="66">
-        <f>IF($F106 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E106&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
+        <f>IF($F106 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E106&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
         <v>0</v>
       </c>
       <c r="J106" s="66">
-        <f>IF($F106 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E106&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
+        <f>IF($F106 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E106&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
         <v>0</v>
       </c>
       <c r="K106" s="66">
-        <f>IF($F106 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E106&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
+        <f>IF($F106 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E106&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
         <v>0</v>
       </c>
     </row>
@@ -9340,7 +9400,7 @@
         <v>453</v>
       </c>
       <c r="C107" s="30" t="s">
-        <v>529</v>
+        <v>518</v>
       </c>
       <c r="D107" t="s">
         <v>146</v>
@@ -9358,19 +9418,19 @@
         <v>0</v>
       </c>
       <c r="H107" s="66">
-        <f>IF($F107 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E107&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
+        <f>IF($F107 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E107&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
         <v>0</v>
       </c>
       <c r="I107" s="66">
-        <f>IF($F107 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E107&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
+        <f>IF($F107 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E107&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
         <v>0</v>
       </c>
       <c r="J107" s="66">
-        <f>IF($F107 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E107&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
+        <f>IF($F107 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E107&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
         <v>0</v>
       </c>
       <c r="K107" s="66">
-        <f>IF($F107 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E107&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
+        <f>IF($F107 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E107&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
         <v>0</v>
       </c>
     </row>
@@ -9382,7 +9442,7 @@
         <v>455</v>
       </c>
       <c r="C108" s="30" t="s">
-        <v>529</v>
+        <v>518</v>
       </c>
       <c r="D108" t="s">
         <v>149</v>
@@ -9400,19 +9460,19 @@
         <v>0</v>
       </c>
       <c r="H108" s="66">
-        <f>IF($F108 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E108&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
+        <f>IF($F108 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E108&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
         <v>0</v>
       </c>
       <c r="I108" s="66">
-        <f>IF($F108 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E108&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
+        <f>IF($F108 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E108&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
         <v>0</v>
       </c>
       <c r="J108" s="66">
-        <f>IF($F108 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E108&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
+        <f>IF($F108 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E108&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
         <v>0</v>
       </c>
       <c r="K108" s="66">
-        <f>IF($F108 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E108&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
+        <f>IF($F108 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E108&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
         <v>0</v>
       </c>
     </row>
@@ -9424,7 +9484,7 @@
         <v>453</v>
       </c>
       <c r="C109" s="30" t="s">
-        <v>529</v>
+        <v>518</v>
       </c>
       <c r="D109" t="s">
         <v>149</v>
@@ -9442,19 +9502,19 @@
         <v>0</v>
       </c>
       <c r="H109" s="66">
-        <f>IF($F109 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E109&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
+        <f>IF($F109 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E109&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
         <v>0</v>
       </c>
       <c r="I109" s="66">
-        <f>IF($F109 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E109&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
+        <f>IF($F109 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E109&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
         <v>0</v>
       </c>
       <c r="J109" s="66">
-        <f>IF($F109 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E109&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
+        <f>IF($F109 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E109&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
         <v>0</v>
       </c>
       <c r="K109" s="66">
-        <f>IF($F109 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E109&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
+        <f>IF($F109 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E109&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
         <v>0</v>
       </c>
     </row>
@@ -9466,7 +9526,7 @@
         <v>455</v>
       </c>
       <c r="C110" s="30" t="s">
-        <v>529</v>
+        <v>518</v>
       </c>
       <c r="D110" t="s">
         <v>29</v>
@@ -9483,21 +9543,21 @@
         <f>IFERROR(INDEX(raw!$J$2:$K$86,MATCH(data!D110,raw!$B$2:$B$100,0),MATCH(data!B110,raw!$J$1:$K$1,0)), "NA")</f>
         <v>42</v>
       </c>
-      <c r="H110" s="66" t="str">
-        <f>IF($F110 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E110&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
-        <v>NA</v>
-      </c>
-      <c r="I110" s="66" t="str">
-        <f>IF($F110 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E110&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
-        <v>NA</v>
-      </c>
-      <c r="J110" s="66" t="str">
-        <f>IF($F110 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E110&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
-        <v>NA</v>
-      </c>
-      <c r="K110" s="66" t="str">
-        <f>IF($F110 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E110&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
-        <v>NA</v>
+      <c r="H110" s="66">
+        <f>IF($F110 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E110&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
+        <v>72.44</v>
+      </c>
+      <c r="I110" s="66">
+        <f>IF($F110 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E110&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
+        <v>23.37</v>
+      </c>
+      <c r="J110" s="66">
+        <f>IF($F110 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E110&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
+        <v>203.4</v>
+      </c>
+      <c r="K110" s="66">
+        <f>IF($F110 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E110&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
+        <v>0.2777</v>
       </c>
     </row>
     <row r="111" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -9508,7 +9568,7 @@
         <v>453</v>
       </c>
       <c r="C111" s="30" t="s">
-        <v>529</v>
+        <v>518</v>
       </c>
       <c r="D111" t="s">
         <v>29</v>
@@ -9525,21 +9585,21 @@
         <f>IFERROR(INDEX(raw!$J$2:$K$86,MATCH(data!D111,raw!$B$2:$B$100,0),MATCH(data!B111,raw!$J$1:$K$1,0)), "NA")</f>
         <v>141</v>
       </c>
-      <c r="H111" s="66" t="str">
-        <f>IF($F111 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E111&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
-        <v>NA</v>
-      </c>
-      <c r="I111" s="66" t="str">
-        <f>IF($F111 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E111&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
-        <v>NA</v>
-      </c>
-      <c r="J111" s="66" t="str">
-        <f>IF($F111 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E111&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
-        <v>NA</v>
-      </c>
-      <c r="K111" s="66" t="str">
-        <f>IF($F111 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E111&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
-        <v>NA</v>
+      <c r="H111" s="66">
+        <f>IF($F111 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E111&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
+        <v>71.790000000000006</v>
+      </c>
+      <c r="I111" s="66">
+        <f>IF($F111 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E111&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
+        <v>16.05</v>
+      </c>
+      <c r="J111" s="66">
+        <f>IF($F111 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E111&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
+        <v>217.38</v>
+      </c>
+      <c r="K111" s="66">
+        <f>IF($F111 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E111&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
+        <v>0.93279999999999996</v>
       </c>
     </row>
     <row r="112" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -9550,7 +9610,7 @@
         <v>455</v>
       </c>
       <c r="C112" s="30" t="s">
-        <v>529</v>
+        <v>518</v>
       </c>
       <c r="D112" t="s">
         <v>39</v>
@@ -9568,19 +9628,19 @@
         <v>0</v>
       </c>
       <c r="H112" s="66" t="str">
-        <f>IF($F112 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E112&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
+        <f>IF($F112 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E112&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="I112" s="66" t="str">
-        <f>IF($F112 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E112&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
+        <f>IF($F112 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E112&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="J112" s="66" t="str">
-        <f>IF($F112 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E112&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
+        <f>IF($F112 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E112&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="K112" s="66" t="str">
-        <f>IF($F112 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E112&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
+        <f>IF($F112 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E112&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
         <v>NA</v>
       </c>
     </row>
@@ -9592,7 +9652,7 @@
         <v>453</v>
       </c>
       <c r="C113" s="30" t="s">
-        <v>529</v>
+        <v>518</v>
       </c>
       <c r="D113" t="s">
         <v>39</v>
@@ -9610,19 +9670,19 @@
         <v>0</v>
       </c>
       <c r="H113" s="66" t="str">
-        <f>IF($F113 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E113&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
+        <f>IF($F113 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E113&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="I113" s="66" t="str">
-        <f>IF($F113 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E113&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
+        <f>IF($F113 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E113&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="J113" s="66" t="str">
-        <f>IF($F113 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E113&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
+        <f>IF($F113 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E113&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="K113" s="66" t="str">
-        <f>IF($F113 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E113&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
+        <f>IF($F113 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E113&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
         <v>NA</v>
       </c>
     </row>
@@ -9634,7 +9694,7 @@
         <v>455</v>
       </c>
       <c r="C114" s="30" t="s">
-        <v>529</v>
+        <v>518</v>
       </c>
       <c r="D114" t="s">
         <v>59</v>
@@ -9652,19 +9712,19 @@
         <v>0</v>
       </c>
       <c r="H114" s="66" t="str">
-        <f>IF($F114 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E114&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
+        <f>IF($F114 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E114&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="I114" s="66" t="str">
-        <f>IF($F114 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E114&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
+        <f>IF($F114 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E114&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="J114" s="66" t="str">
-        <f>IF($F114 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E114&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
+        <f>IF($F114 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E114&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="K114" s="66" t="str">
-        <f>IF($F114 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E114&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
+        <f>IF($F114 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E114&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
         <v>NA</v>
       </c>
     </row>
@@ -9676,7 +9736,7 @@
         <v>453</v>
       </c>
       <c r="C115" s="30" t="s">
-        <v>529</v>
+        <v>518</v>
       </c>
       <c r="D115" t="s">
         <v>59</v>
@@ -9694,19 +9754,19 @@
         <v>0</v>
       </c>
       <c r="H115" s="66" t="str">
-        <f>IF($F115 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E115&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
+        <f>IF($F115 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E115&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="I115" s="66" t="str">
-        <f>IF($F115 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E115&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
+        <f>IF($F115 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E115&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="J115" s="66" t="str">
-        <f>IF($F115 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E115&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
+        <f>IF($F115 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E115&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="K115" s="66" t="str">
-        <f>IF($F115 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E115&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
+        <f>IF($F115 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E115&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
         <v>NA</v>
       </c>
     </row>
@@ -9718,7 +9778,7 @@
         <v>455</v>
       </c>
       <c r="C116" s="30" t="s">
-        <v>529</v>
+        <v>518</v>
       </c>
       <c r="D116" t="s">
         <v>75</v>
@@ -9735,21 +9795,21 @@
         <f>IFERROR(INDEX(raw!$J$2:$K$86,MATCH(data!D116,raw!$B$2:$B$100,0),MATCH(data!B116,raw!$J$1:$K$1,0)), "NA")</f>
         <v>2695</v>
       </c>
-      <c r="H116" s="66" t="str">
-        <f>IF($F116 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E116&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
-        <v>NA</v>
-      </c>
-      <c r="I116" s="66" t="str">
-        <f>IF($F116 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E116&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
-        <v>NA</v>
-      </c>
-      <c r="J116" s="66" t="str">
-        <f>IF($F116 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E116&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
-        <v>NA</v>
-      </c>
-      <c r="K116" s="66" t="str">
-        <f>IF($F116 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E116&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
-        <v>NA</v>
+      <c r="H116" s="66">
+        <f>IF($F116 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E116&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
+        <v>78.14</v>
+      </c>
+      <c r="I116" s="66">
+        <f>IF($F116 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E116&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
+        <v>23.36</v>
+      </c>
+      <c r="J116" s="66">
+        <f>IF($F116 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E116&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
+        <v>207.98</v>
+      </c>
+      <c r="K116" s="66">
+        <f>IF($F116 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E116&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
+        <v>0.6583</v>
       </c>
     </row>
     <row r="117" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -9760,7 +9820,7 @@
         <v>453</v>
       </c>
       <c r="C117" s="30" t="s">
-        <v>529</v>
+        <v>518</v>
       </c>
       <c r="D117" t="s">
         <v>75</v>
@@ -9777,21 +9837,21 @@
         <f>IFERROR(INDEX(raw!$J$2:$K$86,MATCH(data!D117,raw!$B$2:$B$100,0),MATCH(data!B117,raw!$J$1:$K$1,0)), "NA")</f>
         <v>1160</v>
       </c>
-      <c r="H117" s="66" t="str">
-        <f>IF($F117 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E117&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
-        <v>NA</v>
-      </c>
-      <c r="I117" s="66" t="str">
-        <f>IF($F117 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E117&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
-        <v>NA</v>
-      </c>
-      <c r="J117" s="66" t="str">
-        <f>IF($F117 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E117&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
-        <v>NA</v>
-      </c>
-      <c r="K117" s="66" t="str">
-        <f>IF($F117 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E117&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
-        <v>NA</v>
+      <c r="H117" s="66">
+        <f>IF($F117 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E117&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
+        <v>77.47</v>
+      </c>
+      <c r="I117" s="66">
+        <f>IF($F117 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E117&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
+        <v>19.59</v>
+      </c>
+      <c r="J117" s="66">
+        <f>IF($F117 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E117&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
+        <v>214.68</v>
+      </c>
+      <c r="K117" s="66">
+        <f>IF($F117 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E117&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
+        <v>0.83840000000000003</v>
       </c>
     </row>
     <row r="118" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -9802,7 +9862,7 @@
         <v>455</v>
       </c>
       <c r="C118" s="30" t="s">
-        <v>529</v>
+        <v>518</v>
       </c>
       <c r="D118" t="s">
         <v>89</v>
@@ -9819,21 +9879,21 @@
         <f>IFERROR(INDEX(raw!$J$2:$K$86,MATCH(data!D118,raw!$B$2:$B$100,0),MATCH(data!B118,raw!$J$1:$K$1,0)), "NA")</f>
         <v>2790</v>
       </c>
-      <c r="H118" s="66" t="str">
-        <f>IF($F118 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E118&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
-        <v>NA</v>
-      </c>
-      <c r="I118" s="66" t="str">
-        <f>IF($F118 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E118&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
-        <v>NA</v>
-      </c>
-      <c r="J118" s="66" t="str">
-        <f>IF($F118 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E118&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
-        <v>NA</v>
-      </c>
-      <c r="K118" s="66" t="str">
-        <f>IF($F118 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E118&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
-        <v>NA</v>
+      <c r="H118" s="66">
+        <f>IF($F118 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E118&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
+        <v>76.77</v>
+      </c>
+      <c r="I118" s="66">
+        <f>IF($F118 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E118&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
+        <v>21.82</v>
+      </c>
+      <c r="J118" s="66">
+        <f>IF($F118 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E118&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
+        <v>202.31</v>
+      </c>
+      <c r="K118" s="66">
+        <f>IF($F118 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E118&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
+        <v>1.6120000000000001</v>
       </c>
     </row>
     <row r="119" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -9844,7 +9904,7 @@
         <v>453</v>
       </c>
       <c r="C119" s="30" t="s">
-        <v>529</v>
+        <v>518</v>
       </c>
       <c r="D119" t="s">
         <v>89</v>
@@ -9861,21 +9921,21 @@
         <f>IFERROR(INDEX(raw!$J$2:$K$86,MATCH(data!D119,raw!$B$2:$B$100,0),MATCH(data!B119,raw!$J$1:$K$1,0)), "NA")</f>
         <v>888</v>
       </c>
-      <c r="H119" s="66" t="str">
-        <f>IF($F119 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E119&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
-        <v>NA</v>
-      </c>
-      <c r="I119" s="66" t="str">
-        <f>IF($F119 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E119&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
-        <v>NA</v>
-      </c>
-      <c r="J119" s="66" t="str">
-        <f>IF($F119 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E119&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
-        <v>NA</v>
-      </c>
-      <c r="K119" s="66" t="str">
-        <f>IF($F119 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E119&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
-        <v>NA</v>
+      <c r="H119" s="66">
+        <f>IF($F119 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E119&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
+        <v>72.19</v>
+      </c>
+      <c r="I119" s="66">
+        <f>IF($F119 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E119&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
+        <v>16.66</v>
+      </c>
+      <c r="J119" s="66">
+        <f>IF($F119 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E119&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
+        <v>201.97</v>
+      </c>
+      <c r="K119" s="66">
+        <f>IF($F119 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E119&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
+        <v>1.1459999999999999</v>
       </c>
     </row>
     <row r="120" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -9886,7 +9946,7 @@
         <v>455</v>
       </c>
       <c r="C120" s="30" t="s">
-        <v>529</v>
+        <v>518</v>
       </c>
       <c r="D120" t="s">
         <v>108</v>
@@ -9903,21 +9963,21 @@
         <f>IFERROR(INDEX(raw!$J$2:$K$86,MATCH(data!D120,raw!$B$2:$B$100,0),MATCH(data!B120,raw!$J$1:$K$1,0)), "NA")</f>
         <v>2715</v>
       </c>
-      <c r="H120" s="66" t="str">
-        <f>IF($F120 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E120&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
-        <v>NA</v>
-      </c>
-      <c r="I120" s="66" t="str">
-        <f>IF($F120 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E120&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
-        <v>NA</v>
-      </c>
-      <c r="J120" s="66" t="str">
-        <f>IF($F120 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E120&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
-        <v>NA</v>
-      </c>
-      <c r="K120" s="66" t="str">
-        <f>IF($F120 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E120&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
-        <v>NA</v>
+      <c r="H120" s="66">
+        <f>IF($F120 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E120&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
+        <v>70.52</v>
+      </c>
+      <c r="I120" s="66">
+        <f>IF($F120 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E120&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
+        <v>20.329999999999998</v>
+      </c>
+      <c r="J120" s="66">
+        <f>IF($F120 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E120&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
+        <v>219.22</v>
+      </c>
+      <c r="K120" s="66">
+        <f>IF($F120 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E120&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
+        <v>0.94920000000000004</v>
       </c>
     </row>
     <row r="121" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -9928,7 +9988,7 @@
         <v>453</v>
       </c>
       <c r="C121" s="30" t="s">
-        <v>529</v>
+        <v>518</v>
       </c>
       <c r="D121" t="s">
         <v>108</v>
@@ -9945,21 +10005,21 @@
         <f>IFERROR(INDEX(raw!$J$2:$K$86,MATCH(data!D121,raw!$B$2:$B$100,0),MATCH(data!B121,raw!$J$1:$K$1,0)), "NA")</f>
         <v>1696</v>
       </c>
-      <c r="H121" s="66" t="str">
-        <f>IF($F121 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E121&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
-        <v>NA</v>
-      </c>
-      <c r="I121" s="66" t="str">
-        <f>IF($F121 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E121&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
-        <v>NA</v>
-      </c>
-      <c r="J121" s="66" t="str">
-        <f>IF($F121 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E121&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
-        <v>NA</v>
-      </c>
-      <c r="K121" s="66" t="str">
-        <f>IF($F121 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E121&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
-        <v>NA</v>
+      <c r="H121" s="66">
+        <f>IF($F121 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E121&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
+        <v>75.41</v>
+      </c>
+      <c r="I121" s="66">
+        <f>IF($F121 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E121&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
+        <v>19.3</v>
+      </c>
+      <c r="J121" s="66">
+        <f>IF($F121 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E121&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
+        <v>222.34</v>
+      </c>
+      <c r="K121" s="66">
+        <f>IF($F121 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E121&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
+        <v>1.0329999999999999</v>
       </c>
     </row>
     <row r="122" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -9970,7 +10030,7 @@
         <v>455</v>
       </c>
       <c r="C122" s="30" t="s">
-        <v>529</v>
+        <v>518</v>
       </c>
       <c r="D122" t="s">
         <v>140</v>
@@ -9987,21 +10047,21 @@
         <f>IFERROR(INDEX(raw!$J$2:$K$86,MATCH(data!D122,raw!$B$2:$B$100,0),MATCH(data!B122,raw!$J$1:$K$1,0)), "NA")</f>
         <v>1871</v>
       </c>
-      <c r="H122" s="66" t="str">
-        <f>IF($F122 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E122&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
-        <v>NA</v>
-      </c>
-      <c r="I122" s="66" t="str">
-        <f>IF($F122 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E122&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
-        <v>NA</v>
-      </c>
-      <c r="J122" s="66" t="str">
-        <f>IF($F122 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E122&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
-        <v>NA</v>
-      </c>
-      <c r="K122" s="66" t="str">
-        <f>IF($F122 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E122&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
-        <v>NA</v>
+      <c r="H122" s="66">
+        <f>IF($F122 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E122&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
+        <v>70.739999999999995</v>
+      </c>
+      <c r="I122" s="66">
+        <f>IF($F122 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E122&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
+        <v>19.760000000000002</v>
+      </c>
+      <c r="J122" s="66">
+        <f>IF($F122 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E122&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
+        <v>203.01</v>
+      </c>
+      <c r="K122" s="66">
+        <f>IF($F122 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E122&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
+        <v>0.40550000000000003</v>
       </c>
     </row>
     <row r="123" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -10012,7 +10072,7 @@
         <v>453</v>
       </c>
       <c r="C123" s="30" t="s">
-        <v>529</v>
+        <v>518</v>
       </c>
       <c r="D123" t="s">
         <v>140</v>
@@ -10029,21 +10089,21 @@
         <f>IFERROR(INDEX(raw!$J$2:$K$86,MATCH(data!D123,raw!$B$2:$B$100,0),MATCH(data!B123,raw!$J$1:$K$1,0)), "NA")</f>
         <v>1585</v>
       </c>
-      <c r="H123" s="66" t="str">
-        <f>IF($F123 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E123&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
-        <v>NA</v>
-      </c>
-      <c r="I123" s="66" t="str">
-        <f>IF($F123 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E123&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
-        <v>NA</v>
-      </c>
-      <c r="J123" s="66" t="str">
-        <f>IF($F123 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E123&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
-        <v>NA</v>
-      </c>
-      <c r="K123" s="66" t="str">
-        <f>IF($F123 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E123&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
-        <v>NA</v>
+      <c r="H123" s="66">
+        <f>IF($F123 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E123&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
+        <v>75.75</v>
+      </c>
+      <c r="I123" s="66">
+        <f>IF($F123 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E123&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
+        <v>18.14</v>
+      </c>
+      <c r="J123" s="66">
+        <f>IF($F123 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E123&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
+        <v>212.14</v>
+      </c>
+      <c r="K123" s="66">
+        <f>IF($F123 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E123&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
+        <v>0.25940000000000002</v>
       </c>
     </row>
     <row r="124" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -10054,7 +10114,7 @@
         <v>455</v>
       </c>
       <c r="C124" s="30" t="s">
-        <v>529</v>
+        <v>518</v>
       </c>
       <c r="D124" t="s">
         <v>136</v>
@@ -10071,21 +10131,21 @@
         <f>IFERROR(INDEX(raw!$J$2:$K$86,MATCH(data!D124,raw!$B$2:$B$100,0),MATCH(data!B124,raw!$J$1:$K$1,0)), "NA")</f>
         <v>645</v>
       </c>
-      <c r="H124" s="66" t="str">
-        <f>IF($F124 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E124&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
-        <v>NA</v>
-      </c>
-      <c r="I124" s="66" t="str">
-        <f>IF($F124 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E124&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
-        <v>NA</v>
-      </c>
-      <c r="J124" s="66" t="str">
-        <f>IF($F124 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E124&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
-        <v>NA</v>
-      </c>
-      <c r="K124" s="66" t="str">
-        <f>IF($F124 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E124&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
-        <v>NA</v>
+      <c r="H124" s="66">
+        <f>IF($F124 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E124&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
+        <v>76.7</v>
+      </c>
+      <c r="I124" s="66">
+        <f>IF($F124 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E124&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
+        <v>23.23</v>
+      </c>
+      <c r="J124" s="66">
+        <f>IF($F124 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E124&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
+        <v>209.94</v>
+      </c>
+      <c r="K124" s="66">
+        <f>IF($F124 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E124&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
+        <v>1.333</v>
       </c>
     </row>
     <row r="125" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -10096,7 +10156,7 @@
         <v>453</v>
       </c>
       <c r="C125" s="30" t="s">
-        <v>529</v>
+        <v>518</v>
       </c>
       <c r="D125" t="s">
         <v>136</v>
@@ -10113,21 +10173,21 @@
         <f>IFERROR(INDEX(raw!$J$2:$K$86,MATCH(data!D125,raw!$B$2:$B$100,0),MATCH(data!B125,raw!$J$1:$K$1,0)), "NA")</f>
         <v>607</v>
       </c>
-      <c r="H125" s="66" t="str">
-        <f>IF($F125 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E125&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
-        <v>NA</v>
-      </c>
-      <c r="I125" s="66" t="str">
-        <f>IF($F125 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E125&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
-        <v>NA</v>
-      </c>
-      <c r="J125" s="66" t="str">
-        <f>IF($F125 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E125&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
-        <v>NA</v>
-      </c>
-      <c r="K125" s="66" t="str">
-        <f>IF($F125 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E125&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
-        <v>NA</v>
+      <c r="H125" s="66">
+        <f>IF($F125 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E125&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
+        <v>70.63</v>
+      </c>
+      <c r="I125" s="66">
+        <f>IF($F125 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E125&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
+        <v>16.899999999999999</v>
+      </c>
+      <c r="J125" s="66">
+        <f>IF($F125 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E125&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
+        <v>202.3</v>
+      </c>
+      <c r="K125" s="66">
+        <f>IF($F125 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E125&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
+        <v>0.2412</v>
       </c>
     </row>
     <row r="126" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -10138,7 +10198,7 @@
         <v>455</v>
       </c>
       <c r="C126" s="30" t="s">
-        <v>529</v>
+        <v>518</v>
       </c>
       <c r="D126" t="s">
         <v>25</v>
@@ -10155,21 +10215,21 @@
         <f>IFERROR(INDEX(raw!$J$2:$K$86,MATCH(data!D126,raw!$B$2:$B$100,0),MATCH(data!B126,raw!$J$1:$K$1,0)), "NA")</f>
         <v>315</v>
       </c>
-      <c r="H126" s="66" t="str">
-        <f>IF($F126 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E126&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
-        <v>NA</v>
-      </c>
-      <c r="I126" s="66" t="str">
-        <f>IF($F126 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E126&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
-        <v>NA</v>
-      </c>
-      <c r="J126" s="66" t="str">
-        <f>IF($F126 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E126&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
-        <v>NA</v>
-      </c>
-      <c r="K126" s="66" t="str">
-        <f>IF($F126 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E126&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
-        <v>NA</v>
+      <c r="H126" s="66">
+        <f>IF($F126 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E126&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
+        <v>72.44</v>
+      </c>
+      <c r="I126" s="66">
+        <f>IF($F126 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E126&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
+        <v>23.37</v>
+      </c>
+      <c r="J126" s="66">
+        <f>IF($F126 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E126&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
+        <v>203.4</v>
+      </c>
+      <c r="K126" s="66">
+        <f>IF($F126 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E126&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
+        <v>0.2777</v>
       </c>
     </row>
     <row r="127" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -10180,7 +10240,7 @@
         <v>453</v>
       </c>
       <c r="C127" s="30" t="s">
-        <v>529</v>
+        <v>518</v>
       </c>
       <c r="D127" t="s">
         <v>25</v>
@@ -10197,21 +10257,21 @@
         <f>IFERROR(INDEX(raw!$J$2:$K$86,MATCH(data!D127,raw!$B$2:$B$100,0),MATCH(data!B127,raw!$J$1:$K$1,0)), "NA")</f>
         <v>250</v>
       </c>
-      <c r="H127" s="66" t="str">
-        <f>IF($F127 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E127&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
-        <v>NA</v>
-      </c>
-      <c r="I127" s="66" t="str">
-        <f>IF($F127 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E127&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
-        <v>NA</v>
-      </c>
-      <c r="J127" s="66" t="str">
-        <f>IF($F127 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E127&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
-        <v>NA</v>
-      </c>
-      <c r="K127" s="66" t="str">
-        <f>IF($F127 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E127&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
-        <v>NA</v>
+      <c r="H127" s="66">
+        <f>IF($F127 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E127&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
+        <v>71.790000000000006</v>
+      </c>
+      <c r="I127" s="66">
+        <f>IF($F127 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E127&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
+        <v>16.05</v>
+      </c>
+      <c r="J127" s="66">
+        <f>IF($F127 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E127&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
+        <v>217.38</v>
+      </c>
+      <c r="K127" s="66">
+        <f>IF($F127 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E127&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
+        <v>0.93279999999999996</v>
       </c>
     </row>
     <row r="128" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -10222,7 +10282,7 @@
         <v>455</v>
       </c>
       <c r="C128" s="30" t="s">
-        <v>529</v>
+        <v>518</v>
       </c>
       <c r="D128" t="s">
         <v>48</v>
@@ -10240,19 +10300,19 @@
         <v>2797</v>
       </c>
       <c r="H128" s="66" t="str">
-        <f>IF($F128 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E128&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
+        <f>IF($F128 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E128&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="I128" s="66" t="str">
-        <f>IF($F128 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E128&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
+        <f>IF($F128 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E128&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="J128" s="66" t="str">
-        <f>IF($F128 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E128&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
+        <f>IF($F128 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E128&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="K128" s="66" t="str">
-        <f>IF($F128 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E128&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
+        <f>IF($F128 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E128&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
         <v>NA</v>
       </c>
     </row>
@@ -10264,7 +10324,7 @@
         <v>453</v>
       </c>
       <c r="C129" s="30" t="s">
-        <v>529</v>
+        <v>518</v>
       </c>
       <c r="D129" t="s">
         <v>48</v>
@@ -10282,19 +10342,19 @@
         <v>1048</v>
       </c>
       <c r="H129" s="66" t="str">
-        <f>IF($F129 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E129&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
+        <f>IF($F129 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E129&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="I129" s="66" t="str">
-        <f>IF($F129 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E129&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
+        <f>IF($F129 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E129&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="J129" s="66" t="str">
-        <f>IF($F129 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E129&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
+        <f>IF($F129 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E129&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="K129" s="66" t="str">
-        <f>IF($F129 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E129&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
+        <f>IF($F129 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E129&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
         <v>NA</v>
       </c>
     </row>
@@ -10306,7 +10366,7 @@
         <v>455</v>
       </c>
       <c r="C130" s="30" t="s">
-        <v>529</v>
+        <v>518</v>
       </c>
       <c r="D130" t="s">
         <v>56</v>
@@ -10324,19 +10384,19 @@
         <v>1701</v>
       </c>
       <c r="H130" s="66" t="str">
-        <f>IF($F130 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E130&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
+        <f>IF($F130 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E130&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="I130" s="66" t="str">
-        <f>IF($F130 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E130&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
+        <f>IF($F130 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E130&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="J130" s="66" t="str">
-        <f>IF($F130 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E130&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
+        <f>IF($F130 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E130&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="K130" s="66" t="str">
-        <f>IF($F130 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E130&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
+        <f>IF($F130 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E130&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
         <v>NA</v>
       </c>
     </row>
@@ -10348,7 +10408,7 @@
         <v>453</v>
       </c>
       <c r="C131" s="30" t="s">
-        <v>529</v>
+        <v>518</v>
       </c>
       <c r="D131" t="s">
         <v>56</v>
@@ -10366,19 +10426,19 @@
         <v>1821</v>
       </c>
       <c r="H131" s="66" t="str">
-        <f>IF($F131 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E131&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
+        <f>IF($F131 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E131&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="I131" s="66" t="str">
-        <f>IF($F131 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E131&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
+        <f>IF($F131 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E131&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="J131" s="66" t="str">
-        <f>IF($F131 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E131&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
+        <f>IF($F131 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E131&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="K131" s="66" t="str">
-        <f>IF($F131 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E131&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
+        <f>IF($F131 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E131&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
         <v>NA</v>
       </c>
     </row>
@@ -10390,7 +10450,7 @@
         <v>455</v>
       </c>
       <c r="C132" s="30" t="s">
-        <v>529</v>
+        <v>518</v>
       </c>
       <c r="D132" t="s">
         <v>272</v>
@@ -10408,19 +10468,19 @@
         <v>NA</v>
       </c>
       <c r="H132" s="66" t="str">
-        <f>IF($F132 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E132&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
+        <f>IF($F132 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E132&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="I132" s="66" t="str">
-        <f>IF($F132 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E132&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
+        <f>IF($F132 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E132&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="J132" s="66" t="str">
-        <f>IF($F132 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E132&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
+        <f>IF($F132 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E132&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="K132" s="66" t="str">
-        <f>IF($F132 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E132&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
+        <f>IF($F132 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E132&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
         <v>NA</v>
       </c>
     </row>
@@ -10432,7 +10492,7 @@
         <v>453</v>
       </c>
       <c r="C133" s="30" t="s">
-        <v>529</v>
+        <v>518</v>
       </c>
       <c r="D133" t="s">
         <v>272</v>
@@ -10450,19 +10510,19 @@
         <v>NA</v>
       </c>
       <c r="H133" s="66" t="str">
-        <f>IF($F133 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E133&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
+        <f>IF($F133 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E133&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="I133" s="66" t="str">
-        <f>IF($F133 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E133&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
+        <f>IF($F133 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E133&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="J133" s="66" t="str">
-        <f>IF($F133 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E133&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
+        <f>IF($F133 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E133&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="K133" s="66" t="str">
-        <f>IF($F133 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E133&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
+        <f>IF($F133 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E133&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
         <v>NA</v>
       </c>
     </row>
@@ -10474,7 +10534,7 @@
         <v>455</v>
       </c>
       <c r="C134" s="30" t="s">
-        <v>529</v>
+        <v>518</v>
       </c>
       <c r="D134" t="s">
         <v>80</v>
@@ -10492,19 +10552,19 @@
         <v>0</v>
       </c>
       <c r="H134" s="66">
-        <f>IF($F134 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E134&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
+        <f>IF($F134 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E134&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
         <v>0</v>
       </c>
       <c r="I134" s="66">
-        <f>IF($F134 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E134&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
+        <f>IF($F134 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E134&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
         <v>0</v>
       </c>
       <c r="J134" s="66">
-        <f>IF($F134 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E134&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
+        <f>IF($F134 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E134&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
         <v>0</v>
       </c>
       <c r="K134" s="66">
-        <f>IF($F134 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E134&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
+        <f>IF($F134 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E134&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
         <v>0</v>
       </c>
     </row>
@@ -10516,7 +10576,7 @@
         <v>453</v>
       </c>
       <c r="C135" s="30" t="s">
-        <v>529</v>
+        <v>518</v>
       </c>
       <c r="D135" t="s">
         <v>80</v>
@@ -10534,19 +10594,19 @@
         <v>0</v>
       </c>
       <c r="H135" s="66">
-        <f>IF($F135 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E135&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
+        <f>IF($F135 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E135&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
         <v>0</v>
       </c>
       <c r="I135" s="66">
-        <f>IF($F135 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E135&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
+        <f>IF($F135 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E135&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
         <v>0</v>
       </c>
       <c r="J135" s="66">
-        <f>IF($F135 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E135&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
+        <f>IF($F135 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E135&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
         <v>0</v>
       </c>
       <c r="K135" s="66">
-        <f>IF($F135 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E135&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
+        <f>IF($F135 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E135&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
         <v>0</v>
       </c>
     </row>
@@ -10558,7 +10618,7 @@
         <v>455</v>
       </c>
       <c r="C136" s="30" t="s">
-        <v>529</v>
+        <v>518</v>
       </c>
       <c r="D136" t="s">
         <v>115</v>
@@ -10576,19 +10636,19 @@
         <v>228</v>
       </c>
       <c r="H136" s="66">
-        <f>IF($F136 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E136&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
+        <f>IF($F136 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E136&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
         <v>0</v>
       </c>
       <c r="I136" s="66">
-        <f>IF($F136 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E136&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
+        <f>IF($F136 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E136&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
         <v>0</v>
       </c>
       <c r="J136" s="66">
-        <f>IF($F136 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E136&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
+        <f>IF($F136 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E136&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
         <v>0</v>
       </c>
       <c r="K136" s="66">
-        <f>IF($F136 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E136&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
+        <f>IF($F136 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E136&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
         <v>0</v>
       </c>
     </row>
@@ -10600,7 +10660,7 @@
         <v>453</v>
       </c>
       <c r="C137" s="30" t="s">
-        <v>529</v>
+        <v>518</v>
       </c>
       <c r="D137" t="s">
         <v>115</v>
@@ -10618,19 +10678,19 @@
         <v>191</v>
       </c>
       <c r="H137" s="66">
-        <f>IF($F137 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E137&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
+        <f>IF($F137 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E137&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
         <v>0</v>
       </c>
       <c r="I137" s="66">
-        <f>IF($F137 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E137&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
+        <f>IF($F137 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E137&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
         <v>0</v>
       </c>
       <c r="J137" s="66">
-        <f>IF($F137 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E137&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
+        <f>IF($F137 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E137&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
         <v>0</v>
       </c>
       <c r="K137" s="66">
-        <f>IF($F137 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E137&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
+        <f>IF($F137 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E137&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
         <v>0</v>
       </c>
     </row>
@@ -10642,7 +10702,7 @@
         <v>455</v>
       </c>
       <c r="C138" s="30" t="s">
-        <v>529</v>
+        <v>518</v>
       </c>
       <c r="D138" t="s">
         <v>128</v>
@@ -10660,19 +10720,19 @@
         <v>0</v>
       </c>
       <c r="H138" s="66">
-        <f>IF($F138 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E138&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
+        <f>IF($F138 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E138&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
         <v>0</v>
       </c>
       <c r="I138" s="66">
-        <f>IF($F138 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E138&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
+        <f>IF($F138 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E138&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
         <v>0</v>
       </c>
       <c r="J138" s="66">
-        <f>IF($F138 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E138&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
+        <f>IF($F138 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E138&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
         <v>0</v>
       </c>
       <c r="K138" s="66">
-        <f>IF($F138 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E138&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
+        <f>IF($F138 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E138&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
         <v>0</v>
       </c>
     </row>
@@ -10684,7 +10744,7 @@
         <v>453</v>
       </c>
       <c r="C139" s="30" t="s">
-        <v>529</v>
+        <v>518</v>
       </c>
       <c r="D139" t="s">
         <v>128</v>
@@ -10702,19 +10762,19 @@
         <v>0</v>
       </c>
       <c r="H139" s="66">
-        <f>IF($F139 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E139&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
+        <f>IF($F139 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E139&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
         <v>0</v>
       </c>
       <c r="I139" s="66">
-        <f>IF($F139 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E139&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
+        <f>IF($F139 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E139&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
         <v>0</v>
       </c>
       <c r="J139" s="66">
-        <f>IF($F139 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E139&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
+        <f>IF($F139 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E139&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
         <v>0</v>
       </c>
       <c r="K139" s="66">
-        <f>IF($F139 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E139&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
+        <f>IF($F139 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E139&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
         <v>0</v>
       </c>
     </row>
@@ -10726,7 +10786,7 @@
         <v>455</v>
       </c>
       <c r="C140" s="30" t="s">
-        <v>529</v>
+        <v>518</v>
       </c>
       <c r="D140" t="s">
         <v>156</v>
@@ -10743,21 +10803,21 @@
         <f>IFERROR(INDEX(raw!$J$2:$K$86,MATCH(data!D140,raw!$B$2:$B$100,0),MATCH(data!B140,raw!$J$1:$K$1,0)), "NA")</f>
         <v>400</v>
       </c>
-      <c r="H140" s="66" t="str">
-        <f>IF($F140 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E140&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
-        <v>NA</v>
-      </c>
-      <c r="I140" s="66" t="str">
-        <f>IF($F140 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E140&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
-        <v>NA</v>
-      </c>
-      <c r="J140" s="66" t="str">
-        <f>IF($F140 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E140&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
-        <v>NA</v>
-      </c>
-      <c r="K140" s="66" t="str">
-        <f>IF($F140 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E140&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
-        <v>NA</v>
+      <c r="H140" s="66">
+        <f>IF($F140 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E140&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
+        <v>71.72</v>
+      </c>
+      <c r="I140" s="66">
+        <f>IF($F140 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E140&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
+        <v>20.49</v>
+      </c>
+      <c r="J140" s="66">
+        <f>IF($F140 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E140&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
+        <v>202.43</v>
+      </c>
+      <c r="K140" s="66">
+        <f>IF($F140 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E140&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
+        <v>0</v>
       </c>
     </row>
     <row r="141" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -10768,7 +10828,7 @@
         <v>453</v>
       </c>
       <c r="C141" s="30" t="s">
-        <v>529</v>
+        <v>518</v>
       </c>
       <c r="D141" t="s">
         <v>156</v>
@@ -10785,21 +10845,21 @@
         <f>IFERROR(INDEX(raw!$J$2:$K$86,MATCH(data!D141,raw!$B$2:$B$100,0),MATCH(data!B141,raw!$J$1:$K$1,0)), "NA")</f>
         <v>338</v>
       </c>
-      <c r="H141" s="66" t="str">
-        <f>IF($F141 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E141&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
-        <v>NA</v>
-      </c>
-      <c r="I141" s="66" t="str">
-        <f>IF($F141 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E141&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
-        <v>NA</v>
-      </c>
-      <c r="J141" s="66" t="str">
-        <f>IF($F141 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E141&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
-        <v>NA</v>
-      </c>
-      <c r="K141" s="66" t="str">
-        <f>IF($F141 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E141&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
-        <v>NA</v>
+      <c r="H141" s="66">
+        <f>IF($F141 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E141&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
+        <v>76.319999999999993</v>
+      </c>
+      <c r="I141" s="66">
+        <f>IF($F141 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E141&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
+        <v>14.86</v>
+      </c>
+      <c r="J141" s="66">
+        <f>IF($F141 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E141&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
+        <v>188.26</v>
+      </c>
+      <c r="K141" s="66">
+        <f>IF($F141 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E141&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
+        <v>0</v>
       </c>
     </row>
     <row r="142" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -10810,7 +10870,7 @@
         <v>455</v>
       </c>
       <c r="C142" s="30" t="s">
-        <v>529</v>
+        <v>518</v>
       </c>
       <c r="D142" t="s">
         <v>14</v>
@@ -10828,19 +10888,19 @@
         <v>0</v>
       </c>
       <c r="H142" s="66" t="str">
-        <f>IF($F142 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E142&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
+        <f>IF($F142 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E142&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="I142" s="66" t="str">
-        <f>IF($F142 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E142&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
+        <f>IF($F142 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E142&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="J142" s="66" t="str">
-        <f>IF($F142 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E142&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
+        <f>IF($F142 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E142&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="K142" s="66" t="str">
-        <f>IF($F142 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E142&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
+        <f>IF($F142 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E142&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
         <v>NA</v>
       </c>
     </row>
@@ -10852,7 +10912,7 @@
         <v>453</v>
       </c>
       <c r="C143" s="30" t="s">
-        <v>529</v>
+        <v>518</v>
       </c>
       <c r="D143" t="s">
         <v>14</v>
@@ -10870,19 +10930,19 @@
         <v>0</v>
       </c>
       <c r="H143" s="66" t="str">
-        <f>IF($F143 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E143&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
+        <f>IF($F143 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E143&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="I143" s="66" t="str">
-        <f>IF($F143 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E143&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
+        <f>IF($F143 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E143&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="J143" s="66" t="str">
-        <f>IF($F143 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E143&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
+        <f>IF($F143 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E143&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="K143" s="66" t="str">
-        <f>IF($F143 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E143&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
+        <f>IF($F143 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E143&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
         <v>NA</v>
       </c>
     </row>
@@ -10894,7 +10954,7 @@
         <v>455</v>
       </c>
       <c r="C144" s="30" t="s">
-        <v>529</v>
+        <v>518</v>
       </c>
       <c r="D144" t="s">
         <v>274</v>
@@ -10912,19 +10972,19 @@
         <v>NA</v>
       </c>
       <c r="H144" s="66" t="str">
-        <f>IF($F144 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E144&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
+        <f>IF($F144 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E144&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="I144" s="66" t="str">
-        <f>IF($F144 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E144&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
+        <f>IF($F144 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E144&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="J144" s="66" t="str">
-        <f>IF($F144 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E144&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
+        <f>IF($F144 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E144&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="K144" s="66" t="str">
-        <f>IF($F144 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E144&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
+        <f>IF($F144 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E144&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
         <v>NA</v>
       </c>
     </row>
@@ -10936,7 +10996,7 @@
         <v>453</v>
       </c>
       <c r="C145" s="30" t="s">
-        <v>529</v>
+        <v>518</v>
       </c>
       <c r="D145" t="s">
         <v>274</v>
@@ -10954,19 +11014,19 @@
         <v>NA</v>
       </c>
       <c r="H145" s="66" t="str">
-        <f>IF($F145 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E145&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
+        <f>IF($F145 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E145&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="I145" s="66" t="str">
-        <f>IF($F145 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E145&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
+        <f>IF($F145 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E145&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="J145" s="66" t="str">
-        <f>IF($F145 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E145&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
+        <f>IF($F145 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E145&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="K145" s="66" t="str">
-        <f>IF($F145 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E145&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
+        <f>IF($F145 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E145&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
         <v>NA</v>
       </c>
     </row>
@@ -10978,7 +11038,7 @@
         <v>455</v>
       </c>
       <c r="C146" s="30" t="s">
-        <v>529</v>
+        <v>518</v>
       </c>
       <c r="D146" t="s">
         <v>275</v>
@@ -10996,19 +11056,19 @@
         <v>NA</v>
       </c>
       <c r="H146" s="66" t="str">
-        <f>IF($F146 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E146&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
+        <f>IF($F146 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E146&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="I146" s="66" t="str">
-        <f>IF($F146 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E146&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
+        <f>IF($F146 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E146&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="J146" s="66" t="str">
-        <f>IF($F146 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E146&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
+        <f>IF($F146 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E146&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="K146" s="66" t="str">
-        <f>IF($F146 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E146&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
+        <f>IF($F146 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E146&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
         <v>NA</v>
       </c>
     </row>
@@ -11020,7 +11080,7 @@
         <v>453</v>
       </c>
       <c r="C147" s="30" t="s">
-        <v>529</v>
+        <v>518</v>
       </c>
       <c r="D147" t="s">
         <v>275</v>
@@ -11038,19 +11098,19 @@
         <v>NA</v>
       </c>
       <c r="H147" s="66" t="str">
-        <f>IF($F147 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E147&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
+        <f>IF($F147 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E147&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="I147" s="66" t="str">
-        <f>IF($F147 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E147&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
+        <f>IF($F147 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E147&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="J147" s="66" t="str">
-        <f>IF($F147 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E147&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
+        <f>IF($F147 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E147&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="K147" s="66" t="str">
-        <f>IF($F147 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E147&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
+        <f>IF($F147 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E147&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
         <v>NA</v>
       </c>
     </row>
@@ -11062,7 +11122,7 @@
         <v>455</v>
       </c>
       <c r="C148" s="30" t="s">
-        <v>529</v>
+        <v>518</v>
       </c>
       <c r="D148" t="s">
         <v>276</v>
@@ -11080,19 +11140,19 @@
         <v>NA</v>
       </c>
       <c r="H148" s="66" t="str">
-        <f>IF($F148 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E148&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
+        <f>IF($F148 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E148&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="I148" s="66" t="str">
-        <f>IF($F148 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E148&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
+        <f>IF($F148 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E148&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="J148" s="66" t="str">
-        <f>IF($F148 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E148&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
+        <f>IF($F148 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E148&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="K148" s="66" t="str">
-        <f>IF($F148 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E148&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
+        <f>IF($F148 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E148&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
         <v>NA</v>
       </c>
     </row>
@@ -11104,7 +11164,7 @@
         <v>453</v>
       </c>
       <c r="C149" s="30" t="s">
-        <v>529</v>
+        <v>518</v>
       </c>
       <c r="D149" t="s">
         <v>276</v>
@@ -11122,19 +11182,19 @@
         <v>NA</v>
       </c>
       <c r="H149" s="66" t="str">
-        <f>IF($F149 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E149&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
+        <f>IF($F149 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E149&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="I149" s="66" t="str">
-        <f>IF($F149 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E149&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
+        <f>IF($F149 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E149&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="J149" s="66" t="str">
-        <f>IF($F149 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E149&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
+        <f>IF($F149 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E149&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="K149" s="66" t="str">
-        <f>IF($F149 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E149&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
+        <f>IF($F149 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E149&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
         <v>NA</v>
       </c>
     </row>
@@ -11146,7 +11206,7 @@
         <v>455</v>
       </c>
       <c r="C150" s="30" t="s">
-        <v>529</v>
+        <v>518</v>
       </c>
       <c r="D150" t="s">
         <v>277</v>
@@ -11164,19 +11224,19 @@
         <v>NA</v>
       </c>
       <c r="H150" s="66" t="str">
-        <f>IF($F150 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E150&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
+        <f>IF($F150 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E150&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="I150" s="66" t="str">
-        <f>IF($F150 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E150&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
+        <f>IF($F150 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E150&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="J150" s="66" t="str">
-        <f>IF($F150 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E150&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
+        <f>IF($F150 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E150&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="K150" s="66" t="str">
-        <f>IF($F150 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E150&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
+        <f>IF($F150 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E150&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
         <v>NA</v>
       </c>
     </row>
@@ -11188,7 +11248,7 @@
         <v>453</v>
       </c>
       <c r="C151" s="30" t="s">
-        <v>529</v>
+        <v>518</v>
       </c>
       <c r="D151" t="s">
         <v>277</v>
@@ -11206,19 +11266,19 @@
         <v>NA</v>
       </c>
       <c r="H151" s="66" t="str">
-        <f>IF($F151 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E151&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
+        <f>IF($F151 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E151&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="I151" s="66" t="str">
-        <f>IF($F151 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E151&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
+        <f>IF($F151 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E151&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="J151" s="66" t="str">
-        <f>IF($F151 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E151&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
+        <f>IF($F151 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E151&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="K151" s="66" t="str">
-        <f>IF($F151 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E151&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
+        <f>IF($F151 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E151&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
         <v>NA</v>
       </c>
     </row>
@@ -11230,7 +11290,7 @@
         <v>455</v>
       </c>
       <c r="C152" s="30" t="s">
-        <v>529</v>
+        <v>518</v>
       </c>
       <c r="D152" t="s">
         <v>278</v>
@@ -11248,19 +11308,19 @@
         <v>NA</v>
       </c>
       <c r="H152" s="66" t="str">
-        <f>IF($F152 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E152&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
+        <f>IF($F152 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E152&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="I152" s="66" t="str">
-        <f>IF($F152 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E152&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
+        <f>IF($F152 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E152&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="J152" s="66" t="str">
-        <f>IF($F152 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E152&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
+        <f>IF($F152 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E152&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="K152" s="66" t="str">
-        <f>IF($F152 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E152&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
+        <f>IF($F152 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E152&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
         <v>NA</v>
       </c>
     </row>
@@ -11272,7 +11332,7 @@
         <v>453</v>
       </c>
       <c r="C153" s="30" t="s">
-        <v>529</v>
+        <v>518</v>
       </c>
       <c r="D153" t="s">
         <v>278</v>
@@ -11290,19 +11350,19 @@
         <v>NA</v>
       </c>
       <c r="H153" s="66" t="str">
-        <f>IF($F153 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E153&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
+        <f>IF($F153 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E153&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="I153" s="66" t="str">
-        <f>IF($F153 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E153&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
+        <f>IF($F153 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E153&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="J153" s="66" t="str">
-        <f>IF($F153 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E153&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
+        <f>IF($F153 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E153&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="K153" s="66" t="str">
-        <f>IF($F153 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E153&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
+        <f>IF($F153 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E153&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
         <v>NA</v>
       </c>
     </row>
@@ -11314,7 +11374,7 @@
         <v>455</v>
       </c>
       <c r="C154" s="30" t="s">
-        <v>529</v>
+        <v>518</v>
       </c>
       <c r="D154" t="s">
         <v>125</v>
@@ -11332,19 +11392,19 @@
         <v>0</v>
       </c>
       <c r="H154" s="66">
-        <f>IF($F154 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E154&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
+        <f>IF($F154 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E154&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
         <v>0</v>
       </c>
       <c r="I154" s="66">
-        <f>IF($F154 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E154&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
+        <f>IF($F154 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E154&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
         <v>0</v>
       </c>
       <c r="J154" s="66">
-        <f>IF($F154 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E154&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
+        <f>IF($F154 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E154&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
         <v>0</v>
       </c>
       <c r="K154" s="66">
-        <f>IF($F154 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E154&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
+        <f>IF($F154 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E154&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
         <v>0</v>
       </c>
     </row>
@@ -11356,7 +11416,7 @@
         <v>453</v>
       </c>
       <c r="C155" s="30" t="s">
-        <v>529</v>
+        <v>518</v>
       </c>
       <c r="D155" t="s">
         <v>125</v>
@@ -11374,19 +11434,19 @@
         <v>0</v>
       </c>
       <c r="H155" s="66">
-        <f>IF($F155 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E155&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
+        <f>IF($F155 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E155&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
         <v>0</v>
       </c>
       <c r="I155" s="66">
-        <f>IF($F155 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E155&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
+        <f>IF($F155 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E155&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
         <v>0</v>
       </c>
       <c r="J155" s="66">
-        <f>IF($F155 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E155&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
+        <f>IF($F155 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E155&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
         <v>0</v>
       </c>
       <c r="K155" s="66">
-        <f>IF($F155 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E155&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
+        <f>IF($F155 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E155&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
         <v>0</v>
       </c>
     </row>
@@ -11398,7 +11458,7 @@
         <v>455</v>
       </c>
       <c r="C156" s="30" t="s">
-        <v>529</v>
+        <v>518</v>
       </c>
       <c r="D156" t="s">
         <v>279</v>
@@ -11416,19 +11476,19 @@
         <v>NA</v>
       </c>
       <c r="H156" s="66" t="str">
-        <f>IF($F156 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E156&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
+        <f>IF($F156 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E156&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="I156" s="66" t="str">
-        <f>IF($F156 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E156&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
+        <f>IF($F156 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E156&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="J156" s="66" t="str">
-        <f>IF($F156 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E156&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
+        <f>IF($F156 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E156&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="K156" s="66" t="str">
-        <f>IF($F156 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E156&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
+        <f>IF($F156 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E156&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
         <v>NA</v>
       </c>
     </row>
@@ -11440,7 +11500,7 @@
         <v>453</v>
       </c>
       <c r="C157" s="30" t="s">
-        <v>529</v>
+        <v>518</v>
       </c>
       <c r="D157" t="s">
         <v>279</v>
@@ -11458,19 +11518,19 @@
         <v>NA</v>
       </c>
       <c r="H157" s="66" t="str">
-        <f>IF($F157 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E157&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
+        <f>IF($F157 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E157&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="I157" s="66" t="str">
-        <f>IF($F157 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E157&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
+        <f>IF($F157 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E157&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="J157" s="66" t="str">
-        <f>IF($F157 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E157&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
+        <f>IF($F157 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E157&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="K157" s="66" t="str">
-        <f>IF($F157 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E157&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
+        <f>IF($F157 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E157&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
         <v>NA</v>
       </c>
     </row>
@@ -11482,7 +11542,7 @@
         <v>455</v>
       </c>
       <c r="C158" s="30" t="s">
-        <v>529</v>
+        <v>518</v>
       </c>
       <c r="D158" t="s">
         <v>280</v>
@@ -11500,19 +11560,19 @@
         <v>NA</v>
       </c>
       <c r="H158" s="66" t="str">
-        <f>IF($F158 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E158&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
+        <f>IF($F158 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E158&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="I158" s="66" t="str">
-        <f>IF($F158 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E158&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
+        <f>IF($F158 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E158&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="J158" s="66" t="str">
-        <f>IF($F158 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E158&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
+        <f>IF($F158 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E158&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="K158" s="66" t="str">
-        <f>IF($F158 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E158&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
+        <f>IF($F158 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E158&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
         <v>NA</v>
       </c>
     </row>
@@ -11524,7 +11584,7 @@
         <v>453</v>
       </c>
       <c r="C159" s="30" t="s">
-        <v>529</v>
+        <v>518</v>
       </c>
       <c r="D159" t="s">
         <v>280</v>
@@ -11542,19 +11602,19 @@
         <v>NA</v>
       </c>
       <c r="H159" s="66" t="str">
-        <f>IF($F159 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E159&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
+        <f>IF($F159 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E159&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="I159" s="66" t="str">
-        <f>IF($F159 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E159&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
+        <f>IF($F159 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E159&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="J159" s="66" t="str">
-        <f>IF($F159 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E159&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
+        <f>IF($F159 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E159&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="K159" s="66" t="str">
-        <f>IF($F159 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E159&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
+        <f>IF($F159 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E159&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
         <v>NA</v>
       </c>
     </row>
@@ -11566,7 +11626,7 @@
         <v>455</v>
       </c>
       <c r="C160" s="30" t="s">
-        <v>529</v>
+        <v>518</v>
       </c>
       <c r="D160" t="s">
         <v>62</v>
@@ -11584,19 +11644,19 @@
         <v>31</v>
       </c>
       <c r="H160" s="66" t="str">
-        <f>IF($F160 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E160&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
+        <f>IF($F160 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E160&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="I160" s="66" t="str">
-        <f>IF($F160 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E160&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
+        <f>IF($F160 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E160&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="J160" s="66" t="str">
-        <f>IF($F160 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E160&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
+        <f>IF($F160 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E160&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="K160" s="66" t="str">
-        <f>IF($F160 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E160&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
+        <f>IF($F160 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E160&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
         <v>NA</v>
       </c>
     </row>
@@ -11608,7 +11668,7 @@
         <v>453</v>
       </c>
       <c r="C161" s="30" t="s">
-        <v>529</v>
+        <v>518</v>
       </c>
       <c r="D161" t="s">
         <v>62</v>
@@ -11626,19 +11686,19 @@
         <v>189</v>
       </c>
       <c r="H161" s="66" t="str">
-        <f>IF($F161 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E161&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
+        <f>IF($F161 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E161&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="I161" s="66" t="str">
-        <f>IF($F161 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E161&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
+        <f>IF($F161 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E161&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="J161" s="66" t="str">
-        <f>IF($F161 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E161&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
+        <f>IF($F161 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E161&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="K161" s="66" t="str">
-        <f>IF($F161 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E161&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
+        <f>IF($F161 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E161&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
         <v>NA</v>
       </c>
     </row>
@@ -11650,7 +11710,7 @@
         <v>455</v>
       </c>
       <c r="C162" s="30" t="s">
-        <v>529</v>
+        <v>518</v>
       </c>
       <c r="D162" t="s">
         <v>72</v>
@@ -11668,19 +11728,19 @@
         <v>2523</v>
       </c>
       <c r="H162" s="66" t="str">
-        <f>IF($F162 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E162&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
+        <f>IF($F162 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E162&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="I162" s="66" t="str">
-        <f>IF($F162 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E162&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
+        <f>IF($F162 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E162&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="J162" s="66" t="str">
-        <f>IF($F162 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E162&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
+        <f>IF($F162 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E162&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="K162" s="66" t="str">
-        <f>IF($F162 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E162&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
+        <f>IF($F162 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E162&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
         <v>NA</v>
       </c>
     </row>
@@ -11692,7 +11752,7 @@
         <v>453</v>
       </c>
       <c r="C163" s="30" t="s">
-        <v>529</v>
+        <v>518</v>
       </c>
       <c r="D163" t="s">
         <v>72</v>
@@ -11710,19 +11770,19 @@
         <v>1219</v>
       </c>
       <c r="H163" s="66" t="str">
-        <f>IF($F163 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E163&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
+        <f>IF($F163 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E163&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="I163" s="66" t="str">
-        <f>IF($F163 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E163&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
+        <f>IF($F163 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E163&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="J163" s="66" t="str">
-        <f>IF($F163 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E163&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
+        <f>IF($F163 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E163&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="K163" s="66" t="str">
-        <f>IF($F163 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E163&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
+        <f>IF($F163 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E163&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
         <v>NA</v>
       </c>
     </row>
@@ -11734,7 +11794,7 @@
         <v>455</v>
       </c>
       <c r="C164" s="30" t="s">
-        <v>529</v>
+        <v>518</v>
       </c>
       <c r="D164" t="s">
         <v>93</v>
@@ -11752,19 +11812,19 @@
         <v>2113</v>
       </c>
       <c r="H164" s="66">
-        <f>IF($F164 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E164&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
+        <f>IF($F164 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E164&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
         <v>71.209999999999994</v>
       </c>
       <c r="I164" s="66">
-        <f>IF($F164 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E164&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
+        <f>IF($F164 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E164&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
         <v>20.43</v>
       </c>
       <c r="J164" s="66">
-        <f>IF($F164 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E164&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
+        <f>IF($F164 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E164&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
         <v>218.99</v>
       </c>
       <c r="K164" s="66">
-        <f>IF($F164 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E164&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
+        <f>IF($F164 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E164&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
         <v>0.50880000000000003</v>
       </c>
     </row>
@@ -11776,7 +11836,7 @@
         <v>453</v>
       </c>
       <c r="C165" s="30" t="s">
-        <v>529</v>
+        <v>518</v>
       </c>
       <c r="D165" t="s">
         <v>93</v>
@@ -11794,19 +11854,19 @@
         <v>675</v>
       </c>
       <c r="H165" s="66">
-        <f>IF($F165 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E165&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
+        <f>IF($F165 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E165&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
         <v>77.02</v>
       </c>
       <c r="I165" s="66">
-        <f>IF($F165 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E165&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
+        <f>IF($F165 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E165&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
         <v>19.96</v>
       </c>
       <c r="J165" s="66">
-        <f>IF($F165 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E165&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
+        <f>IF($F165 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E165&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
         <v>212</v>
       </c>
       <c r="K165" s="66">
-        <f>IF($F165 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E165&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
+        <f>IF($F165 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E165&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
         <v>1.6419999999999999</v>
       </c>
     </row>
@@ -11818,7 +11878,7 @@
         <v>455</v>
       </c>
       <c r="C166" s="30" t="s">
-        <v>529</v>
+        <v>518</v>
       </c>
       <c r="D166" t="s">
         <v>105</v>
@@ -11836,19 +11896,19 @@
         <v>39</v>
       </c>
       <c r="H166" s="66" t="str">
-        <f>IF($F166 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E166&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
+        <f>IF($F166 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E166&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="I166" s="66" t="str">
-        <f>IF($F166 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E166&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
+        <f>IF($F166 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E166&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="J166" s="66" t="str">
-        <f>IF($F166 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E166&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
+        <f>IF($F166 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E166&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="K166" s="66" t="str">
-        <f>IF($F166 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E166&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
+        <f>IF($F166 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E166&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
         <v>NA</v>
       </c>
     </row>
@@ -11860,7 +11920,7 @@
         <v>453</v>
       </c>
       <c r="C167" s="30" t="s">
-        <v>529</v>
+        <v>518</v>
       </c>
       <c r="D167" t="s">
         <v>105</v>
@@ -11878,19 +11938,19 @@
         <v>161</v>
       </c>
       <c r="H167" s="66" t="str">
-        <f>IF($F167 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E167&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
+        <f>IF($F167 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E167&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="I167" s="66" t="str">
-        <f>IF($F167 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E167&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
+        <f>IF($F167 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E167&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="J167" s="66" t="str">
-        <f>IF($F167 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E167&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
+        <f>IF($F167 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E167&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="K167" s="66" t="str">
-        <f>IF($F167 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E167&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
+        <f>IF($F167 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E167&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
         <v>NA</v>
       </c>
     </row>
@@ -11902,7 +11962,7 @@
         <v>455</v>
       </c>
       <c r="C168" s="30" t="s">
-        <v>529</v>
+        <v>518</v>
       </c>
       <c r="D168" t="s">
         <v>143</v>
@@ -11920,19 +11980,19 @@
         <v>1642</v>
       </c>
       <c r="H168" s="66">
-        <f>IF($F168 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E168&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
+        <f>IF($F168 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E168&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
         <v>73.08</v>
       </c>
       <c r="I168" s="66">
-        <f>IF($F168 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E168&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
+        <f>IF($F168 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E168&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
         <v>22.02</v>
       </c>
       <c r="J168" s="66">
-        <f>IF($F168 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E168&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
+        <f>IF($F168 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E168&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
         <v>202.53</v>
       </c>
       <c r="K168" s="66">
-        <f>IF($F168 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E168&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
+        <f>IF($F168 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E168&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
         <v>0.5071</v>
       </c>
     </row>
@@ -11944,7 +12004,7 @@
         <v>453</v>
       </c>
       <c r="C169" s="30" t="s">
-        <v>529</v>
+        <v>518</v>
       </c>
       <c r="D169" t="s">
         <v>143</v>
@@ -11962,19 +12022,19 @@
         <v>1381</v>
       </c>
       <c r="H169" s="66">
-        <f>IF($F169 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E169&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
+        <f>IF($F169 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E169&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
         <v>77.510000000000005</v>
       </c>
       <c r="I169" s="66">
-        <f>IF($F169 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E169&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
+        <f>IF($F169 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E169&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
         <v>20.100000000000001</v>
       </c>
       <c r="J169" s="66">
-        <f>IF($F169 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E169&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
+        <f>IF($F169 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E169&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
         <v>211.54</v>
       </c>
       <c r="K169" s="66">
-        <f>IF($F169 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E169&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
+        <f>IF($F169 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E169&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
         <v>1.006</v>
       </c>
     </row>
@@ -11986,7 +12046,7 @@
         <v>455</v>
       </c>
       <c r="C170" s="30" t="s">
-        <v>529</v>
+        <v>518</v>
       </c>
       <c r="D170" t="s">
         <v>153</v>
@@ -12004,19 +12064,19 @@
         <v>2745</v>
       </c>
       <c r="H170" s="66">
-        <f>IF($F170 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E170&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
+        <f>IF($F170 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E170&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
         <v>76.14</v>
       </c>
       <c r="I170" s="66">
-        <f>IF($F170 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E170&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
+        <f>IF($F170 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E170&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
         <v>23.83</v>
       </c>
       <c r="J170" s="66">
-        <f>IF($F170 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E170&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
+        <f>IF($F170 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E170&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
         <v>215.17</v>
       </c>
       <c r="K170" s="66">
-        <f>IF($F170 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E170&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
+        <f>IF($F170 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E170&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
         <v>0.53690000000000004</v>
       </c>
     </row>
@@ -12028,7 +12088,7 @@
         <v>453</v>
       </c>
       <c r="C171" s="30" t="s">
-        <v>529</v>
+        <v>518</v>
       </c>
       <c r="D171" t="s">
         <v>153</v>
@@ -12046,20 +12106,20 @@
         <v>1244</v>
       </c>
       <c r="H171" s="66">
-        <f>IF($F171 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E171&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
+        <f>IF($F171 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E171&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
         <v>74.8</v>
       </c>
       <c r="I171" s="66">
-        <f>IF($F171 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E171&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
+        <f>IF($F171 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E171&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
         <v>23.22</v>
       </c>
-      <c r="J171" s="66" t="str">
-        <f>IF($F171 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E171&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
-        <v>NA</v>
-      </c>
-      <c r="K171" s="66" t="str">
-        <f>IF($F171 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E171&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
-        <v>NA</v>
+      <c r="J171" s="66">
+        <f>IF($F171 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E171&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
+        <v>209.63</v>
+      </c>
+      <c r="K171" s="66">
+        <f>IF($F171 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E171&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
+        <v>1.194</v>
       </c>
     </row>
     <row r="172" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -12070,7 +12130,7 @@
         <v>455</v>
       </c>
       <c r="C172" s="30" t="s">
-        <v>529</v>
+        <v>518</v>
       </c>
       <c r="D172" t="s">
         <v>45</v>
@@ -12088,19 +12148,19 @@
         <v>1377</v>
       </c>
       <c r="H172" s="66" t="str">
-        <f>IF($F172 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E172&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
+        <f>IF($F172 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E172&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="I172" s="66" t="str">
-        <f>IF($F172 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E172&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
+        <f>IF($F172 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E172&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="J172" s="66" t="str">
-        <f>IF($F172 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E172&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
+        <f>IF($F172 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E172&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="K172" s="66" t="str">
-        <f>IF($F172 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E172&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
+        <f>IF($F172 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E172&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
         <v>NA</v>
       </c>
     </row>
@@ -12112,7 +12172,7 @@
         <v>453</v>
       </c>
       <c r="C173" s="30" t="s">
-        <v>529</v>
+        <v>518</v>
       </c>
       <c r="D173" t="s">
         <v>45</v>
@@ -12130,19 +12190,19 @@
         <v>1864</v>
       </c>
       <c r="H173" s="66" t="str">
-        <f>IF($F173 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E173&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
+        <f>IF($F173 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E173&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="I173" s="66" t="str">
-        <f>IF($F173 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E173&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
+        <f>IF($F173 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E173&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="J173" s="66" t="str">
-        <f>IF($F173 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E173&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
+        <f>IF($F173 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E173&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="K173" s="66" t="str">
-        <f>IF($F173 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E173&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
+        <f>IF($F173 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E173&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
         <v>NA</v>
       </c>
     </row>
@@ -12154,7 +12214,7 @@
         <v>455</v>
       </c>
       <c r="C174" s="30" t="s">
-        <v>529</v>
+        <v>518</v>
       </c>
       <c r="D174" t="s">
         <v>42</v>
@@ -12172,19 +12232,19 @@
         <v>2418</v>
       </c>
       <c r="H174" s="66">
-        <f>IF($F174 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E174&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
+        <f>IF($F174 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E174&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
         <v>76.67</v>
       </c>
       <c r="I174" s="66">
-        <f>IF($F174 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E174&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
+        <f>IF($F174 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E174&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
         <v>23.6</v>
       </c>
       <c r="J174" s="66">
-        <f>IF($F174 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E174&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
+        <f>IF($F174 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E174&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
         <v>201.56</v>
       </c>
       <c r="K174" s="66">
-        <f>IF($F174 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E174&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
+        <f>IF($F174 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E174&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
         <v>1.4849000000000001</v>
       </c>
     </row>
@@ -12196,7 +12256,7 @@
         <v>453</v>
       </c>
       <c r="C175" s="30" t="s">
-        <v>529</v>
+        <v>518</v>
       </c>
       <c r="D175" t="s">
         <v>42</v>
@@ -12214,19 +12274,19 @@
         <v>1706</v>
       </c>
       <c r="H175" s="66" t="str">
-        <f>IF($F175 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E175&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
+        <f>IF($F175 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E175&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="I175" s="66" t="str">
-        <f>IF($F175 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E175&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
+        <f>IF($F175 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E175&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="J175" s="66" t="str">
-        <f>IF($F175 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E175&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
+        <f>IF($F175 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E175&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="K175" s="66" t="str">
-        <f>IF($F175 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E175&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
+        <f>IF($F175 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E175&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
         <v>NA</v>
       </c>
     </row>
@@ -12238,7 +12298,7 @@
         <v>455</v>
       </c>
       <c r="C176" s="30" t="s">
-        <v>529</v>
+        <v>518</v>
       </c>
       <c r="D176" t="s">
         <v>282</v>
@@ -12256,19 +12316,19 @@
         <v>NA</v>
       </c>
       <c r="H176" s="66" t="str">
-        <f>IF($F176 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E176&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
+        <f>IF($F176 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E176&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="I176" s="66" t="str">
-        <f>IF($F176 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E176&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
+        <f>IF($F176 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E176&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="J176" s="66" t="str">
-        <f>IF($F176 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E176&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
+        <f>IF($F176 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E176&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="K176" s="66" t="str">
-        <f>IF($F176 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E176&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
+        <f>IF($F176 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E176&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
         <v>NA</v>
       </c>
     </row>
@@ -12280,7 +12340,7 @@
         <v>453</v>
       </c>
       <c r="C177" s="30" t="s">
-        <v>529</v>
+        <v>518</v>
       </c>
       <c r="D177" t="s">
         <v>282</v>
@@ -12298,19 +12358,19 @@
         <v>NA</v>
       </c>
       <c r="H177" s="66" t="str">
-        <f>IF($F177 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E177&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
+        <f>IF($F177 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E177&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="I177" s="66" t="str">
-        <f>IF($F177 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E177&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
+        <f>IF($F177 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E177&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="J177" s="66" t="str">
-        <f>IF($F177 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E177&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
+        <f>IF($F177 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E177&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="K177" s="66" t="str">
-        <f>IF($F177 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E177&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
+        <f>IF($F177 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E177&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
         <v>NA</v>
       </c>
     </row>
@@ -12322,7 +12382,7 @@
         <v>455</v>
       </c>
       <c r="C178" s="30" t="s">
-        <v>529</v>
+        <v>518</v>
       </c>
       <c r="D178" t="s">
         <v>83</v>
@@ -12340,19 +12400,19 @@
         <v>933</v>
       </c>
       <c r="H178" s="66" t="str">
-        <f>IF($F178 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E178&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
+        <f>IF($F178 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E178&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="I178" s="66" t="str">
-        <f>IF($F178 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E178&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
+        <f>IF($F178 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E178&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="J178" s="66" t="str">
-        <f>IF($F178 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E178&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
+        <f>IF($F178 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E178&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="K178" s="66" t="str">
-        <f>IF($F178 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E178&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
+        <f>IF($F178 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E178&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
         <v>NA</v>
       </c>
     </row>
@@ -12364,7 +12424,7 @@
         <v>453</v>
       </c>
       <c r="C179" s="30" t="s">
-        <v>529</v>
+        <v>518</v>
       </c>
       <c r="D179" t="s">
         <v>83</v>
@@ -12382,19 +12442,19 @@
         <v>750</v>
       </c>
       <c r="H179" s="66" t="str">
-        <f>IF($F179 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E179&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
+        <f>IF($F179 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E179&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="I179" s="66" t="str">
-        <f>IF($F179 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E179&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
+        <f>IF($F179 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E179&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="J179" s="66" t="str">
-        <f>IF($F179 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E179&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
+        <f>IF($F179 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E179&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="K179" s="66" t="str">
-        <f>IF($F179 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E179&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
+        <f>IF($F179 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E179&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
         <v>NA</v>
       </c>
     </row>
@@ -12406,7 +12466,7 @@
         <v>455</v>
       </c>
       <c r="C180" s="30" t="s">
-        <v>529</v>
+        <v>518</v>
       </c>
       <c r="D180" t="s">
         <v>86</v>
@@ -12424,19 +12484,19 @@
         <v>85</v>
       </c>
       <c r="H180" s="66" t="str">
-        <f>IF($F180 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E180&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
+        <f>IF($F180 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E180&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="I180" s="66" t="str">
-        <f>IF($F180 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E180&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
+        <f>IF($F180 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E180&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="J180" s="66" t="str">
-        <f>IF($F180 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E180&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
+        <f>IF($F180 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E180&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="K180" s="66" t="str">
-        <f>IF($F180 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E180&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
+        <f>IF($F180 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E180&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
         <v>NA</v>
       </c>
     </row>
@@ -12448,7 +12508,7 @@
         <v>453</v>
       </c>
       <c r="C181" s="30" t="s">
-        <v>529</v>
+        <v>518</v>
       </c>
       <c r="D181" t="s">
         <v>86</v>
@@ -12466,19 +12526,19 @@
         <v>719</v>
       </c>
       <c r="H181" s="66" t="str">
-        <f>IF($F181 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E181&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
+        <f>IF($F181 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E181&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="I181" s="66" t="str">
-        <f>IF($F181 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E181&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
+        <f>IF($F181 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E181&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="J181" s="66" t="str">
-        <f>IF($F181 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E181&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
+        <f>IF($F181 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E181&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="K181" s="66" t="str">
-        <f>IF($F181 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E181&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
+        <f>IF($F181 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E181&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
         <v>NA</v>
       </c>
     </row>
@@ -12490,7 +12550,7 @@
         <v>455</v>
       </c>
       <c r="C182" s="30" t="s">
-        <v>529</v>
+        <v>518</v>
       </c>
       <c r="D182" t="s">
         <v>111</v>
@@ -12508,19 +12568,19 @@
         <v>1294</v>
       </c>
       <c r="H182" s="66">
-        <f>IF($F182 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E182&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
+        <f>IF($F182 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E182&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
         <v>71</v>
       </c>
       <c r="I182" s="66">
-        <f>IF($F182 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E182&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
+        <f>IF($F182 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E182&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
         <v>21.58</v>
       </c>
       <c r="J182" s="66">
-        <f>IF($F182 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E182&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
+        <f>IF($F182 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E182&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
         <v>211.32</v>
       </c>
       <c r="K182" s="66">
-        <f>IF($F182 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E182&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
+        <f>IF($F182 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E182&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
         <v>1.512</v>
       </c>
     </row>
@@ -12532,7 +12592,7 @@
         <v>453</v>
       </c>
       <c r="C183" s="30" t="s">
-        <v>529</v>
+        <v>518</v>
       </c>
       <c r="D183" t="s">
         <v>111</v>
@@ -12550,20 +12610,20 @@
         <v>454</v>
       </c>
       <c r="H183" s="66">
-        <f>IF($F183 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E183&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
+        <f>IF($F183 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E183&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
         <v>72.09</v>
       </c>
       <c r="I183" s="66">
-        <f>IF($F183 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E183&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
+        <f>IF($F183 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E183&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
         <v>17.09</v>
       </c>
-      <c r="J183" s="66" t="str">
-        <f>IF($F183 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E183&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
-        <v>NA</v>
-      </c>
-      <c r="K183" s="66" t="str">
-        <f>IF($F183 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E183&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
-        <v>NA</v>
+      <c r="J183" s="66">
+        <f>IF($F183 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E183&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
+        <v>214.72</v>
+      </c>
+      <c r="K183" s="66">
+        <f>IF($F183 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E183&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
+        <v>0.43509999999999999</v>
       </c>
     </row>
     <row r="184" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -12574,7 +12634,7 @@
         <v>455</v>
       </c>
       <c r="C184" s="30" t="s">
-        <v>529</v>
+        <v>518</v>
       </c>
       <c r="D184" t="s">
         <v>132</v>
@@ -12592,19 +12652,19 @@
         <v>206.02</v>
       </c>
       <c r="H184" s="66">
-        <f>IF($F184 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E184&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
+        <f>IF($F184 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E184&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
         <v>73.150000000000006</v>
       </c>
       <c r="I184" s="66">
-        <f>IF($F184 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E184&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
+        <f>IF($F184 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E184&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
         <v>19.22</v>
       </c>
       <c r="J184" s="66">
-        <f>IF($F184 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E184&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
+        <f>IF($F184 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E184&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
         <v>208.28</v>
       </c>
       <c r="K184" s="66">
-        <f>IF($F184 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E184&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
+        <f>IF($F184 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E184&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
         <v>0.76939999999999997</v>
       </c>
     </row>
@@ -12616,7 +12676,7 @@
         <v>453</v>
       </c>
       <c r="C185" s="30" t="s">
-        <v>529</v>
+        <v>518</v>
       </c>
       <c r="D185" t="s">
         <v>132</v>
@@ -12634,19 +12694,19 @@
         <v>212.4</v>
       </c>
       <c r="H185" s="66">
-        <f>IF($F185 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E185&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
+        <f>IF($F185 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E185&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
         <v>71.650000000000006</v>
       </c>
       <c r="I185" s="66">
-        <f>IF($F185 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E185&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
+        <f>IF($F185 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E185&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
         <v>17.59</v>
       </c>
       <c r="J185" s="66">
-        <f>IF($F185 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E185&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
+        <f>IF($F185 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E185&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
         <v>201.37</v>
       </c>
       <c r="K185" s="66">
-        <f>IF($F185 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E185&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
+        <f>IF($F185 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E185&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
         <v>0.62519999999999998</v>
       </c>
     </row>
@@ -12658,7 +12718,7 @@
         <v>455</v>
       </c>
       <c r="C186" s="30" t="s">
-        <v>529</v>
+        <v>518</v>
       </c>
       <c r="D186" t="s">
         <v>21</v>
@@ -12676,19 +12736,19 @@
         <v>0</v>
       </c>
       <c r="H186" s="66" t="str">
-        <f>IF($F186 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E186&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
+        <f>IF($F186 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E186&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="I186" s="66" t="str">
-        <f>IF($F186 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E186&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
+        <f>IF($F186 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E186&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="J186" s="66" t="str">
-        <f>IF($F186 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E186&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
+        <f>IF($F186 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E186&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="K186" s="66" t="str">
-        <f>IF($F186 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E186&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
+        <f>IF($F186 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E186&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
         <v>NA</v>
       </c>
     </row>
@@ -12700,7 +12760,7 @@
         <v>453</v>
       </c>
       <c r="C187" s="30" t="s">
-        <v>529</v>
+        <v>518</v>
       </c>
       <c r="D187" t="s">
         <v>21</v>
@@ -12718,19 +12778,19 @@
         <v>0</v>
       </c>
       <c r="H187" s="66" t="str">
-        <f>IF($F187 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E187&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
+        <f>IF($F187 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E187&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="I187" s="66" t="str">
-        <f>IF($F187 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E187&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
+        <f>IF($F187 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E187&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="J187" s="66" t="str">
-        <f>IF($F187 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E187&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
+        <f>IF($F187 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E187&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="K187" s="66" t="str">
-        <f>IF($F187 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E187&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
+        <f>IF($F187 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E187&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
         <v>NA</v>
       </c>
     </row>
@@ -12742,7 +12802,7 @@
         <v>455</v>
       </c>
       <c r="C188" s="30" t="s">
-        <v>529</v>
+        <v>518</v>
       </c>
       <c r="D188" t="s">
         <v>50</v>
@@ -12760,19 +12820,19 @@
         <v>3628</v>
       </c>
       <c r="H188" s="66" t="str">
-        <f>IF($F188 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E188&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
+        <f>IF($F188 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E188&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="I188" s="66" t="str">
-        <f>IF($F188 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E188&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
+        <f>IF($F188 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E188&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="J188" s="66" t="str">
-        <f>IF($F188 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E188&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
+        <f>IF($F188 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E188&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="K188" s="66" t="str">
-        <f>IF($F188 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E188&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
+        <f>IF($F188 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E188&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
         <v>NA</v>
       </c>
     </row>
@@ -12784,7 +12844,7 @@
         <v>453</v>
       </c>
       <c r="C189" s="30" t="s">
-        <v>529</v>
+        <v>518</v>
       </c>
       <c r="D189" t="s">
         <v>50</v>
@@ -12802,19 +12862,19 @@
         <v>977</v>
       </c>
       <c r="H189" s="66" t="str">
-        <f>IF($F189 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E189&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
+        <f>IF($F189 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E189&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="I189" s="66" t="str">
-        <f>IF($F189 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E189&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
+        <f>IF($F189 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E189&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="J189" s="66" t="str">
-        <f>IF($F189 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E189&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
+        <f>IF($F189 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E189&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="K189" s="66" t="str">
-        <f>IF($F189 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E189&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
+        <f>IF($F189 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E189&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
         <v>NA</v>
       </c>
     </row>
@@ -12826,7 +12886,7 @@
         <v>455</v>
       </c>
       <c r="C190" s="30" t="s">
-        <v>529</v>
+        <v>518</v>
       </c>
       <c r="D190" t="s">
         <v>53</v>
@@ -12844,19 +12904,19 @@
         <v>0</v>
       </c>
       <c r="H190" s="66">
-        <f>IF($F190 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E190&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
+        <f>IF($F190 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E190&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
         <v>0</v>
       </c>
       <c r="I190" s="66">
-        <f>IF($F190 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E190&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
+        <f>IF($F190 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E190&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
         <v>0</v>
       </c>
       <c r="J190" s="66">
-        <f>IF($F190 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E190&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
+        <f>IF($F190 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E190&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
         <v>0</v>
       </c>
       <c r="K190" s="66">
-        <f>IF($F190 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E190&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
+        <f>IF($F190 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E190&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
         <v>0</v>
       </c>
     </row>
@@ -12868,7 +12928,7 @@
         <v>453</v>
       </c>
       <c r="C191" s="30" t="s">
-        <v>529</v>
+        <v>518</v>
       </c>
       <c r="D191" t="s">
         <v>53</v>
@@ -12886,19 +12946,19 @@
         <v>0</v>
       </c>
       <c r="H191" s="66">
-        <f>IF($F191 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E191&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
+        <f>IF($F191 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E191&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
         <v>0</v>
       </c>
       <c r="I191" s="66">
-        <f>IF($F191 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E191&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
+        <f>IF($F191 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E191&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
         <v>0</v>
       </c>
       <c r="J191" s="66">
-        <f>IF($F191 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E191&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
+        <f>IF($F191 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E191&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
         <v>0</v>
       </c>
       <c r="K191" s="66">
-        <f>IF($F191 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E191&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
+        <f>IF($F191 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E191&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
         <v>0</v>
       </c>
     </row>
@@ -12910,7 +12970,7 @@
         <v>455</v>
       </c>
       <c r="C192" s="30" t="s">
-        <v>529</v>
+        <v>518</v>
       </c>
       <c r="D192" t="s">
         <v>284</v>
@@ -12928,19 +12988,19 @@
         <v>NA</v>
       </c>
       <c r="H192" s="66" t="str">
-        <f>IF($F192 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E192&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
+        <f>IF($F192 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E192&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="I192" s="66" t="str">
-        <f>IF($F192 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E192&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
+        <f>IF($F192 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E192&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="J192" s="66" t="str">
-        <f>IF($F192 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E192&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
+        <f>IF($F192 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E192&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="K192" s="66" t="str">
-        <f>IF($F192 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E192&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
+        <f>IF($F192 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E192&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
         <v>NA</v>
       </c>
     </row>
@@ -12952,7 +13012,7 @@
         <v>453</v>
       </c>
       <c r="C193" s="30" t="s">
-        <v>529</v>
+        <v>518</v>
       </c>
       <c r="D193" t="s">
         <v>284</v>
@@ -12970,19 +13030,19 @@
         <v>NA</v>
       </c>
       <c r="H193" s="66" t="str">
-        <f>IF($F193 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E193&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
+        <f>IF($F193 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E193&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="I193" s="66" t="str">
-        <f>IF($F193 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E193&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
+        <f>IF($F193 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E193&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="J193" s="66" t="str">
-        <f>IF($F193 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E193&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
+        <f>IF($F193 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E193&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="K193" s="66" t="str">
-        <f>IF($F193 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E193&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
+        <f>IF($F193 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E193&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
         <v>NA</v>
       </c>
     </row>
@@ -12994,7 +13054,7 @@
         <v>455</v>
       </c>
       <c r="C194" s="30" t="s">
-        <v>529</v>
+        <v>518</v>
       </c>
       <c r="D194" t="s">
         <v>119</v>
@@ -13012,19 +13072,19 @@
         <v>0</v>
       </c>
       <c r="H194" s="66">
-        <f>IF($F194 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E194&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
+        <f>IF($F194 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E194&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
         <v>0</v>
       </c>
       <c r="I194" s="66">
-        <f>IF($F194 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E194&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
+        <f>IF($F194 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E194&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
         <v>0</v>
       </c>
       <c r="J194" s="66">
-        <f>IF($F194 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E194&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
+        <f>IF($F194 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E194&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
         <v>0</v>
       </c>
       <c r="K194" s="66">
-        <f>IF($F194 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E194&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
+        <f>IF($F194 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E194&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
         <v>0</v>
       </c>
     </row>
@@ -13036,7 +13096,7 @@
         <v>453</v>
       </c>
       <c r="C195" s="30" t="s">
-        <v>529</v>
+        <v>518</v>
       </c>
       <c r="D195" t="s">
         <v>119</v>
@@ -13054,19 +13114,19 @@
         <v>0</v>
       </c>
       <c r="H195" s="66">
-        <f>IF($F195 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E195&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
+        <f>IF($F195 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E195&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
         <v>0</v>
       </c>
       <c r="I195" s="66">
-        <f>IF($F195 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E195&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
+        <f>IF($F195 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E195&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
         <v>0</v>
       </c>
       <c r="J195" s="66">
-        <f>IF($F195 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E195&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
+        <f>IF($F195 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E195&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
         <v>0</v>
       </c>
       <c r="K195" s="66">
-        <f>IF($F195 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E195&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
+        <f>IF($F195 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E195&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
         <v>0</v>
       </c>
     </row>
@@ -13078,7 +13138,7 @@
         <v>455</v>
       </c>
       <c r="C196" s="30" t="s">
-        <v>529</v>
+        <v>518</v>
       </c>
       <c r="D196" t="s">
         <v>122</v>
@@ -13096,19 +13156,19 @@
         <v>0</v>
       </c>
       <c r="H196" s="66">
-        <f>IF($F196 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E196&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
+        <f>IF($F196 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E196&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
         <v>0</v>
       </c>
       <c r="I196" s="66">
-        <f>IF($F196 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E196&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
+        <f>IF($F196 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E196&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
         <v>0</v>
       </c>
       <c r="J196" s="66">
-        <f>IF($F196 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E196&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
+        <f>IF($F196 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E196&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
         <v>0</v>
       </c>
       <c r="K196" s="66">
-        <f>IF($F196 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E196&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
+        <f>IF($F196 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E196&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
         <v>0</v>
       </c>
     </row>
@@ -13120,7 +13180,7 @@
         <v>453</v>
       </c>
       <c r="C197" s="30" t="s">
-        <v>529</v>
+        <v>518</v>
       </c>
       <c r="D197" t="s">
         <v>122</v>
@@ -13138,19 +13198,19 @@
         <v>0</v>
       </c>
       <c r="H197" s="66">
-        <f>IF($F197 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E197&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
+        <f>IF($F197 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E197&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
         <v>0</v>
       </c>
       <c r="I197" s="66">
-        <f>IF($F197 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E197&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
+        <f>IF($F197 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E197&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
         <v>0</v>
       </c>
       <c r="J197" s="66">
-        <f>IF($F197 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E197&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
+        <f>IF($F197 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E197&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
         <v>0</v>
       </c>
       <c r="K197" s="66">
-        <f>IF($F197 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E197&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
+        <f>IF($F197 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E197&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
         <v>0</v>
       </c>
     </row>
@@ -13162,7 +13222,7 @@
         <v>455</v>
       </c>
       <c r="C198" s="30" t="s">
-        <v>529</v>
+        <v>518</v>
       </c>
       <c r="D198" t="s">
         <v>285</v>
@@ -13180,19 +13240,19 @@
         <v>NA</v>
       </c>
       <c r="H198" s="66" t="str">
-        <f>IF($F198 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E198&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
+        <f>IF($F198 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E198&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="I198" s="66" t="str">
-        <f>IF($F198 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E198&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
+        <f>IF($F198 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E198&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="J198" s="66" t="str">
-        <f>IF($F198 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E198&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
+        <f>IF($F198 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E198&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="K198" s="66" t="str">
-        <f>IF($F198 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E198&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
+        <f>IF($F198 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E198&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
         <v>NA</v>
       </c>
     </row>
@@ -13204,7 +13264,7 @@
         <v>453</v>
       </c>
       <c r="C199" s="30" t="s">
-        <v>529</v>
+        <v>518</v>
       </c>
       <c r="D199" t="s">
         <v>285</v>
@@ -13222,19 +13282,19 @@
         <v>NA</v>
       </c>
       <c r="H199" s="66" t="str">
-        <f>IF($F199 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E199&amp;"*",carbon!$A$14:$A$70,0),2), "NA"))</f>
+        <f>IF($F199 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E199&amp;"*",carbon!$A$14:$A$93,0),2), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="I199" s="66" t="str">
-        <f>IF($F199 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E199&amp;"*",carbon!$A$14:$A$70,0),4), "NA"))</f>
+        <f>IF($F199 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E199&amp;"*",carbon!$A$14:$A$93,0),4), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="J199" s="66" t="str">
-        <f>IF($F199 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E199&amp;"*",carbon!$A$14:$A$70,0),6), "NA"))</f>
+        <f>IF($F199 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E199&amp;"*",carbon!$A$14:$A$93,0),6), "NA"))</f>
         <v>NA</v>
       </c>
       <c r="K199" s="66" t="str">
-        <f>IF($F199 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$70,MATCH("*"&amp;$E199&amp;"*",carbon!$A$14:$A$70,0),8), "NA"))</f>
+        <f>IF($F199 = "bare", 0, IFERROR(INDEX(carbon!$A$14:$J$93,MATCH("*"&amp;$E199&amp;"*",carbon!$A$14:$A$93,0),8), "NA"))</f>
         <v>NA</v>
       </c>
     </row>
@@ -13550,7 +13610,7 @@
       </c>
       <c r="J7" s="2">
         <f>VLOOKUP($F7,'seagrass biomass'!$G:$L,2,FALSE)</f>
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="K7" s="2">
         <f>VLOOKUP($F7,'seagrass biomass'!$G:$L,3,FALSE)</f>
@@ -16583,7 +16643,7 @@
       </c>
       <c r="J78" s="2">
         <f>VLOOKUP($F78,'seagrass biomass'!$G:$L,2,FALSE)</f>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="K78" s="2">
         <f>VLOOKUP($F78,'seagrass biomass'!$G:$L,3,FALSE)</f>
@@ -17102,7 +17162,7 @@
         <v>40.673422172042883</v>
       </c>
       <c r="I95" s="2" t="s">
-        <v>530</v>
+        <v>519</v>
       </c>
       <c r="O95" s="1" t="s">
         <v>283</v>
@@ -17450,14 +17510,14 @@
         <v>2025006</v>
       </c>
       <c r="H6" s="63">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="I6" s="63">
         <v>0</v>
       </c>
       <c r="J6" s="63"/>
       <c r="K6" s="63">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="O6" s="21" t="s">
         <v>309</v>
@@ -17679,7 +17739,7 @@
       </c>
       <c r="E12" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="G12" s="5">
         <v>2025012</v>
@@ -18930,7 +18990,7 @@
         <v>380</v>
       </c>
       <c r="P45" s="55">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="46" spans="1:16" x14ac:dyDescent="0.25">
@@ -19651,14 +19711,14 @@
         <v>2025134</v>
       </c>
       <c r="H65" s="63">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="I65" s="63">
         <v>0</v>
       </c>
       <c r="J65" s="63"/>
       <c r="K65" s="63">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O65" s="22" t="s">
         <v>414</v>
@@ -20678,14 +20738,14 @@
         <v>302</v>
       </c>
       <c r="H93" s="63">
-        <v>1171.2564044943822</v>
+        <v>1171.5822471910112</v>
       </c>
       <c r="I93" s="63">
         <v>739.57191011235943</v>
       </c>
       <c r="J93" s="63"/>
       <c r="K93" s="63">
-        <v>955.41415730337076</v>
+        <v>955.57707865168538</v>
       </c>
       <c r="O93" s="24" t="s">
         <v>399</v>
@@ -21311,7 +21371,7 @@
         <v>320</v>
       </c>
       <c r="P119" s="56">
-        <v>0</v>
+        <v>17</v>
       </c>
     </row>
     <row r="120" spans="1:16" x14ac:dyDescent="0.25">
@@ -22106,7 +22166,7 @@
       </c>
       <c r="E154" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="155" spans="1:16" x14ac:dyDescent="0.25">
@@ -22567,7 +22627,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J71"/>
+  <dimension ref="A1:J95"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="4" width="16" style="33" customWidth="1"/>
@@ -22739,7 +22799,7 @@
     </row>
     <row r="14" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="44" t="s">
-        <v>475</v>
+        <v>545</v>
       </c>
       <c r="B14" s="45">
         <v>78.55</v>
@@ -22774,7 +22834,7 @@
     </row>
     <row r="15" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="44" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B15" s="45">
         <v>79.540000000000006</v>
@@ -22809,7 +22869,7 @@
     </row>
     <row r="16" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="44" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B16" s="45">
         <v>76</v>
@@ -22844,7 +22904,7 @@
     </row>
     <row r="17" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="44" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B17" s="45">
         <v>78.48</v>
@@ -22879,7 +22939,7 @@
     </row>
     <row r="18" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="44" t="s">
-        <v>479</v>
+        <v>546</v>
       </c>
       <c r="B18" s="45">
         <v>73.34</v>
@@ -22914,7 +22974,7 @@
     </row>
     <row r="19" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="44" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="B19" s="45">
         <v>71.319999999999993</v>
@@ -22961,7 +23021,7 @@
     </row>
     <row r="21" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="44" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="B21" s="45">
         <v>77.400000000000006</v>
@@ -22996,7 +23056,7 @@
     </row>
     <row r="22" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="44" t="s">
-        <v>482</v>
+        <v>547</v>
       </c>
       <c r="B22" s="45">
         <v>78.98</v>
@@ -23031,7 +23091,7 @@
     </row>
     <row r="23" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="44" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="B23" s="45">
         <v>70.209999999999994</v>
@@ -23066,7 +23126,7 @@
     </row>
     <row r="24" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="44" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="B24" s="45">
         <v>75.290000000000006</v>
@@ -23101,7 +23161,7 @@
     </row>
     <row r="25" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="44" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="B25" s="45">
         <v>72.7</v>
@@ -23136,7 +23196,7 @@
     </row>
     <row r="26" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="44" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="B26" s="45">
         <v>71.37</v>
@@ -23183,7 +23243,7 @@
     </row>
     <row r="28" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="44" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="B28" s="45">
         <v>78.52</v>
@@ -23218,7 +23278,7 @@
     </row>
     <row r="29" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="44" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="B29" s="45">
         <v>71.180000000000007</v>
@@ -23253,7 +23313,7 @@
     </row>
     <row r="30" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="44" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="B30" s="45">
         <v>74.400000000000006</v>
@@ -23288,7 +23348,7 @@
     </row>
     <row r="31" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="44" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="B31" s="45">
         <v>72.2</v>
@@ -23323,7 +23383,7 @@
     </row>
     <row r="32" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="44" t="s">
-        <v>491</v>
+        <v>548</v>
       </c>
       <c r="B32" s="45">
         <v>70.680000000000007</v>
@@ -23358,7 +23418,7 @@
     </row>
     <row r="33" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="44" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B33" s="45">
         <v>71.760000000000005</v>
@@ -23405,7 +23465,7 @@
     </row>
     <row r="35" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="44" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="B35" s="45">
         <v>70.52</v>
@@ -23440,7 +23500,7 @@
     </row>
     <row r="36" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="44" t="s">
-        <v>494</v>
+        <v>490</v>
       </c>
       <c r="B36" s="45">
         <v>78.010000000000005</v>
@@ -23475,7 +23535,7 @@
     </row>
     <row r="37" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="44" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="B37" s="45">
         <v>76.260000000000005</v>
@@ -23510,7 +23570,7 @@
     </row>
     <row r="38" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="44" t="s">
-        <v>496</v>
+        <v>549</v>
       </c>
       <c r="B38" s="45">
         <v>77.64</v>
@@ -23545,7 +23605,7 @@
     </row>
     <row r="39" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="44" t="s">
-        <v>497</v>
+        <v>550</v>
       </c>
       <c r="B39" s="45">
         <v>72.239999999999995</v>
@@ -23580,7 +23640,7 @@
     </row>
     <row r="40" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="44" t="s">
-        <v>498</v>
+        <v>551</v>
       </c>
       <c r="B40" s="45">
         <v>70.900000000000006</v>
@@ -23627,7 +23687,7 @@
     </row>
     <row r="42" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="44" t="s">
-        <v>499</v>
+        <v>492</v>
       </c>
       <c r="B42" s="45">
         <v>72.83</v>
@@ -23662,7 +23722,7 @@
     </row>
     <row r="43" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="44" t="s">
-        <v>500</v>
+        <v>552</v>
       </c>
       <c r="B43" s="45">
         <v>70.86</v>
@@ -23697,7 +23757,7 @@
     </row>
     <row r="44" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="44" t="s">
-        <v>501</v>
+        <v>493</v>
       </c>
       <c r="B44" s="45">
         <v>71.849999999999994</v>
@@ -23732,7 +23792,7 @@
     </row>
     <row r="45" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="44" t="s">
-        <v>502</v>
+        <v>494</v>
       </c>
       <c r="B45" s="45">
         <v>70.849999999999994</v>
@@ -23767,7 +23827,7 @@
     </row>
     <row r="46" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="44" t="s">
-        <v>503</v>
+        <v>495</v>
       </c>
       <c r="B46" s="45">
         <v>73.849999999999994</v>
@@ -23802,7 +23862,7 @@
     </row>
     <row r="47" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="44" t="s">
-        <v>504</v>
+        <v>496</v>
       </c>
       <c r="B47" s="45">
         <v>74.42</v>
@@ -23849,7 +23909,7 @@
     </row>
     <row r="49" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="44" t="s">
-        <v>505</v>
+        <v>553</v>
       </c>
       <c r="B49" s="45">
         <v>72.86</v>
@@ -23861,7 +23921,7 @@
         <v>30.09</v>
       </c>
       <c r="E49" s="48">
-        <f t="shared" ref="E49:E70" si="15">(D49*1000/B49)*C49</f>
+        <f t="shared" ref="E49:E92" si="15">(D49*1000/B49)*C49</f>
         <v>412.98380455668405</v>
       </c>
       <c r="F49" s="49">
@@ -23884,7 +23944,7 @@
     </row>
     <row r="50" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="44" t="s">
-        <v>506</v>
+        <v>497</v>
       </c>
       <c r="B50" s="45">
         <v>77.36</v>
@@ -23919,7 +23979,7 @@
     </row>
     <row r="51" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="44" t="s">
-        <v>507</v>
+        <v>498</v>
       </c>
       <c r="B51" s="45">
         <v>72.73</v>
@@ -23954,7 +24014,7 @@
     </row>
     <row r="52" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="44" t="s">
-        <v>508</v>
+        <v>499</v>
       </c>
       <c r="B52" s="45">
         <v>71.72</v>
@@ -23989,7 +24049,7 @@
     </row>
     <row r="53" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="44" t="s">
-        <v>509</v>
+        <v>500</v>
       </c>
       <c r="B53" s="45">
         <v>74.63</v>
@@ -24024,7 +24084,7 @@
     </row>
     <row r="54" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="44" t="s">
-        <v>510</v>
+        <v>501</v>
       </c>
       <c r="B54" s="45">
         <v>70.69</v>
@@ -24071,7 +24131,7 @@
     </row>
     <row r="56" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="44" t="s">
-        <v>511</v>
+        <v>502</v>
       </c>
       <c r="B56" s="45">
         <v>74.73</v>
@@ -24106,7 +24166,7 @@
     </row>
     <row r="57" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="44" t="s">
-        <v>512</v>
+        <v>503</v>
       </c>
       <c r="B57" s="45">
         <v>73.150000000000006</v>
@@ -24141,7 +24201,7 @@
     </row>
     <row r="58" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="44" t="s">
-        <v>513</v>
+        <v>504</v>
       </c>
       <c r="B58" s="45">
         <v>71.209999999999994</v>
@@ -24176,7 +24236,7 @@
     </row>
     <row r="59" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="44" t="s">
-        <v>514</v>
+        <v>505</v>
       </c>
       <c r="B59" s="45">
         <v>73.08</v>
@@ -24211,7 +24271,7 @@
     </row>
     <row r="60" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="44" t="s">
-        <v>515</v>
+        <v>506</v>
       </c>
       <c r="B60" s="45">
         <v>76.14</v>
@@ -24246,7 +24306,7 @@
     </row>
     <row r="61" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="44" t="s">
-        <v>516</v>
+        <v>554</v>
       </c>
       <c r="B61" s="45">
         <v>76.67</v>
@@ -24281,7 +24341,7 @@
     </row>
     <row r="62" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="44" t="s">
-        <v>517</v>
+        <v>507</v>
       </c>
       <c r="B62" s="45">
         <v>71</v>
@@ -24328,7 +24388,7 @@
     </row>
     <row r="64" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="44" t="s">
-        <v>518</v>
+        <v>508</v>
       </c>
       <c r="B64" s="45">
         <v>71.97</v>
@@ -24363,7 +24423,7 @@
     </row>
     <row r="65" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="44" t="s">
-        <v>519</v>
+        <v>509</v>
       </c>
       <c r="B65" s="45">
         <v>71.650000000000006</v>
@@ -24398,7 +24458,7 @@
     </row>
     <row r="66" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="44" t="s">
-        <v>520</v>
+        <v>510</v>
       </c>
       <c r="B66" s="45">
         <v>77.02</v>
@@ -24433,7 +24493,7 @@
     </row>
     <row r="67" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="44" t="s">
-        <v>521</v>
+        <v>511</v>
       </c>
       <c r="B67" s="45">
         <v>77.510000000000005</v>
@@ -24468,7 +24528,7 @@
     </row>
     <row r="68" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="44" t="s">
-        <v>522</v>
+        <v>555</v>
       </c>
       <c r="B68" s="45">
         <v>74.8</v>
@@ -24483,27 +24543,27 @@
         <f t="shared" si="15"/>
         <v>310.42780748663102</v>
       </c>
-      <c r="F68" s="49" t="s">
-        <v>530</v>
+      <c r="F68" s="49">
+        <v>209.63</v>
       </c>
       <c r="G68" s="46">
         <v>1</v>
       </c>
-      <c r="H68" s="50" t="s">
-        <v>530</v>
-      </c>
-      <c r="I68" s="51" t="e">
+      <c r="H68" s="50">
+        <v>1.194</v>
+      </c>
+      <c r="I68" s="51">
         <f t="shared" si="20"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="J68" s="48" t="e">
+        <v>5.6957496541525545</v>
+      </c>
+      <c r="J68" s="48">
         <f t="shared" si="21"/>
-        <v>#VALUE!</v>
+        <v>304.73205783247846</v>
       </c>
     </row>
     <row r="69" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="44" t="s">
-        <v>523</v>
+        <v>512</v>
       </c>
       <c r="B69" s="45">
         <v>75.38</v>
@@ -24518,27 +24578,27 @@
         <f t="shared" si="15"/>
         <v>275.93526134253119</v>
       </c>
-      <c r="F69" s="49" t="s">
-        <v>530</v>
+      <c r="F69" s="49">
+        <v>208.89</v>
       </c>
       <c r="G69" s="46">
         <v>1</v>
       </c>
-      <c r="H69" s="50" t="s">
-        <v>530</v>
-      </c>
-      <c r="I69" s="51" t="e">
+      <c r="H69" s="50">
+        <v>1.024</v>
+      </c>
+      <c r="I69" s="51">
         <f t="shared" si="20"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="J69" s="48" t="e">
+        <v>4.9021015845660401</v>
+      </c>
+      <c r="J69" s="48">
         <f t="shared" si="21"/>
-        <v>#VALUE!</v>
+        <v>271.03315975796517</v>
       </c>
     </row>
     <row r="70" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="44" t="s">
-        <v>524</v>
+        <v>513</v>
       </c>
       <c r="B70" s="45">
         <v>72.09</v>
@@ -24553,22 +24613,22 @@
         <f t="shared" si="15"/>
         <v>237.06478013594116</v>
       </c>
-      <c r="F70" s="49" t="s">
-        <v>530</v>
+      <c r="F70" s="49">
+        <v>214.72</v>
       </c>
       <c r="G70" s="46">
         <v>1</v>
       </c>
-      <c r="H70" s="50" t="s">
-        <v>530</v>
-      </c>
-      <c r="I70" s="51" t="e">
+      <c r="H70" s="50">
+        <v>0.43509999999999999</v>
+      </c>
+      <c r="I70" s="51">
         <f t="shared" si="20"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="J70" s="48" t="e">
+        <v>2.0263599105812218</v>
+      </c>
+      <c r="J70" s="48">
         <f t="shared" si="21"/>
-        <v>#VALUE!</v>
+        <v>235.03842022535994</v>
       </c>
     </row>
     <row r="71" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -24582,6 +24642,689 @@
       <c r="H71" s="50"/>
       <c r="I71" s="51"/>
       <c r="J71" s="48"/>
+    </row>
+    <row r="72" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A72" s="44" t="s">
+        <v>527</v>
+      </c>
+      <c r="B72" s="45">
+        <v>70.150000000000006</v>
+      </c>
+      <c r="C72" s="46">
+        <v>1</v>
+      </c>
+      <c r="D72" s="47">
+        <v>22.38</v>
+      </c>
+      <c r="E72" s="48">
+        <f t="shared" si="15"/>
+        <v>319.03064861012115</v>
+      </c>
+      <c r="F72" s="49">
+        <v>226.21</v>
+      </c>
+      <c r="G72" s="46">
+        <v>1</v>
+      </c>
+      <c r="H72" s="50">
+        <v>1.8839999999999999</v>
+      </c>
+      <c r="I72" s="51">
+        <f t="shared" ref="I72:I76" si="22">(H72*1000/F72)*G72</f>
+        <v>8.3285442730206434</v>
+      </c>
+      <c r="J72" s="48">
+        <f t="shared" ref="J72:J76" si="23">E72-I72</f>
+        <v>310.70210433710048</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A73" s="44" t="s">
+        <v>528</v>
+      </c>
+      <c r="B73" s="45">
+        <v>75.31</v>
+      </c>
+      <c r="C73" s="46">
+        <v>1</v>
+      </c>
+      <c r="D73" s="47">
+        <v>22.2</v>
+      </c>
+      <c r="E73" s="48">
+        <f t="shared" si="15"/>
+        <v>294.7815695126809</v>
+      </c>
+      <c r="F73" s="49">
+        <v>200.58</v>
+      </c>
+      <c r="G73" s="46">
+        <v>1</v>
+      </c>
+      <c r="H73" s="50">
+        <v>1.0369999999999999</v>
+      </c>
+      <c r="I73" s="51">
+        <f t="shared" si="22"/>
+        <v>5.1700069797586998</v>
+      </c>
+      <c r="J73" s="48">
+        <f t="shared" si="23"/>
+        <v>289.61156253292222</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A74" s="44" t="s">
+        <v>529</v>
+      </c>
+      <c r="B74" s="45">
+        <v>72.44</v>
+      </c>
+      <c r="C74" s="46">
+        <v>1</v>
+      </c>
+      <c r="D74" s="47">
+        <v>23.37</v>
+      </c>
+      <c r="E74" s="48">
+        <f t="shared" si="15"/>
+        <v>322.6118166758697</v>
+      </c>
+      <c r="F74" s="49">
+        <v>203.4</v>
+      </c>
+      <c r="G74" s="46">
+        <v>1</v>
+      </c>
+      <c r="H74" s="50">
+        <v>0.2777</v>
+      </c>
+      <c r="I74" s="51">
+        <f t="shared" si="22"/>
+        <v>1.3652900688298917</v>
+      </c>
+      <c r="J74" s="48">
+        <f t="shared" si="23"/>
+        <v>321.24652660703981</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A75" s="44" t="s">
+        <v>530</v>
+      </c>
+      <c r="B75" s="45">
+        <v>78.14</v>
+      </c>
+      <c r="C75" s="46">
+        <v>1</v>
+      </c>
+      <c r="D75" s="47">
+        <v>23.36</v>
+      </c>
+      <c r="E75" s="48">
+        <f t="shared" si="15"/>
+        <v>298.95060148451495</v>
+      </c>
+      <c r="F75" s="49">
+        <v>207.98</v>
+      </c>
+      <c r="G75" s="46">
+        <v>1</v>
+      </c>
+      <c r="H75" s="50">
+        <v>0.6583</v>
+      </c>
+      <c r="I75" s="51">
+        <f t="shared" si="22"/>
+        <v>3.1652081930954901</v>
+      </c>
+      <c r="J75" s="48">
+        <f t="shared" si="23"/>
+        <v>295.78539329141944</v>
+      </c>
+    </row>
+    <row r="76" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A76" s="44" t="s">
+        <v>531</v>
+      </c>
+      <c r="B76" s="45">
+        <v>70.52</v>
+      </c>
+      <c r="C76" s="46">
+        <v>1</v>
+      </c>
+      <c r="D76" s="47">
+        <v>20.329999999999998</v>
+      </c>
+      <c r="E76" s="48">
+        <f t="shared" si="15"/>
+        <v>288.2870107770845</v>
+      </c>
+      <c r="F76" s="49">
+        <v>219.22</v>
+      </c>
+      <c r="G76" s="46">
+        <v>1</v>
+      </c>
+      <c r="H76" s="50">
+        <v>0.94920000000000004</v>
+      </c>
+      <c r="I76" s="51">
+        <f t="shared" si="22"/>
+        <v>4.3298969072164954</v>
+      </c>
+      <c r="J76" s="48">
+        <f t="shared" si="23"/>
+        <v>283.95711386986801</v>
+      </c>
+    </row>
+    <row r="77" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A77" s="44"/>
+      <c r="B77" s="45"/>
+      <c r="C77" s="46"/>
+      <c r="D77" s="47"/>
+      <c r="E77" s="48"/>
+      <c r="F77" s="49"/>
+      <c r="G77" s="46"/>
+      <c r="H77" s="50"/>
+      <c r="I77" s="51"/>
+      <c r="J77" s="48"/>
+    </row>
+    <row r="78" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A78" s="44" t="s">
+        <v>532</v>
+      </c>
+      <c r="B78" s="45">
+        <v>70.91</v>
+      </c>
+      <c r="C78" s="46">
+        <v>1</v>
+      </c>
+      <c r="D78" s="47">
+        <v>16.93</v>
+      </c>
+      <c r="E78" s="48">
+        <f t="shared" si="15"/>
+        <v>238.75334931603442</v>
+      </c>
+      <c r="F78" s="49">
+        <v>234.58</v>
+      </c>
+      <c r="G78" s="46">
+        <v>1</v>
+      </c>
+      <c r="H78" s="50">
+        <v>0.74280000000000002</v>
+      </c>
+      <c r="I78" s="51">
+        <f t="shared" ref="I78:I82" si="24">(H78*1000/F78)*G78</f>
+        <v>3.166510358939381</v>
+      </c>
+      <c r="J78" s="48">
+        <f t="shared" ref="J78:J82" si="25">E78-I78</f>
+        <v>235.58683895709504</v>
+      </c>
+    </row>
+    <row r="79" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A79" s="44" t="s">
+        <v>533</v>
+      </c>
+      <c r="B79" s="45">
+        <v>79.260000000000005</v>
+      </c>
+      <c r="C79" s="46">
+        <v>1</v>
+      </c>
+      <c r="D79" s="47">
+        <v>21.04</v>
+      </c>
+      <c r="E79" s="48">
+        <f t="shared" si="15"/>
+        <v>265.45546303305576</v>
+      </c>
+      <c r="F79" s="49">
+        <v>202.92</v>
+      </c>
+      <c r="G79" s="46">
+        <v>1</v>
+      </c>
+      <c r="H79" s="50">
+        <v>0.46689999999999998</v>
+      </c>
+      <c r="I79" s="51">
+        <f t="shared" si="24"/>
+        <v>2.3009067612852356</v>
+      </c>
+      <c r="J79" s="48">
+        <f t="shared" si="25"/>
+        <v>263.1545562717705</v>
+      </c>
+    </row>
+    <row r="80" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A80" s="44" t="s">
+        <v>534</v>
+      </c>
+      <c r="B80" s="45">
+        <v>71.790000000000006</v>
+      </c>
+      <c r="C80" s="46">
+        <v>1</v>
+      </c>
+      <c r="D80" s="47">
+        <v>16.05</v>
+      </c>
+      <c r="E80" s="48">
+        <f t="shared" si="15"/>
+        <v>223.56874216464686</v>
+      </c>
+      <c r="F80" s="49">
+        <v>217.38</v>
+      </c>
+      <c r="G80" s="46">
+        <v>1</v>
+      </c>
+      <c r="H80" s="50">
+        <v>0.93279999999999996</v>
+      </c>
+      <c r="I80" s="51">
+        <f t="shared" si="24"/>
+        <v>4.2911031373631427</v>
+      </c>
+      <c r="J80" s="48">
+        <f t="shared" si="25"/>
+        <v>219.27763902728373</v>
+      </c>
+    </row>
+    <row r="81" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A81" s="44" t="s">
+        <v>535</v>
+      </c>
+      <c r="B81" s="45">
+        <v>77.47</v>
+      </c>
+      <c r="C81" s="46">
+        <v>1</v>
+      </c>
+      <c r="D81" s="47">
+        <v>19.59</v>
+      </c>
+      <c r="E81" s="48">
+        <f t="shared" si="15"/>
+        <v>252.87207951465084</v>
+      </c>
+      <c r="F81" s="49">
+        <v>214.68</v>
+      </c>
+      <c r="G81" s="46">
+        <v>1</v>
+      </c>
+      <c r="H81" s="50">
+        <v>0.83840000000000003</v>
+      </c>
+      <c r="I81" s="51">
+        <f t="shared" si="24"/>
+        <v>3.9053474939444759</v>
+      </c>
+      <c r="J81" s="48">
+        <f t="shared" si="25"/>
+        <v>248.96673202070636</v>
+      </c>
+    </row>
+    <row r="82" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A82" s="44" t="s">
+        <v>536</v>
+      </c>
+      <c r="B82" s="45">
+        <v>75.41</v>
+      </c>
+      <c r="C82" s="46">
+        <v>1</v>
+      </c>
+      <c r="D82" s="47">
+        <v>19.3</v>
+      </c>
+      <c r="E82" s="48">
+        <f t="shared" si="15"/>
+        <v>255.93422622994299</v>
+      </c>
+      <c r="F82" s="49">
+        <v>222.34</v>
+      </c>
+      <c r="G82" s="46">
+        <v>1</v>
+      </c>
+      <c r="H82" s="50">
+        <v>1.0329999999999999</v>
+      </c>
+      <c r="I82" s="51">
+        <f t="shared" si="24"/>
+        <v>4.6460376000719616</v>
+      </c>
+      <c r="J82" s="48">
+        <f t="shared" si="25"/>
+        <v>251.28818862987103</v>
+      </c>
+    </row>
+    <row r="83" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A83" s="44"/>
+      <c r="B83" s="45"/>
+      <c r="C83" s="46"/>
+      <c r="D83" s="47"/>
+      <c r="E83" s="48"/>
+      <c r="F83" s="49"/>
+      <c r="G83" s="46"/>
+      <c r="H83" s="50"/>
+      <c r="I83" s="51"/>
+      <c r="J83" s="48"/>
+    </row>
+    <row r="84" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A84" s="44" t="s">
+        <v>537</v>
+      </c>
+      <c r="B84" s="45">
+        <v>76.77</v>
+      </c>
+      <c r="C84" s="46">
+        <v>1</v>
+      </c>
+      <c r="D84" s="47">
+        <v>21.82</v>
+      </c>
+      <c r="E84" s="48">
+        <f t="shared" si="15"/>
+        <v>284.22560896183404</v>
+      </c>
+      <c r="F84" s="49">
+        <v>202.31</v>
+      </c>
+      <c r="G84" s="46">
+        <v>1</v>
+      </c>
+      <c r="H84" s="50">
+        <v>1.6120000000000001</v>
+      </c>
+      <c r="I84" s="51">
+        <f t="shared" ref="I84:I92" si="26">(H84*1000/F84)*G84</f>
+        <v>7.9679699471108698</v>
+      </c>
+      <c r="J84" s="48">
+        <f t="shared" ref="J84:J92" si="27">E84-I84</f>
+        <v>276.25763901472317</v>
+      </c>
+    </row>
+    <row r="85" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A85" s="44" t="s">
+        <v>538</v>
+      </c>
+      <c r="B85" s="45">
+        <v>70.739999999999995</v>
+      </c>
+      <c r="C85" s="46">
+        <v>1</v>
+      </c>
+      <c r="D85" s="47">
+        <v>19.760000000000002</v>
+      </c>
+      <c r="E85" s="48">
+        <f t="shared" si="15"/>
+        <v>279.33276788238624</v>
+      </c>
+      <c r="F85" s="49">
+        <v>203.01</v>
+      </c>
+      <c r="G85" s="46">
+        <v>1</v>
+      </c>
+      <c r="H85" s="50">
+        <v>0.40550000000000003</v>
+      </c>
+      <c r="I85" s="51">
+        <f t="shared" si="26"/>
+        <v>1.9974385498251319</v>
+      </c>
+      <c r="J85" s="48">
+        <f t="shared" si="27"/>
+        <v>277.33532933256112</v>
+      </c>
+    </row>
+    <row r="86" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A86" s="44" t="s">
+        <v>539</v>
+      </c>
+      <c r="B86" s="45">
+        <v>76.7</v>
+      </c>
+      <c r="C86" s="46">
+        <v>1</v>
+      </c>
+      <c r="D86" s="47">
+        <v>23.23</v>
+      </c>
+      <c r="E86" s="48">
+        <f t="shared" si="15"/>
+        <v>302.86831812255542</v>
+      </c>
+      <c r="F86" s="49">
+        <v>209.94</v>
+      </c>
+      <c r="G86" s="46">
+        <v>1</v>
+      </c>
+      <c r="H86" s="50">
+        <v>1.333</v>
+      </c>
+      <c r="I86" s="51">
+        <f t="shared" si="26"/>
+        <v>6.3494331713822998</v>
+      </c>
+      <c r="J86" s="48">
+        <f t="shared" si="27"/>
+        <v>296.51888495117311</v>
+      </c>
+    </row>
+    <row r="87" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A87" s="44" t="s">
+        <v>540</v>
+      </c>
+      <c r="B87" s="45">
+        <v>71.72</v>
+      </c>
+      <c r="C87" s="46">
+        <v>1</v>
+      </c>
+      <c r="D87" s="47">
+        <v>20.49</v>
+      </c>
+      <c r="E87" s="48">
+        <f t="shared" si="15"/>
+        <v>285.69436698271056</v>
+      </c>
+      <c r="F87" s="49">
+        <v>202.43</v>
+      </c>
+      <c r="G87" s="46">
+        <v>1</v>
+      </c>
+      <c r="H87" s="50">
+        <v>0</v>
+      </c>
+      <c r="I87" s="51">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="J87" s="48">
+        <f t="shared" si="27"/>
+        <v>285.69436698271056</v>
+      </c>
+    </row>
+    <row r="88" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A88" s="44"/>
+      <c r="B88" s="45"/>
+      <c r="C88" s="46"/>
+      <c r="D88" s="47"/>
+      <c r="E88" s="48"/>
+      <c r="F88" s="49"/>
+      <c r="G88" s="46"/>
+      <c r="H88" s="50"/>
+      <c r="I88" s="51"/>
+      <c r="J88" s="48"/>
+    </row>
+    <row r="89" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A89" s="44" t="s">
+        <v>541</v>
+      </c>
+      <c r="B89" s="45">
+        <v>72.19</v>
+      </c>
+      <c r="C89" s="46">
+        <v>1</v>
+      </c>
+      <c r="D89" s="47">
+        <v>16.66</v>
+      </c>
+      <c r="E89" s="48">
+        <f t="shared" si="15"/>
+        <v>230.77988641086023</v>
+      </c>
+      <c r="F89" s="49">
+        <v>201.97</v>
+      </c>
+      <c r="G89" s="46">
+        <v>1</v>
+      </c>
+      <c r="H89" s="50">
+        <v>1.1459999999999999</v>
+      </c>
+      <c r="I89" s="51">
+        <f t="shared" si="26"/>
+        <v>5.6741100163390605</v>
+      </c>
+      <c r="J89" s="48">
+        <f t="shared" si="27"/>
+        <v>225.10577639452117</v>
+      </c>
+    </row>
+    <row r="90" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A90" s="44" t="s">
+        <v>542</v>
+      </c>
+      <c r="B90" s="45">
+        <v>75.75</v>
+      </c>
+      <c r="C90" s="46">
+        <v>1</v>
+      </c>
+      <c r="D90" s="47">
+        <v>18.14</v>
+      </c>
+      <c r="E90" s="48">
+        <f t="shared" si="15"/>
+        <v>239.47194719471946</v>
+      </c>
+      <c r="F90" s="49">
+        <v>212.14</v>
+      </c>
+      <c r="G90" s="46">
+        <v>1</v>
+      </c>
+      <c r="H90" s="50">
+        <v>0.25940000000000002</v>
+      </c>
+      <c r="I90" s="51">
+        <f t="shared" si="26"/>
+        <v>1.2227774111435847</v>
+      </c>
+      <c r="J90" s="48">
+        <f t="shared" si="27"/>
+        <v>238.24916978357587</v>
+      </c>
+    </row>
+    <row r="91" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A91" s="44" t="s">
+        <v>543</v>
+      </c>
+      <c r="B91" s="45">
+        <v>70.63</v>
+      </c>
+      <c r="C91" s="46">
+        <v>1</v>
+      </c>
+      <c r="D91" s="47">
+        <v>16.899999999999999</v>
+      </c>
+      <c r="E91" s="48">
+        <f t="shared" si="15"/>
+        <v>239.27509556845536</v>
+      </c>
+      <c r="F91" s="49">
+        <v>202.3</v>
+      </c>
+      <c r="G91" s="46">
+        <v>1</v>
+      </c>
+      <c r="H91" s="50">
+        <v>0.2412</v>
+      </c>
+      <c r="I91" s="51">
+        <f t="shared" si="26"/>
+        <v>1.1922886801779533</v>
+      </c>
+      <c r="J91" s="48">
+        <f t="shared" si="27"/>
+        <v>238.08280688827739</v>
+      </c>
+    </row>
+    <row r="92" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A92" s="44" t="s">
+        <v>544</v>
+      </c>
+      <c r="B92" s="45">
+        <v>76.319999999999993</v>
+      </c>
+      <c r="C92" s="46">
+        <v>1</v>
+      </c>
+      <c r="D92" s="47">
+        <v>14.86</v>
+      </c>
+      <c r="E92" s="48">
+        <f t="shared" si="15"/>
+        <v>194.70649895178198</v>
+      </c>
+      <c r="F92" s="49">
+        <v>188.26</v>
+      </c>
+      <c r="G92" s="46">
+        <v>1</v>
+      </c>
+      <c r="H92" s="50">
+        <v>0</v>
+      </c>
+      <c r="I92" s="51">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="J92" s="48">
+        <f t="shared" si="27"/>
+        <v>194.70649895178198</v>
+      </c>
+    </row>
+    <row r="93" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A93" s="44"/>
+      <c r="B93" s="45"/>
+      <c r="C93" s="46"/>
+      <c r="D93" s="47"/>
+      <c r="E93" s="48"/>
+      <c r="F93" s="49"/>
+      <c r="G93" s="46"/>
+      <c r="H93" s="50"/>
+      <c r="I93" s="51"/>
+      <c r="J93" s="48"/>
+    </row>
+    <row r="95" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A95" s="89" t="s">
+        <v>556</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="24">

--- a/data/carbon/Aveiro2025_Biomass_C_cores.xlsx
+++ b/data/carbon/Aveiro2025_Biomass_C_cores.xlsx
@@ -16,6 +16,7 @@
     <sheet name="raw" sheetId="1" r:id="rId2"/>
     <sheet name="seagrass biomass" sheetId="2" r:id="rId3"/>
     <sheet name="carbon" sheetId="5" r:id="rId4"/>
+    <sheet name="moisture" sheetId="6" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">raw!$A$1:$O$100</definedName>
@@ -24,7 +25,7 @@
   </definedNames>
   <calcPr calcId="162913"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId5"/>
+    <pivotCache cacheId="0" r:id="rId6"/>
   </pivotCaches>
 </workbook>
 </file>
@@ -159,7 +160,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2091" uniqueCount="557">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2136" uniqueCount="569">
   <si>
     <t>type</t>
   </si>
@@ -1984,6 +1985,42 @@
   </si>
   <si>
     <t>* Samples not well homogenised</t>
+  </si>
+  <si>
+    <t>Sample</t>
+  </si>
+  <si>
+    <t>Initial weight</t>
+  </si>
+  <si>
+    <t>Container weight</t>
+  </si>
+  <si>
+    <t>Total weight with container</t>
+  </si>
+  <si>
+    <t>Total weight after 2 hours</t>
+  </si>
+  <si>
+    <t>Total weight after 3 hours</t>
+  </si>
+  <si>
+    <t>Transferred weight after 3 hours</t>
+  </si>
+  <si>
+    <t>NG_16_B</t>
+  </si>
+  <si>
+    <t>NG_27_A</t>
+  </si>
+  <si>
+    <t>RR_41_A</t>
+  </si>
+  <si>
+    <t>RR_41_B</t>
+  </si>
+  <si>
+    <t>RR_39_B</t>
   </si>
 </sst>
 </file>
@@ -2718,26 +2755,8 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="10" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="1" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="2" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="2" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="1" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="0" xfId="6" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="1" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="15" fillId="10" borderId="1" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="1" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="9" borderId="1" xfId="9" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2754,8 +2773,26 @@
     <xf numFmtId="0" fontId="20" fillId="9" borderId="4" xfId="9" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="0" xfId="6" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="1" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="15" fillId="10" borderId="1" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="1" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="1" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="1" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="2" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="2" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="16">
@@ -22638,78 +22675,78 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="77"/>
-      <c r="B1" s="77"/>
-      <c r="C1" s="77"/>
-      <c r="D1" s="78" t="s">
+      <c r="A1" s="87"/>
+      <c r="B1" s="87"/>
+      <c r="C1" s="87"/>
+      <c r="D1" s="88" t="s">
         <v>457</v>
       </c>
-      <c r="E1" s="78"/>
-      <c r="F1" s="78"/>
-      <c r="G1" s="78"/>
-      <c r="H1" s="78"/>
-      <c r="I1" s="78"/>
+      <c r="E1" s="88"/>
+      <c r="F1" s="88"/>
+      <c r="G1" s="88"/>
+      <c r="H1" s="88"/>
+      <c r="I1" s="88"/>
       <c r="J1" s="32"/>
     </row>
     <row r="2" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="77"/>
-      <c r="B2" s="77"/>
-      <c r="C2" s="77"/>
-      <c r="D2" s="78" t="s">
+      <c r="A2" s="87"/>
+      <c r="B2" s="87"/>
+      <c r="C2" s="87"/>
+      <c r="D2" s="88" t="s">
         <v>458</v>
       </c>
-      <c r="E2" s="78"/>
-      <c r="F2" s="78"/>
-      <c r="G2" s="78"/>
-      <c r="H2" s="78"/>
-      <c r="I2" s="78"/>
+      <c r="E2" s="88"/>
+      <c r="F2" s="88"/>
+      <c r="G2" s="88"/>
+      <c r="H2" s="88"/>
+      <c r="I2" s="88"/>
       <c r="J2" s="32"/>
     </row>
     <row r="3" spans="1:10" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="77"/>
-      <c r="B3" s="77"/>
-      <c r="C3" s="77"/>
-      <c r="D3" s="79" t="s">
+      <c r="A3" s="87"/>
+      <c r="B3" s="87"/>
+      <c r="C3" s="87"/>
+      <c r="D3" s="89" t="s">
         <v>459</v>
       </c>
-      <c r="E3" s="79"/>
-      <c r="F3" s="79"/>
-      <c r="G3" s="79"/>
-      <c r="H3" s="79"/>
-      <c r="I3" s="79"/>
+      <c r="E3" s="89"/>
+      <c r="F3" s="89"/>
+      <c r="G3" s="89"/>
+      <c r="H3" s="89"/>
+      <c r="I3" s="89"/>
       <c r="J3" s="32"/>
     </row>
     <row r="5" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="80" t="s">
+      <c r="A5" s="83" t="s">
         <v>460</v>
       </c>
-      <c r="B5" s="80"/>
-      <c r="C5" s="81"/>
-      <c r="D5" s="81"/>
+      <c r="B5" s="83"/>
+      <c r="C5" s="85"/>
+      <c r="D5" s="85"/>
     </row>
     <row r="6" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="80" t="s">
+      <c r="A6" s="83" t="s">
         <v>461</v>
       </c>
-      <c r="B6" s="80"/>
-      <c r="C6" s="82"/>
-      <c r="D6" s="82"/>
+      <c r="B6" s="83"/>
+      <c r="C6" s="84"/>
+      <c r="D6" s="84"/>
     </row>
     <row r="7" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="80" t="s">
+      <c r="A7" s="83" t="s">
         <v>462</v>
       </c>
-      <c r="B7" s="80"/>
-      <c r="C7" s="81"/>
-      <c r="D7" s="81"/>
+      <c r="B7" s="83"/>
+      <c r="C7" s="85"/>
+      <c r="D7" s="85"/>
     </row>
     <row r="8" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="80" t="s">
+      <c r="A8" s="83" t="s">
         <v>463</v>
       </c>
-      <c r="B8" s="80"/>
-      <c r="C8" s="83"/>
-      <c r="D8" s="83"/>
+      <c r="B8" s="83"/>
+      <c r="C8" s="86"/>
+      <c r="D8" s="86"/>
     </row>
     <row r="9" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="34"/>
@@ -22722,62 +22759,62 @@
     </row>
     <row r="10" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="35"/>
-      <c r="B10" s="85" t="s">
+      <c r="B10" s="79" t="s">
         <v>464</v>
       </c>
-      <c r="C10" s="85"/>
-      <c r="D10" s="85"/>
-      <c r="E10" s="85"/>
-      <c r="F10" s="85" t="s">
+      <c r="C10" s="79"/>
+      <c r="D10" s="79"/>
+      <c r="E10" s="79"/>
+      <c r="F10" s="79" t="s">
         <v>465</v>
       </c>
-      <c r="G10" s="85"/>
-      <c r="H10" s="85"/>
-      <c r="I10" s="85"/>
+      <c r="G10" s="79"/>
+      <c r="H10" s="79"/>
+      <c r="I10" s="79"/>
     </row>
     <row r="11" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="86" t="s">
+      <c r="A11" s="80" t="s">
         <v>466</v>
       </c>
-      <c r="B11" s="87" t="s">
+      <c r="B11" s="81" t="s">
         <v>467</v>
       </c>
-      <c r="C11" s="84" t="s">
+      <c r="C11" s="78" t="s">
         <v>468</v>
       </c>
-      <c r="D11" s="88" t="s">
+      <c r="D11" s="82" t="s">
         <v>469</v>
       </c>
-      <c r="E11" s="84" t="s">
+      <c r="E11" s="78" t="s">
         <v>470</v>
       </c>
-      <c r="F11" s="88" t="s">
+      <c r="F11" s="82" t="s">
         <v>467</v>
       </c>
-      <c r="G11" s="84" t="s">
+      <c r="G11" s="78" t="s">
         <v>468</v>
       </c>
-      <c r="H11" s="84" t="s">
+      <c r="H11" s="78" t="s">
         <v>471</v>
       </c>
-      <c r="I11" s="84" t="s">
+      <c r="I11" s="78" t="s">
         <v>472</v>
       </c>
-      <c r="J11" s="84" t="s">
+      <c r="J11" s="78" t="s">
         <v>473</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="86"/>
-      <c r="B12" s="87"/>
-      <c r="C12" s="84"/>
-      <c r="D12" s="88"/>
-      <c r="E12" s="84"/>
-      <c r="F12" s="88"/>
-      <c r="G12" s="84"/>
-      <c r="H12" s="84"/>
-      <c r="I12" s="84"/>
-      <c r="J12" s="84"/>
+      <c r="A12" s="80"/>
+      <c r="B12" s="81"/>
+      <c r="C12" s="78"/>
+      <c r="D12" s="82"/>
+      <c r="E12" s="78"/>
+      <c r="F12" s="82"/>
+      <c r="G12" s="78"/>
+      <c r="H12" s="78"/>
+      <c r="I12" s="78"/>
+      <c r="J12" s="78"/>
     </row>
     <row r="13" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="36"/>
@@ -25322,12 +25359,24 @@
       <c r="J93" s="48"/>
     </row>
     <row r="95" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A95" s="89" t="s">
+      <c r="A95" s="77" t="s">
         <v>556</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="A1:C3"/>
+    <mergeCell ref="D1:I1"/>
+    <mergeCell ref="D2:I2"/>
+    <mergeCell ref="D3:I3"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="C8:D8"/>
     <mergeCell ref="I11:I12"/>
     <mergeCell ref="J11:J12"/>
     <mergeCell ref="B10:E10"/>
@@ -25340,21 +25389,407 @@
     <mergeCell ref="F11:F12"/>
     <mergeCell ref="G11:G12"/>
     <mergeCell ref="H11:H12"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="A1:C3"/>
-    <mergeCell ref="D1:I1"/>
-    <mergeCell ref="D2:I2"/>
-    <mergeCell ref="D3:I3"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="C5:D5"/>
   </mergeCells>
   <pageMargins left="0.23611111111111099" right="0.23611111111111099" top="0.196527777777778" bottom="0.196527777777778" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="81" orientation="landscape" horizontalDpi="300" verticalDpi="300"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:I13"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="25.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="24" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="30.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>557</v>
+      </c>
+      <c r="B1" t="s">
+        <v>456</v>
+      </c>
+      <c r="C1" t="s">
+        <v>516</v>
+      </c>
+      <c r="D1" t="s">
+        <v>558</v>
+      </c>
+      <c r="E1" t="s">
+        <v>559</v>
+      </c>
+      <c r="F1" t="s">
+        <v>560</v>
+      </c>
+      <c r="G1" t="s">
+        <v>561</v>
+      </c>
+      <c r="H1" t="s">
+        <v>562</v>
+      </c>
+      <c r="I1" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>484</v>
+      </c>
+      <c r="B2" t="s">
+        <v>517</v>
+      </c>
+      <c r="C2" t="s">
+        <v>455</v>
+      </c>
+      <c r="D2">
+        <v>250.9</v>
+      </c>
+      <c r="E2">
+        <v>20932.32</v>
+      </c>
+      <c r="F2">
+        <v>21183.25</v>
+      </c>
+      <c r="G2">
+        <v>21155.09</v>
+      </c>
+      <c r="H2">
+        <v>21154.77</v>
+      </c>
+      <c r="I2">
+        <v>222.22</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>564</v>
+      </c>
+      <c r="B3" t="s">
+        <v>517</v>
+      </c>
+      <c r="C3" t="s">
+        <v>453</v>
+      </c>
+      <c r="D3">
+        <v>308.83</v>
+      </c>
+      <c r="E3">
+        <v>22464.61</v>
+      </c>
+      <c r="F3">
+        <v>22773.49</v>
+      </c>
+      <c r="G3">
+        <v>22736.61</v>
+      </c>
+      <c r="H3">
+        <v>22737.17</v>
+      </c>
+      <c r="I3">
+        <v>271.95999999999998</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>493</v>
+      </c>
+      <c r="B4" t="s">
+        <v>517</v>
+      </c>
+      <c r="C4" t="s">
+        <v>455</v>
+      </c>
+      <c r="D4">
+        <v>447.71</v>
+      </c>
+      <c r="E4">
+        <v>23501.38</v>
+      </c>
+      <c r="F4">
+        <v>23949.22</v>
+      </c>
+      <c r="G4">
+        <v>23926.59</v>
+      </c>
+      <c r="H4">
+        <v>23927.93</v>
+      </c>
+      <c r="I4">
+        <v>426.24</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>498</v>
+      </c>
+      <c r="B5" t="s">
+        <v>517</v>
+      </c>
+      <c r="C5" t="s">
+        <v>453</v>
+      </c>
+      <c r="D5">
+        <v>650.63</v>
+      </c>
+      <c r="E5">
+        <v>19958.77</v>
+      </c>
+      <c r="F5">
+        <v>20609.57</v>
+      </c>
+      <c r="G5">
+        <v>20582.150000000001</v>
+      </c>
+      <c r="H5">
+        <v>20583.78</v>
+      </c>
+      <c r="I5">
+        <v>620.85</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>565</v>
+      </c>
+      <c r="B6" t="s">
+        <v>517</v>
+      </c>
+      <c r="C6" t="s">
+        <v>455</v>
+      </c>
+      <c r="D6">
+        <v>271.85000000000002</v>
+      </c>
+      <c r="E6">
+        <v>21210.04</v>
+      </c>
+      <c r="F6">
+        <v>21481.99</v>
+      </c>
+      <c r="G6">
+        <v>21463.05</v>
+      </c>
+      <c r="H6">
+        <v>21464.27</v>
+      </c>
+      <c r="I6">
+        <v>254.28</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>481</v>
+      </c>
+      <c r="B7" t="s">
+        <v>517</v>
+      </c>
+      <c r="C7" t="s">
+        <v>453</v>
+      </c>
+      <c r="D7">
+        <v>531.37</v>
+      </c>
+      <c r="E7">
+        <v>22188.45</v>
+      </c>
+      <c r="F7">
+        <v>22719.85</v>
+      </c>
+      <c r="G7">
+        <v>22694.97</v>
+      </c>
+      <c r="H7">
+        <v>22695.82</v>
+      </c>
+      <c r="I7">
+        <v>505.98</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>538</v>
+      </c>
+      <c r="B8" t="s">
+        <v>518</v>
+      </c>
+      <c r="C8" t="s">
+        <v>455</v>
+      </c>
+      <c r="D8">
+        <v>573.27</v>
+      </c>
+      <c r="E8">
+        <v>23172.37</v>
+      </c>
+      <c r="F8">
+        <v>23747.4</v>
+      </c>
+      <c r="G8">
+        <v>23717.48</v>
+      </c>
+      <c r="H8">
+        <v>23716.77</v>
+      </c>
+      <c r="I8">
+        <v>544.83000000000004</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>566</v>
+      </c>
+      <c r="B9" t="s">
+        <v>518</v>
+      </c>
+      <c r="C9" t="s">
+        <v>453</v>
+      </c>
+      <c r="D9">
+        <v>203.64</v>
+      </c>
+      <c r="E9">
+        <v>18391.900000000001</v>
+      </c>
+      <c r="F9">
+        <v>18596.53</v>
+      </c>
+      <c r="G9">
+        <v>18584.12</v>
+      </c>
+      <c r="H9">
+        <v>18584.759999999998</v>
+      </c>
+      <c r="I9">
+        <v>193.07</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>542</v>
+      </c>
+      <c r="B10" t="s">
+        <v>518</v>
+      </c>
+      <c r="C10" t="s">
+        <v>455</v>
+      </c>
+      <c r="D10">
+        <v>428.34</v>
+      </c>
+      <c r="E10">
+        <v>22187.93</v>
+      </c>
+      <c r="F10">
+        <v>22616.78</v>
+      </c>
+      <c r="G10">
+        <v>22592.639999999999</v>
+      </c>
+      <c r="H10">
+        <v>22593.599999999999</v>
+      </c>
+      <c r="I10">
+        <v>404.99</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>567</v>
+      </c>
+      <c r="B11" t="s">
+        <v>518</v>
+      </c>
+      <c r="C11" t="s">
+        <v>453</v>
+      </c>
+      <c r="D11">
+        <v>347.65</v>
+      </c>
+      <c r="E11">
+        <v>21300.400000000001</v>
+      </c>
+      <c r="F11">
+        <v>21648.2</v>
+      </c>
+      <c r="G11">
+        <v>21629.14</v>
+      </c>
+      <c r="H11">
+        <v>21630.13</v>
+      </c>
+      <c r="I11">
+        <v>327.87</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>506</v>
+      </c>
+      <c r="B12" t="s">
+        <v>518</v>
+      </c>
+      <c r="C12" t="s">
+        <v>455</v>
+      </c>
+      <c r="D12">
+        <v>359.87</v>
+      </c>
+      <c r="E12">
+        <v>21209.53</v>
+      </c>
+      <c r="F12">
+        <v>21571.040000000001</v>
+      </c>
+      <c r="G12">
+        <v>21549.18</v>
+      </c>
+      <c r="H12">
+        <v>21552.29</v>
+      </c>
+      <c r="I12">
+        <v>340.54</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>568</v>
+      </c>
+      <c r="B13" t="s">
+        <v>518</v>
+      </c>
+      <c r="C13" t="s">
+        <v>453</v>
+      </c>
+      <c r="D13">
+        <v>468.86</v>
+      </c>
+      <c r="E13">
+        <v>22464.19</v>
+      </c>
+      <c r="F13">
+        <v>22934.09</v>
+      </c>
+      <c r="G13">
+        <v>22900.32</v>
+      </c>
+      <c r="H13">
+        <v>22903.279999999999</v>
+      </c>
+      <c r="I13">
+        <v>437.59</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>
--- a/data/carbon/Aveiro2025_Biomass_C_cores.xlsx
+++ b/data/carbon/Aveiro2025_Biomass_C_cores.xlsx
@@ -5,11 +5,11 @@
   <workbookPr codeName="ThisWorkbook" hidePivotFieldList="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\REWRITE\Field_data\Nantes_cloud\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\REWRITE\Field_data\seagrass_carbon_2025\data\carbon\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="4" r:id="rId1"/>
@@ -17,6 +17,7 @@
     <sheet name="seagrass biomass" sheetId="2" r:id="rId3"/>
     <sheet name="carbon" sheetId="5" r:id="rId4"/>
     <sheet name="moisture" sheetId="6" r:id="rId5"/>
+    <sheet name="soil" sheetId="7" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">raw!$A$1:$O$100</definedName>
@@ -25,7 +26,7 @@
   </definedNames>
   <calcPr calcId="162913"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId6"/>
+    <pivotCache cacheId="0" r:id="rId7"/>
   </pivotCaches>
 </workbook>
 </file>
@@ -160,7 +161,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2136" uniqueCount="569">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2159" uniqueCount="591">
   <si>
     <t>type</t>
   </si>
@@ -2021,6 +2022,72 @@
   </si>
   <si>
     <t>RR_39_B</t>
+  </si>
+  <si>
+    <t>Petri_dish</t>
+  </si>
+  <si>
+    <t>Init_weight_petri</t>
+  </si>
+  <si>
+    <t>Final_weight_petri</t>
+  </si>
+  <si>
+    <t>RS01</t>
+  </si>
+  <si>
+    <t>RS02</t>
+  </si>
+  <si>
+    <t>RS03</t>
+  </si>
+  <si>
+    <t>RS04</t>
+  </si>
+  <si>
+    <t>RS05</t>
+  </si>
+  <si>
+    <t>RS06</t>
+  </si>
+  <si>
+    <t>RS07</t>
+  </si>
+  <si>
+    <t>RS08</t>
+  </si>
+  <si>
+    <t>NS01</t>
+  </si>
+  <si>
+    <t>NS02</t>
+  </si>
+  <si>
+    <t>NS03</t>
+  </si>
+  <si>
+    <t>NS04</t>
+  </si>
+  <si>
+    <t>NS05</t>
+  </si>
+  <si>
+    <t>NS06</t>
+  </si>
+  <si>
+    <t>NS07</t>
+  </si>
+  <si>
+    <t>NS08</t>
+  </si>
+  <si>
+    <t>Init_weight</t>
+  </si>
+  <si>
+    <t>Final_weight</t>
+  </si>
+  <si>
+    <t>Dry_bulk_density</t>
   </si>
 </sst>
 </file>
@@ -2758,6 +2825,27 @@
     <xf numFmtId="0" fontId="15" fillId="9" borderId="0" xfId="6" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="1" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="2" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="2" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="1" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="1" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="15" fillId="10" borderId="1" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="1" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="20" fillId="9" borderId="1" xfId="9" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2771,27 +2859,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="9" borderId="4" xfId="9" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="1" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="15" fillId="10" borderId="1" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="1" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="1" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="1" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="2" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="2" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -22675,78 +22742,78 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="87"/>
-      <c r="B1" s="87"/>
-      <c r="C1" s="87"/>
-      <c r="D1" s="88" t="s">
+      <c r="A1" s="78"/>
+      <c r="B1" s="78"/>
+      <c r="C1" s="78"/>
+      <c r="D1" s="79" t="s">
         <v>457</v>
       </c>
-      <c r="E1" s="88"/>
-      <c r="F1" s="88"/>
-      <c r="G1" s="88"/>
-      <c r="H1" s="88"/>
-      <c r="I1" s="88"/>
+      <c r="E1" s="79"/>
+      <c r="F1" s="79"/>
+      <c r="G1" s="79"/>
+      <c r="H1" s="79"/>
+      <c r="I1" s="79"/>
       <c r="J1" s="32"/>
     </row>
     <row r="2" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="87"/>
-      <c r="B2" s="87"/>
-      <c r="C2" s="87"/>
-      <c r="D2" s="88" t="s">
+      <c r="A2" s="78"/>
+      <c r="B2" s="78"/>
+      <c r="C2" s="78"/>
+      <c r="D2" s="79" t="s">
         <v>458</v>
       </c>
-      <c r="E2" s="88"/>
-      <c r="F2" s="88"/>
-      <c r="G2" s="88"/>
-      <c r="H2" s="88"/>
-      <c r="I2" s="88"/>
+      <c r="E2" s="79"/>
+      <c r="F2" s="79"/>
+      <c r="G2" s="79"/>
+      <c r="H2" s="79"/>
+      <c r="I2" s="79"/>
       <c r="J2" s="32"/>
     </row>
     <row r="3" spans="1:10" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="87"/>
-      <c r="B3" s="87"/>
-      <c r="C3" s="87"/>
-      <c r="D3" s="89" t="s">
+      <c r="A3" s="78"/>
+      <c r="B3" s="78"/>
+      <c r="C3" s="78"/>
+      <c r="D3" s="80" t="s">
         <v>459</v>
       </c>
-      <c r="E3" s="89"/>
-      <c r="F3" s="89"/>
-      <c r="G3" s="89"/>
-      <c r="H3" s="89"/>
-      <c r="I3" s="89"/>
+      <c r="E3" s="80"/>
+      <c r="F3" s="80"/>
+      <c r="G3" s="80"/>
+      <c r="H3" s="80"/>
+      <c r="I3" s="80"/>
       <c r="J3" s="32"/>
     </row>
     <row r="5" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="83" t="s">
+      <c r="A5" s="81" t="s">
         <v>460</v>
       </c>
-      <c r="B5" s="83"/>
-      <c r="C5" s="85"/>
-      <c r="D5" s="85"/>
+      <c r="B5" s="81"/>
+      <c r="C5" s="82"/>
+      <c r="D5" s="82"/>
     </row>
     <row r="6" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="83" t="s">
+      <c r="A6" s="81" t="s">
         <v>461</v>
       </c>
-      <c r="B6" s="83"/>
-      <c r="C6" s="84"/>
-      <c r="D6" s="84"/>
+      <c r="B6" s="81"/>
+      <c r="C6" s="83"/>
+      <c r="D6" s="83"/>
     </row>
     <row r="7" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="83" t="s">
+      <c r="A7" s="81" t="s">
         <v>462</v>
       </c>
-      <c r="B7" s="83"/>
-      <c r="C7" s="85"/>
-      <c r="D7" s="85"/>
+      <c r="B7" s="81"/>
+      <c r="C7" s="82"/>
+      <c r="D7" s="82"/>
     </row>
     <row r="8" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="83" t="s">
+      <c r="A8" s="81" t="s">
         <v>463</v>
       </c>
-      <c r="B8" s="83"/>
-      <c r="C8" s="86"/>
-      <c r="D8" s="86"/>
+      <c r="B8" s="81"/>
+      <c r="C8" s="84"/>
+      <c r="D8" s="84"/>
     </row>
     <row r="9" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="34"/>
@@ -22759,62 +22826,62 @@
     </row>
     <row r="10" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="35"/>
-      <c r="B10" s="79" t="s">
+      <c r="B10" s="86" t="s">
         <v>464</v>
       </c>
-      <c r="C10" s="79"/>
-      <c r="D10" s="79"/>
-      <c r="E10" s="79"/>
-      <c r="F10" s="79" t="s">
+      <c r="C10" s="86"/>
+      <c r="D10" s="86"/>
+      <c r="E10" s="86"/>
+      <c r="F10" s="86" t="s">
         <v>465</v>
       </c>
-      <c r="G10" s="79"/>
-      <c r="H10" s="79"/>
-      <c r="I10" s="79"/>
+      <c r="G10" s="86"/>
+      <c r="H10" s="86"/>
+      <c r="I10" s="86"/>
     </row>
     <row r="11" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="80" t="s">
+      <c r="A11" s="87" t="s">
         <v>466</v>
       </c>
-      <c r="B11" s="81" t="s">
+      <c r="B11" s="88" t="s">
         <v>467</v>
       </c>
-      <c r="C11" s="78" t="s">
+      <c r="C11" s="85" t="s">
         <v>468</v>
       </c>
-      <c r="D11" s="82" t="s">
+      <c r="D11" s="89" t="s">
         <v>469</v>
       </c>
-      <c r="E11" s="78" t="s">
+      <c r="E11" s="85" t="s">
         <v>470</v>
       </c>
-      <c r="F11" s="82" t="s">
+      <c r="F11" s="89" t="s">
         <v>467</v>
       </c>
-      <c r="G11" s="78" t="s">
+      <c r="G11" s="85" t="s">
         <v>468</v>
       </c>
-      <c r="H11" s="78" t="s">
+      <c r="H11" s="85" t="s">
         <v>471</v>
       </c>
-      <c r="I11" s="78" t="s">
+      <c r="I11" s="85" t="s">
         <v>472</v>
       </c>
-      <c r="J11" s="78" t="s">
+      <c r="J11" s="85" t="s">
         <v>473</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="80"/>
-      <c r="B12" s="81"/>
-      <c r="C12" s="78"/>
-      <c r="D12" s="82"/>
-      <c r="E12" s="78"/>
-      <c r="F12" s="82"/>
-      <c r="G12" s="78"/>
-      <c r="H12" s="78"/>
-      <c r="I12" s="78"/>
-      <c r="J12" s="78"/>
+      <c r="A12" s="87"/>
+      <c r="B12" s="88"/>
+      <c r="C12" s="85"/>
+      <c r="D12" s="89"/>
+      <c r="E12" s="85"/>
+      <c r="F12" s="89"/>
+      <c r="G12" s="85"/>
+      <c r="H12" s="85"/>
+      <c r="I12" s="85"/>
+      <c r="J12" s="85"/>
     </row>
     <row r="13" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="36"/>
@@ -24707,11 +24774,11 @@
         <v>1.8839999999999999</v>
       </c>
       <c r="I72" s="51">
-        <f t="shared" ref="I72:I76" si="22">(H72*1000/F72)*G72</f>
+        <f>(H72*1000/F72)*G72</f>
         <v>8.3285442730206434</v>
       </c>
       <c r="J72" s="48">
-        <f t="shared" ref="J72:J76" si="23">E72-I72</f>
+        <f>E72-I72</f>
         <v>310.70210433710048</v>
       </c>
     </row>
@@ -24742,11 +24809,11 @@
         <v>1.0369999999999999</v>
       </c>
       <c r="I73" s="51">
-        <f t="shared" si="22"/>
+        <f>(H73*1000/F73)*G73</f>
         <v>5.1700069797586998</v>
       </c>
       <c r="J73" s="48">
-        <f t="shared" si="23"/>
+        <f>E73-I73</f>
         <v>289.61156253292222</v>
       </c>
     </row>
@@ -24777,11 +24844,11 @@
         <v>0.2777</v>
       </c>
       <c r="I74" s="51">
-        <f t="shared" si="22"/>
+        <f>(H74*1000/F74)*G74</f>
         <v>1.3652900688298917</v>
       </c>
       <c r="J74" s="48">
-        <f t="shared" si="23"/>
+        <f>E74-I74</f>
         <v>321.24652660703981</v>
       </c>
     </row>
@@ -24812,11 +24879,11 @@
         <v>0.6583</v>
       </c>
       <c r="I75" s="51">
-        <f t="shared" si="22"/>
+        <f>(H75*1000/F75)*G75</f>
         <v>3.1652081930954901</v>
       </c>
       <c r="J75" s="48">
-        <f t="shared" si="23"/>
+        <f>E75-I75</f>
         <v>295.78539329141944</v>
       </c>
     </row>
@@ -24847,11 +24914,11 @@
         <v>0.94920000000000004</v>
       </c>
       <c r="I76" s="51">
-        <f t="shared" si="22"/>
+        <f>(H76*1000/F76)*G76</f>
         <v>4.3298969072164954</v>
       </c>
       <c r="J76" s="48">
-        <f t="shared" si="23"/>
+        <f>E76-I76</f>
         <v>283.95711386986801</v>
       </c>
     </row>
@@ -24894,11 +24961,11 @@
         <v>0.74280000000000002</v>
       </c>
       <c r="I78" s="51">
-        <f t="shared" ref="I78:I82" si="24">(H78*1000/F78)*G78</f>
+        <f>(H78*1000/F78)*G78</f>
         <v>3.166510358939381</v>
       </c>
       <c r="J78" s="48">
-        <f t="shared" ref="J78:J82" si="25">E78-I78</f>
+        <f>E78-I78</f>
         <v>235.58683895709504</v>
       </c>
     </row>
@@ -24929,11 +24996,11 @@
         <v>0.46689999999999998</v>
       </c>
       <c r="I79" s="51">
-        <f t="shared" si="24"/>
+        <f>(H79*1000/F79)*G79</f>
         <v>2.3009067612852356</v>
       </c>
       <c r="J79" s="48">
-        <f t="shared" si="25"/>
+        <f>E79-I79</f>
         <v>263.1545562717705</v>
       </c>
     </row>
@@ -24964,11 +25031,11 @@
         <v>0.93279999999999996</v>
       </c>
       <c r="I80" s="51">
-        <f t="shared" si="24"/>
+        <f>(H80*1000/F80)*G80</f>
         <v>4.2911031373631427</v>
       </c>
       <c r="J80" s="48">
-        <f t="shared" si="25"/>
+        <f>E80-I80</f>
         <v>219.27763902728373</v>
       </c>
     </row>
@@ -24999,11 +25066,11 @@
         <v>0.83840000000000003</v>
       </c>
       <c r="I81" s="51">
-        <f t="shared" si="24"/>
+        <f>(H81*1000/F81)*G81</f>
         <v>3.9053474939444759</v>
       </c>
       <c r="J81" s="48">
-        <f t="shared" si="25"/>
+        <f>E81-I81</f>
         <v>248.96673202070636</v>
       </c>
     </row>
@@ -25034,11 +25101,11 @@
         <v>1.0329999999999999</v>
       </c>
       <c r="I82" s="51">
-        <f t="shared" si="24"/>
+        <f>(H82*1000/F82)*G82</f>
         <v>4.6460376000719616</v>
       </c>
       <c r="J82" s="48">
-        <f t="shared" si="25"/>
+        <f>E82-I82</f>
         <v>251.28818862987103</v>
       </c>
     </row>
@@ -25081,11 +25148,11 @@
         <v>1.6120000000000001</v>
       </c>
       <c r="I84" s="51">
-        <f t="shared" ref="I84:I92" si="26">(H84*1000/F84)*G84</f>
+        <f t="shared" ref="I84:I92" si="22">(H84*1000/F84)*G84</f>
         <v>7.9679699471108698</v>
       </c>
       <c r="J84" s="48">
-        <f t="shared" ref="J84:J92" si="27">E84-I84</f>
+        <f t="shared" ref="J84:J92" si="23">E84-I84</f>
         <v>276.25763901472317</v>
       </c>
     </row>
@@ -25116,11 +25183,11 @@
         <v>0.40550000000000003</v>
       </c>
       <c r="I85" s="51">
-        <f t="shared" si="26"/>
+        <f t="shared" si="22"/>
         <v>1.9974385498251319</v>
       </c>
       <c r="J85" s="48">
-        <f t="shared" si="27"/>
+        <f t="shared" si="23"/>
         <v>277.33532933256112</v>
       </c>
     </row>
@@ -25151,11 +25218,11 @@
         <v>1.333</v>
       </c>
       <c r="I86" s="51">
-        <f t="shared" si="26"/>
+        <f t="shared" si="22"/>
         <v>6.3494331713822998</v>
       </c>
       <c r="J86" s="48">
-        <f t="shared" si="27"/>
+        <f t="shared" si="23"/>
         <v>296.51888495117311</v>
       </c>
     </row>
@@ -25186,11 +25253,11 @@
         <v>0</v>
       </c>
       <c r="I87" s="51">
-        <f t="shared" si="26"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="J87" s="48">
-        <f t="shared" si="27"/>
+        <f t="shared" si="23"/>
         <v>285.69436698271056</v>
       </c>
     </row>
@@ -25233,11 +25300,11 @@
         <v>1.1459999999999999</v>
       </c>
       <c r="I89" s="51">
-        <f t="shared" si="26"/>
+        <f t="shared" si="22"/>
         <v>5.6741100163390605</v>
       </c>
       <c r="J89" s="48">
-        <f t="shared" si="27"/>
+        <f t="shared" si="23"/>
         <v>225.10577639452117</v>
       </c>
     </row>
@@ -25268,11 +25335,11 @@
         <v>0.25940000000000002</v>
       </c>
       <c r="I90" s="51">
-        <f t="shared" si="26"/>
+        <f t="shared" si="22"/>
         <v>1.2227774111435847</v>
       </c>
       <c r="J90" s="48">
-        <f t="shared" si="27"/>
+        <f t="shared" si="23"/>
         <v>238.24916978357587</v>
       </c>
     </row>
@@ -25303,11 +25370,11 @@
         <v>0.2412</v>
       </c>
       <c r="I91" s="51">
-        <f t="shared" si="26"/>
+        <f t="shared" si="22"/>
         <v>1.1922886801779533</v>
       </c>
       <c r="J91" s="48">
-        <f t="shared" si="27"/>
+        <f t="shared" si="23"/>
         <v>238.08280688827739</v>
       </c>
     </row>
@@ -25338,11 +25405,11 @@
         <v>0</v>
       </c>
       <c r="I92" s="51">
-        <f t="shared" si="26"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="J92" s="48">
-        <f t="shared" si="27"/>
+        <f t="shared" si="23"/>
         <v>194.70649895178198</v>
       </c>
     </row>
@@ -25365,18 +25432,6 @@
     </row>
   </sheetData>
   <mergeCells count="24">
-    <mergeCell ref="A1:C3"/>
-    <mergeCell ref="D1:I1"/>
-    <mergeCell ref="D2:I2"/>
-    <mergeCell ref="D3:I3"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="C8:D8"/>
     <mergeCell ref="I11:I12"/>
     <mergeCell ref="J11:J12"/>
     <mergeCell ref="B10:E10"/>
@@ -25389,6 +25444,18 @@
     <mergeCell ref="F11:F12"/>
     <mergeCell ref="G11:G12"/>
     <mergeCell ref="H11:H12"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="A1:C3"/>
+    <mergeCell ref="D1:I1"/>
+    <mergeCell ref="D2:I2"/>
+    <mergeCell ref="D3:I3"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="C5:D5"/>
   </mergeCells>
   <pageMargins left="0.23611111111111099" right="0.23611111111111099" top="0.196527777777778" bottom="0.196527777777778" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="81" orientation="landscape" horizontalDpi="300" verticalDpi="300"/>
@@ -25792,4 +25859,461 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:G17"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>557</v>
+      </c>
+      <c r="B1" t="s">
+        <v>569</v>
+      </c>
+      <c r="C1" t="s">
+        <v>570</v>
+      </c>
+      <c r="D1" t="s">
+        <v>571</v>
+      </c>
+      <c r="E1" t="s">
+        <v>588</v>
+      </c>
+      <c r="F1" t="s">
+        <v>589</v>
+      </c>
+      <c r="G1" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>572</v>
+      </c>
+      <c r="B2">
+        <v>8.4529999999999994</v>
+      </c>
+      <c r="C2">
+        <v>39.57</v>
+      </c>
+      <c r="D2">
+        <v>27.128</v>
+      </c>
+      <c r="E2">
+        <f>C2-$B2</f>
+        <v>31.117000000000001</v>
+      </c>
+      <c r="F2">
+        <f>D2-$B2</f>
+        <v>18.675000000000001</v>
+      </c>
+      <c r="G2">
+        <f>F2/20</f>
+        <v>0.93375000000000008</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>573</v>
+      </c>
+      <c r="B3">
+        <v>7.3449999999999998</v>
+      </c>
+      <c r="C3">
+        <v>36.25</v>
+      </c>
+      <c r="D3">
+        <v>25.039000000000001</v>
+      </c>
+      <c r="E3">
+        <f t="shared" ref="E3:E17" si="0">C3-$B3</f>
+        <v>28.905000000000001</v>
+      </c>
+      <c r="F3">
+        <f t="shared" ref="F3:F17" si="1">D3-$B3</f>
+        <v>17.694000000000003</v>
+      </c>
+      <c r="G3">
+        <f t="shared" ref="G3:G17" si="2">F3/20</f>
+        <v>0.88470000000000015</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>574</v>
+      </c>
+      <c r="B4">
+        <v>8.3119999999999994</v>
+      </c>
+      <c r="C4">
+        <v>40.463000000000001</v>
+      </c>
+      <c r="D4">
+        <v>29.382999999999999</v>
+      </c>
+      <c r="E4">
+        <f t="shared" si="0"/>
+        <v>32.151000000000003</v>
+      </c>
+      <c r="F4">
+        <f t="shared" si="1"/>
+        <v>21.070999999999998</v>
+      </c>
+      <c r="G4">
+        <f t="shared" si="2"/>
+        <v>1.05355</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>575</v>
+      </c>
+      <c r="B5">
+        <v>7.1029999999999998</v>
+      </c>
+      <c r="C5">
+        <v>35.981999999999999</v>
+      </c>
+      <c r="D5">
+        <v>24.556999999999999</v>
+      </c>
+      <c r="E5">
+        <f t="shared" si="0"/>
+        <v>28.878999999999998</v>
+      </c>
+      <c r="F5">
+        <f t="shared" si="1"/>
+        <v>17.454000000000001</v>
+      </c>
+      <c r="G5">
+        <f t="shared" si="2"/>
+        <v>0.87270000000000003</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>576</v>
+      </c>
+      <c r="B6">
+        <v>8.4369999999999994</v>
+      </c>
+      <c r="C6">
+        <v>68.662999999999997</v>
+      </c>
+      <c r="D6">
+        <v>26.135999999999999</v>
+      </c>
+      <c r="E6">
+        <f t="shared" si="0"/>
+        <v>60.225999999999999</v>
+      </c>
+      <c r="F6">
+        <f t="shared" si="1"/>
+        <v>17.698999999999998</v>
+      </c>
+      <c r="G6">
+        <f t="shared" si="2"/>
+        <v>0.8849499999999999</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>577</v>
+      </c>
+      <c r="B7">
+        <v>7.3289999999999997</v>
+      </c>
+      <c r="C7">
+        <v>32.713000000000001</v>
+      </c>
+      <c r="D7">
+        <v>21.346</v>
+      </c>
+      <c r="E7">
+        <f t="shared" si="0"/>
+        <v>25.384</v>
+      </c>
+      <c r="F7">
+        <f t="shared" si="1"/>
+        <v>14.016999999999999</v>
+      </c>
+      <c r="G7">
+        <f t="shared" si="2"/>
+        <v>0.70084999999999997</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>578</v>
+      </c>
+      <c r="B8">
+        <v>8.32</v>
+      </c>
+      <c r="C8">
+        <v>37.764000000000003</v>
+      </c>
+      <c r="D8">
+        <v>25.591999999999999</v>
+      </c>
+      <c r="E8">
+        <f t="shared" si="0"/>
+        <v>29.444000000000003</v>
+      </c>
+      <c r="F8">
+        <f t="shared" si="1"/>
+        <v>17.271999999999998</v>
+      </c>
+      <c r="G8">
+        <f t="shared" si="2"/>
+        <v>0.86359999999999992</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>579</v>
+      </c>
+      <c r="B9">
+        <v>8.4390000000000001</v>
+      </c>
+      <c r="C9">
+        <v>34.822000000000003</v>
+      </c>
+      <c r="D9">
+        <v>25.2</v>
+      </c>
+      <c r="E9">
+        <f t="shared" si="0"/>
+        <v>26.383000000000003</v>
+      </c>
+      <c r="F9">
+        <f t="shared" si="1"/>
+        <v>16.760999999999999</v>
+      </c>
+      <c r="G9">
+        <f t="shared" si="2"/>
+        <v>0.83804999999999996</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>580</v>
+      </c>
+      <c r="B10">
+        <v>7.1150000000000002</v>
+      </c>
+      <c r="C10">
+        <v>36.137</v>
+      </c>
+      <c r="D10">
+        <v>23.271999999999998</v>
+      </c>
+      <c r="E10">
+        <f t="shared" si="0"/>
+        <v>29.021999999999998</v>
+      </c>
+      <c r="F10">
+        <f t="shared" si="1"/>
+        <v>16.156999999999996</v>
+      </c>
+      <c r="G10">
+        <f t="shared" si="2"/>
+        <v>0.80784999999999985</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>581</v>
+      </c>
+      <c r="B11">
+        <v>8.3239999999999998</v>
+      </c>
+      <c r="C11">
+        <v>37.029000000000003</v>
+      </c>
+      <c r="D11">
+        <v>24.58</v>
+      </c>
+      <c r="E11">
+        <f t="shared" si="0"/>
+        <v>28.705000000000005</v>
+      </c>
+      <c r="F11">
+        <f t="shared" si="1"/>
+        <v>16.256</v>
+      </c>
+      <c r="G11">
+        <f t="shared" si="2"/>
+        <v>0.81279999999999997</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>582</v>
+      </c>
+      <c r="B12">
+        <v>7.3310000000000004</v>
+      </c>
+      <c r="C12">
+        <v>37.670999999999999</v>
+      </c>
+      <c r="D12">
+        <v>25.385000000000002</v>
+      </c>
+      <c r="E12">
+        <f t="shared" si="0"/>
+        <v>30.34</v>
+      </c>
+      <c r="F12">
+        <f t="shared" si="1"/>
+        <v>18.054000000000002</v>
+      </c>
+      <c r="G12">
+        <f t="shared" si="2"/>
+        <v>0.90270000000000006</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>583</v>
+      </c>
+      <c r="B13">
+        <v>7.1120000000000001</v>
+      </c>
+      <c r="C13">
+        <v>36.411999999999999</v>
+      </c>
+      <c r="D13">
+        <v>23.952000000000002</v>
+      </c>
+      <c r="E13">
+        <f t="shared" si="0"/>
+        <v>29.299999999999997</v>
+      </c>
+      <c r="F13">
+        <f t="shared" si="1"/>
+        <v>16.840000000000003</v>
+      </c>
+      <c r="G13">
+        <f t="shared" si="2"/>
+        <v>0.84200000000000019</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>584</v>
+      </c>
+      <c r="B14">
+        <v>7.1059999999999999</v>
+      </c>
+      <c r="C14">
+        <v>36.823999999999998</v>
+      </c>
+      <c r="D14">
+        <v>24.004000000000001</v>
+      </c>
+      <c r="E14">
+        <f t="shared" si="0"/>
+        <v>29.717999999999996</v>
+      </c>
+      <c r="F14">
+        <f t="shared" si="1"/>
+        <v>16.898000000000003</v>
+      </c>
+      <c r="G14">
+        <f t="shared" si="2"/>
+        <v>0.84490000000000021</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>585</v>
+      </c>
+      <c r="B15">
+        <v>8.3140000000000001</v>
+      </c>
+      <c r="C15">
+        <v>36.771000000000001</v>
+      </c>
+      <c r="D15">
+        <v>24.411000000000001</v>
+      </c>
+      <c r="E15">
+        <f t="shared" si="0"/>
+        <v>28.457000000000001</v>
+      </c>
+      <c r="F15">
+        <f t="shared" si="1"/>
+        <v>16.097000000000001</v>
+      </c>
+      <c r="G15">
+        <f t="shared" si="2"/>
+        <v>0.80485000000000007</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>586</v>
+      </c>
+      <c r="B16">
+        <v>7.3310000000000004</v>
+      </c>
+      <c r="C16">
+        <v>36.93</v>
+      </c>
+      <c r="D16">
+        <v>24.879000000000001</v>
+      </c>
+      <c r="E16">
+        <f t="shared" si="0"/>
+        <v>29.599</v>
+      </c>
+      <c r="F16">
+        <f t="shared" si="1"/>
+        <v>17.548000000000002</v>
+      </c>
+      <c r="G16">
+        <f t="shared" si="2"/>
+        <v>0.87740000000000007</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>587</v>
+      </c>
+      <c r="B17">
+        <v>8.44</v>
+      </c>
+      <c r="C17">
+        <v>38.298999999999999</v>
+      </c>
+      <c r="D17">
+        <v>26.274000000000001</v>
+      </c>
+      <c r="E17">
+        <f t="shared" si="0"/>
+        <v>29.859000000000002</v>
+      </c>
+      <c r="F17">
+        <f t="shared" si="1"/>
+        <v>17.834000000000003</v>
+      </c>
+      <c r="G17">
+        <f t="shared" si="2"/>
+        <v>0.89170000000000016</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/data/carbon/Aveiro2025_Biomass_C_cores.xlsx
+++ b/data/carbon/Aveiro2025_Biomass_C_cores.xlsx
@@ -18,15 +18,17 @@
     <sheet name="carbon" sheetId="5" r:id="rId4"/>
     <sheet name="moisture" sheetId="6" r:id="rId5"/>
     <sheet name="soil" sheetId="7" r:id="rId6"/>
+    <sheet name="soil carbon" sheetId="8" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">raw!$A$1:$O$100</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'seagrass biomass'!$A$1:$F$179</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">carbon!$A$1:$J$22</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="6">'soil carbon'!$A$1:$J$22</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId7"/>
+    <pivotCache cacheId="0" r:id="rId8"/>
   </pivotCaches>
 </workbook>
 </file>
@@ -161,7 +163,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2159" uniqueCount="591">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2201" uniqueCount="590">
   <si>
     <t>type</t>
   </si>
@@ -2027,12 +2029,6 @@
     <t>Petri_dish</t>
   </si>
   <si>
-    <t>Init_weight_petri</t>
-  </si>
-  <si>
-    <t>Final_weight_petri</t>
-  </si>
-  <si>
     <t>RS01</t>
   </si>
   <si>
@@ -2081,13 +2077,16 @@
     <t>NS08</t>
   </si>
   <si>
-    <t>Init_weight</t>
-  </si>
-  <si>
-    <t>Final_weight</t>
-  </si>
-  <si>
-    <t>Dry_bulk_density</t>
+    <t>DryMassTotal_petri</t>
+  </si>
+  <si>
+    <t>InitWeight_petri</t>
+  </si>
+  <si>
+    <t>InitWeight</t>
+  </si>
+  <si>
+    <t>DryBulkDensity</t>
   </si>
 </sst>
 </file>
@@ -2099,11 +2098,18 @@
     <numFmt numFmtId="165" formatCode="m/d/yyyy"/>
     <numFmt numFmtId="166" formatCode="0.000"/>
   </numFmts>
-  <fonts count="25" x14ac:knownFonts="1">
+  <fonts count="26" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -2574,31 +2580,31 @@
   </borders>
   <cellStyleXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
       <alignment horizontal="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
       <alignment horizontal="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="164" fontId="24" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="25" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="90">
+  <cellXfs count="93">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -2606,16 +2612,16 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="2" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -2649,135 +2655,135 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="1" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="1" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="0" xfId="6" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" xfId="6" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" xfId="8" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" xfId="8" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="0" xfId="9" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" xfId="9" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="5" xfId="9" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="5" xfId="9" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="6" xfId="9" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="6" xfId="9" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="15" fillId="9" borderId="5" xfId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="10" fontId="16" fillId="9" borderId="5" xfId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="15" fillId="9" borderId="7" xfId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="166" fontId="16" fillId="9" borderId="7" xfId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="15" fillId="11" borderId="5" xfId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="2" fontId="16" fillId="11" borderId="5" xfId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="7" xfId="9" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="7" xfId="9" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="15" fillId="9" borderId="5" xfId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="166" fontId="16" fillId="9" borderId="5" xfId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="15" fillId="11" borderId="8" xfId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="166" fontId="16" fillId="11" borderId="8" xfId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="9" xfId="9" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="9" xfId="9" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="10" xfId="9" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="10" xfId="9" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="15" fillId="9" borderId="9" xfId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="10" fontId="16" fillId="9" borderId="9" xfId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="15" fillId="9" borderId="11" xfId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="166" fontId="16" fillId="9" borderId="11" xfId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="15" fillId="11" borderId="12" xfId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="2" fontId="16" fillId="11" borderId="12" xfId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="11" xfId="9" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="11" xfId="9" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="15" fillId="9" borderId="9" xfId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="166" fontId="16" fillId="9" borderId="9" xfId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="15" fillId="11" borderId="13" xfId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="166" fontId="16" fillId="11" borderId="13" xfId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="14" xfId="5" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="14" xfId="5" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="5" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="5" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="14" xfId="5" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="14" xfId="5" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="14" xfId="5" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="14" xfId="5" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="14" xfId="5" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="14" xfId="5" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="14" xfId="5" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="14" xfId="5" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="17" borderId="14" xfId="5" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="14" xfId="5" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="14" xfId="5" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="14" xfId="5" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="14" xfId="5" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="14" xfId="5" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -2792,73 +2798,78 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="10" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="10" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="10" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="10" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="10" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="10" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="10" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="10" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="10" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="10" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="10" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="10" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="10" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="10" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="10" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="10" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="10" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="10" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="0" xfId="6" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" xfId="6" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="1" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="1" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="2" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="1" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="2" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="2" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="2" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="1" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="1" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="1" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="1" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="15" fillId="10" borderId="1" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="165" fontId="16" fillId="10" borderId="1" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="1" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="1" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="1" xfId="9" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="1" xfId="9" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="3" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="3" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="3" xfId="9" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="3" xfId="9" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="2" xfId="9" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="2" xfId="9" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="4" xfId="9" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="4" xfId="9" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2960,6 +2971,48 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>390600</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>190440</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>421560</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>141480</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Image 3"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="390600" y="190440"/>
+          <a:ext cx="2164560" cy="446340"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -22742,78 +22795,78 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="78"/>
-      <c r="B1" s="78"/>
-      <c r="C1" s="78"/>
-      <c r="D1" s="79" t="s">
+      <c r="A1" s="81"/>
+      <c r="B1" s="81"/>
+      <c r="C1" s="81"/>
+      <c r="D1" s="82" t="s">
         <v>457</v>
       </c>
-      <c r="E1" s="79"/>
-      <c r="F1" s="79"/>
-      <c r="G1" s="79"/>
-      <c r="H1" s="79"/>
-      <c r="I1" s="79"/>
+      <c r="E1" s="82"/>
+      <c r="F1" s="82"/>
+      <c r="G1" s="82"/>
+      <c r="H1" s="82"/>
+      <c r="I1" s="82"/>
       <c r="J1" s="32"/>
     </row>
     <row r="2" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="78"/>
-      <c r="B2" s="78"/>
-      <c r="C2" s="78"/>
-      <c r="D2" s="79" t="s">
+      <c r="A2" s="81"/>
+      <c r="B2" s="81"/>
+      <c r="C2" s="81"/>
+      <c r="D2" s="82" t="s">
         <v>458</v>
       </c>
-      <c r="E2" s="79"/>
-      <c r="F2" s="79"/>
-      <c r="G2" s="79"/>
-      <c r="H2" s="79"/>
-      <c r="I2" s="79"/>
+      <c r="E2" s="82"/>
+      <c r="F2" s="82"/>
+      <c r="G2" s="82"/>
+      <c r="H2" s="82"/>
+      <c r="I2" s="82"/>
       <c r="J2" s="32"/>
     </row>
     <row r="3" spans="1:10" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="78"/>
-      <c r="B3" s="78"/>
-      <c r="C3" s="78"/>
-      <c r="D3" s="80" t="s">
+      <c r="A3" s="81"/>
+      <c r="B3" s="81"/>
+      <c r="C3" s="81"/>
+      <c r="D3" s="83" t="s">
         <v>459</v>
       </c>
-      <c r="E3" s="80"/>
-      <c r="F3" s="80"/>
-      <c r="G3" s="80"/>
-      <c r="H3" s="80"/>
-      <c r="I3" s="80"/>
+      <c r="E3" s="83"/>
+      <c r="F3" s="83"/>
+      <c r="G3" s="83"/>
+      <c r="H3" s="83"/>
+      <c r="I3" s="83"/>
       <c r="J3" s="32"/>
     </row>
     <row r="5" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="81" t="s">
+      <c r="A5" s="84" t="s">
         <v>460</v>
       </c>
-      <c r="B5" s="81"/>
-      <c r="C5" s="82"/>
-      <c r="D5" s="82"/>
+      <c r="B5" s="84"/>
+      <c r="C5" s="85"/>
+      <c r="D5" s="85"/>
     </row>
     <row r="6" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="81" t="s">
+      <c r="A6" s="84" t="s">
         <v>461</v>
       </c>
-      <c r="B6" s="81"/>
-      <c r="C6" s="83"/>
-      <c r="D6" s="83"/>
+      <c r="B6" s="84"/>
+      <c r="C6" s="86"/>
+      <c r="D6" s="86"/>
     </row>
     <row r="7" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="81" t="s">
+      <c r="A7" s="84" t="s">
         <v>462</v>
       </c>
-      <c r="B7" s="81"/>
-      <c r="C7" s="82"/>
-      <c r="D7" s="82"/>
+      <c r="B7" s="84"/>
+      <c r="C7" s="85"/>
+      <c r="D7" s="85"/>
     </row>
     <row r="8" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="81" t="s">
+      <c r="A8" s="84" t="s">
         <v>463</v>
       </c>
-      <c r="B8" s="81"/>
-      <c r="C8" s="84"/>
-      <c r="D8" s="84"/>
+      <c r="B8" s="84"/>
+      <c r="C8" s="87"/>
+      <c r="D8" s="87"/>
     </row>
     <row r="9" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="34"/>
@@ -22826,62 +22879,62 @@
     </row>
     <row r="10" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="35"/>
-      <c r="B10" s="86" t="s">
+      <c r="B10" s="89" t="s">
         <v>464</v>
       </c>
-      <c r="C10" s="86"/>
-      <c r="D10" s="86"/>
-      <c r="E10" s="86"/>
-      <c r="F10" s="86" t="s">
+      <c r="C10" s="89"/>
+      <c r="D10" s="89"/>
+      <c r="E10" s="89"/>
+      <c r="F10" s="89" t="s">
         <v>465</v>
       </c>
-      <c r="G10" s="86"/>
-      <c r="H10" s="86"/>
-      <c r="I10" s="86"/>
+      <c r="G10" s="89"/>
+      <c r="H10" s="89"/>
+      <c r="I10" s="89"/>
     </row>
     <row r="11" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="87" t="s">
+      <c r="A11" s="90" t="s">
         <v>466</v>
       </c>
-      <c r="B11" s="88" t="s">
+      <c r="B11" s="91" t="s">
         <v>467</v>
       </c>
-      <c r="C11" s="85" t="s">
+      <c r="C11" s="88" t="s">
         <v>468</v>
       </c>
-      <c r="D11" s="89" t="s">
+      <c r="D11" s="92" t="s">
         <v>469</v>
       </c>
-      <c r="E11" s="85" t="s">
+      <c r="E11" s="88" t="s">
         <v>470</v>
       </c>
-      <c r="F11" s="89" t="s">
+      <c r="F11" s="92" t="s">
         <v>467</v>
       </c>
-      <c r="G11" s="85" t="s">
+      <c r="G11" s="88" t="s">
         <v>468</v>
       </c>
-      <c r="H11" s="85" t="s">
+      <c r="H11" s="88" t="s">
         <v>471</v>
       </c>
-      <c r="I11" s="85" t="s">
+      <c r="I11" s="88" t="s">
         <v>472</v>
       </c>
-      <c r="J11" s="85" t="s">
+      <c r="J11" s="88" t="s">
         <v>473</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="87"/>
-      <c r="B12" s="88"/>
-      <c r="C12" s="85"/>
-      <c r="D12" s="89"/>
-      <c r="E12" s="85"/>
-      <c r="F12" s="89"/>
-      <c r="G12" s="85"/>
-      <c r="H12" s="85"/>
-      <c r="I12" s="85"/>
-      <c r="J12" s="85"/>
+      <c r="A12" s="90"/>
+      <c r="B12" s="91"/>
+      <c r="C12" s="88"/>
+      <c r="D12" s="92"/>
+      <c r="E12" s="88"/>
+      <c r="F12" s="92"/>
+      <c r="G12" s="88"/>
+      <c r="H12" s="88"/>
+      <c r="I12" s="88"/>
+      <c r="J12" s="88"/>
     </row>
     <row r="13" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="36"/>
@@ -25863,43 +25916,59 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:K17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="10" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="16.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.42578125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>557</v>
       </c>
       <c r="B1" t="s">
         <v>569</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="80" t="s">
+        <v>587</v>
+      </c>
+      <c r="D1" s="80" t="s">
+        <v>586</v>
+      </c>
+      <c r="E1" s="80" t="s">
+        <v>588</v>
+      </c>
+      <c r="F1" s="79" t="s">
+        <v>521</v>
+      </c>
+      <c r="G1" s="79" t="s">
+        <v>589</v>
+      </c>
+      <c r="H1" s="31" t="s">
+        <v>520</v>
+      </c>
+      <c r="I1" s="31" t="s">
+        <v>522</v>
+      </c>
+      <c r="J1" s="31" t="s">
+        <v>523</v>
+      </c>
+      <c r="K1" s="31" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>570</v>
-      </c>
-      <c r="D1" t="s">
-        <v>571</v>
-      </c>
-      <c r="E1" t="s">
-        <v>588</v>
-      </c>
-      <c r="F1" t="s">
-        <v>589</v>
-      </c>
-      <c r="G1" t="s">
-        <v>590</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>572</v>
       </c>
       <c r="B2">
         <v>8.4529999999999994</v>
@@ -25922,10 +25991,26 @@
         <f>F2/20</f>
         <v>0.93375000000000008</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H2" s="66">
+        <f>IFERROR(INDEX('soil carbon'!$A$14:$J$30,MATCH($A2,'soil carbon'!$A$14:$A$30,0),2), "NA")</f>
+        <v>76.77</v>
+      </c>
+      <c r="I2" s="66">
+        <f>IFERROR(INDEX('soil carbon'!$A$14:$J$30,MATCH($A2,'soil carbon'!$A$14:$A$30,0),4), "NA")</f>
+        <v>1.66</v>
+      </c>
+      <c r="J2" s="66">
+        <f>IFERROR(INDEX('soil carbon'!$A$14:$J$30,MATCH($A2,'soil carbon'!$A$14:$A$30,0),6), "NA")</f>
+        <v>203.1</v>
+      </c>
+      <c r="K2" s="66">
+        <f>IFERROR(INDEX('soil carbon'!$A$14:$J$30,MATCH($A2,'soil carbon'!$A$14:$A$30,0),8), "NA")</f>
+        <v>0.10730000000000001</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="B3">
         <v>7.3449999999999998</v>
@@ -25948,10 +26033,26 @@
         <f t="shared" ref="G3:G17" si="2">F3/20</f>
         <v>0.88470000000000015</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H3" s="66">
+        <f>IFERROR(INDEX('soil carbon'!$A$14:$J$30,MATCH($A3,'soil carbon'!$A$14:$A$30,0),2), "NA")</f>
+        <v>73.52</v>
+      </c>
+      <c r="I3" s="66">
+        <f>IFERROR(INDEX('soil carbon'!$A$14:$J$30,MATCH($A3,'soil carbon'!$A$14:$A$30,0),4), "NA")</f>
+        <v>1.8089999999999999</v>
+      </c>
+      <c r="J3" s="66">
+        <f>IFERROR(INDEX('soil carbon'!$A$14:$J$30,MATCH($A3,'soil carbon'!$A$14:$A$30,0),6), "NA")</f>
+        <v>210.1</v>
+      </c>
+      <c r="K3" s="66">
+        <f>IFERROR(INDEX('soil carbon'!$A$14:$J$30,MATCH($A3,'soil carbon'!$A$14:$A$30,0),8), "NA")</f>
+        <v>0.1726</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="B4">
         <v>8.3119999999999994</v>
@@ -25974,10 +26075,26 @@
         <f t="shared" si="2"/>
         <v>1.05355</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H4" s="66">
+        <f>IFERROR(INDEX('soil carbon'!$A$14:$J$30,MATCH($A4,'soil carbon'!$A$14:$A$30,0),2), "NA")</f>
+        <v>76.790000000000006</v>
+      </c>
+      <c r="I4" s="66">
+        <f>IFERROR(INDEX('soil carbon'!$A$14:$J$30,MATCH($A4,'soil carbon'!$A$14:$A$30,0),4), "NA")</f>
+        <v>1.24</v>
+      </c>
+      <c r="J4" s="66">
+        <f>IFERROR(INDEX('soil carbon'!$A$14:$J$30,MATCH($A4,'soil carbon'!$A$14:$A$30,0),6), "NA")</f>
+        <v>207.1</v>
+      </c>
+      <c r="K4" s="66">
+        <f>IFERROR(INDEX('soil carbon'!$A$14:$J$30,MATCH($A4,'soil carbon'!$A$14:$A$30,0),8), "NA")</f>
+        <v>1.048E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="B5">
         <v>7.1029999999999998</v>
@@ -26000,10 +26117,26 @@
         <f t="shared" si="2"/>
         <v>0.87270000000000003</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H5" s="66">
+        <f>IFERROR(INDEX('soil carbon'!$A$14:$J$30,MATCH($A5,'soil carbon'!$A$14:$A$30,0),2), "NA")</f>
+        <v>73.13</v>
+      </c>
+      <c r="I5" s="66">
+        <f>IFERROR(INDEX('soil carbon'!$A$14:$J$30,MATCH($A5,'soil carbon'!$A$14:$A$30,0),4), "NA")</f>
+        <v>1.7250000000000001</v>
+      </c>
+      <c r="J5" s="66">
+        <f>IFERROR(INDEX('soil carbon'!$A$14:$J$30,MATCH($A5,'soil carbon'!$A$14:$A$30,0),6), "NA")</f>
+        <v>203.8</v>
+      </c>
+      <c r="K5" s="66">
+        <f>IFERROR(INDEX('soil carbon'!$A$14:$J$30,MATCH($A5,'soil carbon'!$A$14:$A$30,0),8), "NA")</f>
+        <v>0.22020000000000001</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="B6">
         <v>8.4369999999999994</v>
@@ -26026,10 +26159,26 @@
         <f t="shared" si="2"/>
         <v>0.8849499999999999</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H6" s="66">
+        <f>IFERROR(INDEX('soil carbon'!$A$14:$J$30,MATCH($A6,'soil carbon'!$A$14:$A$30,0),2), "NA")</f>
+        <v>75.63</v>
+      </c>
+      <c r="I6" s="66">
+        <f>IFERROR(INDEX('soil carbon'!$A$14:$J$30,MATCH($A6,'soil carbon'!$A$14:$A$30,0),4), "NA")</f>
+        <v>2.3620000000000001</v>
+      </c>
+      <c r="J6" s="66">
+        <f>IFERROR(INDEX('soil carbon'!$A$14:$J$30,MATCH($A6,'soil carbon'!$A$14:$A$30,0),6), "NA")</f>
+        <v>201.8</v>
+      </c>
+      <c r="K6" s="66">
+        <f>IFERROR(INDEX('soil carbon'!$A$14:$J$30,MATCH($A6,'soil carbon'!$A$14:$A$30,0),8), "NA")</f>
+        <v>8.4159999999999999E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="B7">
         <v>7.3289999999999997</v>
@@ -26052,10 +26201,26 @@
         <f t="shared" si="2"/>
         <v>0.70084999999999997</v>
       </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H7" s="66">
+        <f>IFERROR(INDEX('soil carbon'!$A$14:$J$30,MATCH($A7,'soil carbon'!$A$14:$A$30,0),2), "NA")</f>
+        <v>72.069999999999993</v>
+      </c>
+      <c r="I7" s="66">
+        <f>IFERROR(INDEX('soil carbon'!$A$14:$J$30,MATCH($A7,'soil carbon'!$A$14:$A$30,0),4), "NA")</f>
+        <v>2.081</v>
+      </c>
+      <c r="J7" s="66">
+        <f>IFERROR(INDEX('soil carbon'!$A$14:$J$30,MATCH($A7,'soil carbon'!$A$14:$A$30,0),6), "NA")</f>
+        <v>212.3</v>
+      </c>
+      <c r="K7" s="66">
+        <f>IFERROR(INDEX('soil carbon'!$A$14:$J$30,MATCH($A7,'soil carbon'!$A$14:$A$30,0),8), "NA")</f>
+        <v>0.1186</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="B8">
         <v>8.32</v>
@@ -26078,10 +26243,26 @@
         <f t="shared" si="2"/>
         <v>0.86359999999999992</v>
       </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H8" s="66">
+        <f>IFERROR(INDEX('soil carbon'!$A$14:$J$30,MATCH($A8,'soil carbon'!$A$14:$A$30,0),2), "NA")</f>
+        <v>72.760000000000005</v>
+      </c>
+      <c r="I8" s="66">
+        <f>IFERROR(INDEX('soil carbon'!$A$14:$J$30,MATCH($A8,'soil carbon'!$A$14:$A$30,0),4), "NA")</f>
+        <v>1.927</v>
+      </c>
+      <c r="J8" s="66">
+        <f>IFERROR(INDEX('soil carbon'!$A$14:$J$30,MATCH($A8,'soil carbon'!$A$14:$A$30,0),6), "NA")</f>
+        <v>203.8</v>
+      </c>
+      <c r="K8" s="66">
+        <f>IFERROR(INDEX('soil carbon'!$A$14:$J$30,MATCH($A8,'soil carbon'!$A$14:$A$30,0),8), "NA")</f>
+        <v>0.12870000000000001</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="B9">
         <v>8.4390000000000001</v>
@@ -26104,10 +26285,26 @@
         <f t="shared" si="2"/>
         <v>0.83804999999999996</v>
       </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H9" s="66">
+        <f>IFERROR(INDEX('soil carbon'!$A$14:$J$30,MATCH($A9,'soil carbon'!$A$14:$A$30,0),2), "NA")</f>
+        <v>75.42</v>
+      </c>
+      <c r="I9" s="66">
+        <f>IFERROR(INDEX('soil carbon'!$A$14:$J$30,MATCH($A9,'soil carbon'!$A$14:$A$30,0),4), "NA")</f>
+        <v>1.8560000000000001</v>
+      </c>
+      <c r="J9" s="66">
+        <f>IFERROR(INDEX('soil carbon'!$A$14:$J$30,MATCH($A9,'soil carbon'!$A$14:$A$30,0),6), "NA")</f>
+        <v>202.3</v>
+      </c>
+      <c r="K9" s="66">
+        <f>IFERROR(INDEX('soil carbon'!$A$14:$J$30,MATCH($A9,'soil carbon'!$A$14:$A$30,0),8), "NA")</f>
+        <v>0.3664</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="B10">
         <v>7.1150000000000002</v>
@@ -26130,10 +26327,26 @@
         <f t="shared" si="2"/>
         <v>0.80784999999999985</v>
       </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H10" s="66">
+        <f>IFERROR(INDEX('soil carbon'!$A$14:$J$30,MATCH($A10,'soil carbon'!$A$14:$A$30,0),2), "NA")</f>
+        <v>79.290000000000006</v>
+      </c>
+      <c r="I10" s="66">
+        <f>IFERROR(INDEX('soil carbon'!$A$14:$J$30,MATCH($A10,'soil carbon'!$A$14:$A$30,0),4), "NA")</f>
+        <v>2.1259999999999999</v>
+      </c>
+      <c r="J10" s="66">
+        <f>IFERROR(INDEX('soil carbon'!$A$14:$J$30,MATCH($A10,'soil carbon'!$A$14:$A$30,0),6), "NA")</f>
+        <v>212.3</v>
+      </c>
+      <c r="K10" s="66">
+        <f>IFERROR(INDEX('soil carbon'!$A$14:$J$30,MATCH($A10,'soil carbon'!$A$14:$A$30,0),8), "NA")</f>
+        <v>0.21440000000000001</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="B11">
         <v>8.3239999999999998</v>
@@ -26156,10 +26369,26 @@
         <f t="shared" si="2"/>
         <v>0.81279999999999997</v>
       </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H11" s="66">
+        <f>IFERROR(INDEX('soil carbon'!$A$14:$J$30,MATCH($A11,'soil carbon'!$A$14:$A$30,0),2), "NA")</f>
+        <v>74.98</v>
+      </c>
+      <c r="I11" s="66">
+        <f>IFERROR(INDEX('soil carbon'!$A$14:$J$30,MATCH($A11,'soil carbon'!$A$14:$A$30,0),4), "NA")</f>
+        <v>2.024</v>
+      </c>
+      <c r="J11" s="66">
+        <f>IFERROR(INDEX('soil carbon'!$A$14:$J$30,MATCH($A11,'soil carbon'!$A$14:$A$30,0),6), "NA")</f>
+        <v>200.28</v>
+      </c>
+      <c r="K11" s="66">
+        <f>IFERROR(INDEX('soil carbon'!$A$14:$J$30,MATCH($A11,'soil carbon'!$A$14:$A$30,0),8), "NA")</f>
+        <v>0.2049</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="B12">
         <v>7.3310000000000004</v>
@@ -26182,10 +26411,26 @@
         <f t="shared" si="2"/>
         <v>0.90270000000000006</v>
       </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H12" s="66">
+        <f>IFERROR(INDEX('soil carbon'!$A$14:$J$30,MATCH($A12,'soil carbon'!$A$14:$A$30,0),2), "NA")</f>
+        <v>79.52</v>
+      </c>
+      <c r="I12" s="66">
+        <f>IFERROR(INDEX('soil carbon'!$A$14:$J$30,MATCH($A12,'soil carbon'!$A$14:$A$30,0),4), "NA")</f>
+        <v>1.786</v>
+      </c>
+      <c r="J12" s="66">
+        <f>IFERROR(INDEX('soil carbon'!$A$14:$J$30,MATCH($A12,'soil carbon'!$A$14:$A$30,0),6), "NA")</f>
+        <v>208.69</v>
+      </c>
+      <c r="K12" s="66">
+        <f>IFERROR(INDEX('soil carbon'!$A$14:$J$30,MATCH($A12,'soil carbon'!$A$14:$A$30,0),8), "NA")</f>
+        <v>0.1961</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="B13">
         <v>7.1120000000000001</v>
@@ -26208,10 +26453,26 @@
         <f t="shared" si="2"/>
         <v>0.84200000000000019</v>
       </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H13" s="66">
+        <f>IFERROR(INDEX('soil carbon'!$A$14:$J$30,MATCH($A13,'soil carbon'!$A$14:$A$30,0),2), "NA")</f>
+        <v>78.75</v>
+      </c>
+      <c r="I13" s="66">
+        <f>IFERROR(INDEX('soil carbon'!$A$14:$J$30,MATCH($A13,'soil carbon'!$A$14:$A$30,0),4), "NA")</f>
+        <v>1.7829999999999999</v>
+      </c>
+      <c r="J13" s="66">
+        <f>IFERROR(INDEX('soil carbon'!$A$14:$J$30,MATCH($A13,'soil carbon'!$A$14:$A$30,0),6), "NA")</f>
+        <v>203.43</v>
+      </c>
+      <c r="K13" s="66">
+        <f>IFERROR(INDEX('soil carbon'!$A$14:$J$30,MATCH($A13,'soil carbon'!$A$14:$A$30,0),8), "NA")</f>
+        <v>0.40510000000000002</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="B14">
         <v>7.1059999999999999</v>
@@ -26234,10 +26495,26 @@
         <f t="shared" si="2"/>
         <v>0.84490000000000021</v>
       </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H14" s="66">
+        <f>IFERROR(INDEX('soil carbon'!$A$14:$J$30,MATCH($A14,'soil carbon'!$A$14:$A$30,0),2), "NA")</f>
+        <v>75.040000000000006</v>
+      </c>
+      <c r="I14" s="66">
+        <f>IFERROR(INDEX('soil carbon'!$A$14:$J$30,MATCH($A14,'soil carbon'!$A$14:$A$30,0),4), "NA")</f>
+        <v>1.595</v>
+      </c>
+      <c r="J14" s="66">
+        <f>IFERROR(INDEX('soil carbon'!$A$14:$J$30,MATCH($A14,'soil carbon'!$A$14:$A$30,0),6), "NA")</f>
+        <v>203.09</v>
+      </c>
+      <c r="K14" s="66">
+        <f>IFERROR(INDEX('soil carbon'!$A$14:$J$30,MATCH($A14,'soil carbon'!$A$14:$A$30,0),8), "NA")</f>
+        <v>0.29580000000000001</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="B15">
         <v>8.3140000000000001</v>
@@ -26260,10 +26537,26 @@
         <f t="shared" si="2"/>
         <v>0.80485000000000007</v>
       </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H15" s="66">
+        <f>IFERROR(INDEX('soil carbon'!$A$14:$J$30,MATCH($A15,'soil carbon'!$A$14:$A$30,0),2), "NA")</f>
+        <v>72.94</v>
+      </c>
+      <c r="I15" s="66">
+        <f>IFERROR(INDEX('soil carbon'!$A$14:$J$30,MATCH($A15,'soil carbon'!$A$14:$A$30,0),4), "NA")</f>
+        <v>1.7350000000000001</v>
+      </c>
+      <c r="J15" s="66">
+        <f>IFERROR(INDEX('soil carbon'!$A$14:$J$30,MATCH($A15,'soil carbon'!$A$14:$A$30,0),6), "NA")</f>
+        <v>201.41</v>
+      </c>
+      <c r="K15" s="66">
+        <f>IFERROR(INDEX('soil carbon'!$A$14:$J$30,MATCH($A15,'soil carbon'!$A$14:$A$30,0),8), "NA")</f>
+        <v>0.17269999999999999</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="B16">
         <v>7.3310000000000004</v>
@@ -26286,10 +26579,26 @@
         <f t="shared" si="2"/>
         <v>0.87740000000000007</v>
       </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H16" s="66">
+        <f>IFERROR(INDEX('soil carbon'!$A$14:$J$30,MATCH($A16,'soil carbon'!$A$14:$A$30,0),2), "NA")</f>
+        <v>78.959999999999994</v>
+      </c>
+      <c r="I16" s="66">
+        <f>IFERROR(INDEX('soil carbon'!$A$14:$J$30,MATCH($A16,'soil carbon'!$A$14:$A$30,0),4), "NA")</f>
+        <v>1.601</v>
+      </c>
+      <c r="J16" s="66">
+        <f>IFERROR(INDEX('soil carbon'!$A$14:$J$30,MATCH($A16,'soil carbon'!$A$14:$A$30,0),6), "NA")</f>
+        <v>201.06</v>
+      </c>
+      <c r="K16" s="66">
+        <f>IFERROR(INDEX('soil carbon'!$A$14:$J$30,MATCH($A16,'soil carbon'!$A$14:$A$30,0),8), "NA")</f>
+        <v>7.9960000000000003E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="B17">
         <v>8.44</v>
@@ -26312,8 +26621,1561 @@
         <f t="shared" si="2"/>
         <v>0.89170000000000016</v>
       </c>
+      <c r="H17" s="66">
+        <f>IFERROR(INDEX('soil carbon'!$A$14:$J$30,MATCH($A17,'soil carbon'!$A$14:$A$30,0),2), "NA")</f>
+        <v>70.8</v>
+      </c>
+      <c r="I17" s="66">
+        <f>IFERROR(INDEX('soil carbon'!$A$14:$J$30,MATCH($A17,'soil carbon'!$A$14:$A$30,0),4), "NA")</f>
+        <v>1.4259999999999999</v>
+      </c>
+      <c r="J17" s="66">
+        <f>IFERROR(INDEX('soil carbon'!$A$14:$J$30,MATCH($A17,'soil carbon'!$A$14:$A$30,0),6), "NA")</f>
+        <v>203.05</v>
+      </c>
+      <c r="K17" s="66">
+        <f>IFERROR(INDEX('soil carbon'!$A$14:$J$30,MATCH($A17,'soil carbon'!$A$14:$A$30,0),8), "NA")</f>
+        <v>0.11360000000000001</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:J95"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="4" width="16" style="33" customWidth="1"/>
+    <col min="5" max="5" width="20.140625" style="33" customWidth="1"/>
+    <col min="6" max="9" width="16" style="33" customWidth="1"/>
+    <col min="10" max="10" width="20.140625" style="33" customWidth="1"/>
+    <col min="11" max="16384" width="11.42578125" style="33"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="81"/>
+      <c r="B1" s="81"/>
+      <c r="C1" s="81"/>
+      <c r="D1" s="82" t="s">
+        <v>457</v>
+      </c>
+      <c r="E1" s="82"/>
+      <c r="F1" s="82"/>
+      <c r="G1" s="82"/>
+      <c r="H1" s="82"/>
+      <c r="I1" s="82"/>
+      <c r="J1" s="78"/>
+    </row>
+    <row r="2" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="81"/>
+      <c r="B2" s="81"/>
+      <c r="C2" s="81"/>
+      <c r="D2" s="82" t="s">
+        <v>458</v>
+      </c>
+      <c r="E2" s="82"/>
+      <c r="F2" s="82"/>
+      <c r="G2" s="82"/>
+      <c r="H2" s="82"/>
+      <c r="I2" s="82"/>
+      <c r="J2" s="78"/>
+    </row>
+    <row r="3" spans="1:10" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="81"/>
+      <c r="B3" s="81"/>
+      <c r="C3" s="81"/>
+      <c r="D3" s="83" t="s">
+        <v>459</v>
+      </c>
+      <c r="E3" s="83"/>
+      <c r="F3" s="83"/>
+      <c r="G3" s="83"/>
+      <c r="H3" s="83"/>
+      <c r="I3" s="83"/>
+      <c r="J3" s="78"/>
+    </row>
+    <row r="5" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="84" t="s">
+        <v>460</v>
+      </c>
+      <c r="B5" s="84"/>
+      <c r="C5" s="85"/>
+      <c r="D5" s="85"/>
+    </row>
+    <row r="6" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="84" t="s">
+        <v>461</v>
+      </c>
+      <c r="B6" s="84"/>
+      <c r="C6" s="86"/>
+      <c r="D6" s="86"/>
+    </row>
+    <row r="7" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="84" t="s">
+        <v>462</v>
+      </c>
+      <c r="B7" s="84"/>
+      <c r="C7" s="85"/>
+      <c r="D7" s="85"/>
+    </row>
+    <row r="8" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="84" t="s">
+        <v>463</v>
+      </c>
+      <c r="B8" s="84"/>
+      <c r="C8" s="87"/>
+      <c r="D8" s="87"/>
+    </row>
+    <row r="9" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="34"/>
+      <c r="B9" s="34"/>
+      <c r="C9" s="34"/>
+      <c r="D9" s="34"/>
+      <c r="E9" s="34"/>
+      <c r="F9" s="34"/>
+      <c r="G9" s="34"/>
+    </row>
+    <row r="10" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="35"/>
+      <c r="B10" s="89" t="s">
+        <v>464</v>
+      </c>
+      <c r="C10" s="89"/>
+      <c r="D10" s="89"/>
+      <c r="E10" s="89"/>
+      <c r="F10" s="89" t="s">
+        <v>465</v>
+      </c>
+      <c r="G10" s="89"/>
+      <c r="H10" s="89"/>
+      <c r="I10" s="89"/>
+    </row>
+    <row r="11" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="90" t="s">
+        <v>466</v>
+      </c>
+      <c r="B11" s="91" t="s">
+        <v>467</v>
+      </c>
+      <c r="C11" s="88" t="s">
+        <v>468</v>
+      </c>
+      <c r="D11" s="92" t="s">
+        <v>469</v>
+      </c>
+      <c r="E11" s="88" t="s">
+        <v>470</v>
+      </c>
+      <c r="F11" s="92" t="s">
+        <v>467</v>
+      </c>
+      <c r="G11" s="88" t="s">
+        <v>468</v>
+      </c>
+      <c r="H11" s="88" t="s">
+        <v>471</v>
+      </c>
+      <c r="I11" s="88" t="s">
+        <v>472</v>
+      </c>
+      <c r="J11" s="88" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="90"/>
+      <c r="B12" s="91"/>
+      <c r="C12" s="88"/>
+      <c r="D12" s="92"/>
+      <c r="E12" s="88"/>
+      <c r="F12" s="92"/>
+      <c r="G12" s="88"/>
+      <c r="H12" s="88"/>
+      <c r="I12" s="88"/>
+      <c r="J12" s="88"/>
+    </row>
+    <row r="13" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="36"/>
+      <c r="B13" s="37"/>
+      <c r="C13" s="38"/>
+      <c r="D13" s="39"/>
+      <c r="E13" s="40" t="s">
+        <v>474</v>
+      </c>
+      <c r="F13" s="41"/>
+      <c r="G13" s="38"/>
+      <c r="H13" s="42"/>
+      <c r="I13" s="43" t="s">
+        <v>474</v>
+      </c>
+      <c r="J13" s="40" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="44" t="s">
+        <v>570</v>
+      </c>
+      <c r="B14" s="45">
+        <v>76.77</v>
+      </c>
+      <c r="C14" s="46">
+        <v>1</v>
+      </c>
+      <c r="D14" s="47">
+        <v>1.66</v>
+      </c>
+      <c r="E14" s="48">
+        <f t="shared" ref="E14:E30" si="0">(D14*1000/B14)*C14</f>
+        <v>21.62302982936043</v>
+      </c>
+      <c r="F14" s="49">
+        <v>203.1</v>
+      </c>
+      <c r="G14" s="46">
+        <v>1</v>
+      </c>
+      <c r="H14" s="50">
+        <v>0.10730000000000001</v>
+      </c>
+      <c r="I14" s="51">
+        <f t="shared" ref="I14:I21" si="1">(H14*1000/F14)*G14</f>
+        <v>0.52831117676021666</v>
+      </c>
+      <c r="J14" s="48">
+        <f t="shared" ref="J14:J21" si="2">E14-I14</f>
+        <v>21.094718652600214</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="44" t="s">
+        <v>571</v>
+      </c>
+      <c r="B15" s="45">
+        <v>73.52</v>
+      </c>
+      <c r="C15" s="46">
+        <v>1</v>
+      </c>
+      <c r="D15" s="47">
+        <v>1.8089999999999999</v>
+      </c>
+      <c r="E15" s="48">
+        <f t="shared" si="0"/>
+        <v>24.605549510337326</v>
+      </c>
+      <c r="F15" s="49">
+        <v>210.1</v>
+      </c>
+      <c r="G15" s="46">
+        <v>1</v>
+      </c>
+      <c r="H15" s="50">
+        <v>0.1726</v>
+      </c>
+      <c r="I15" s="51">
+        <f t="shared" si="1"/>
+        <v>0.82151356496906236</v>
+      </c>
+      <c r="J15" s="48">
+        <f t="shared" si="2"/>
+        <v>23.784035945368263</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="44" t="s">
+        <v>572</v>
+      </c>
+      <c r="B16" s="45">
+        <v>76.790000000000006</v>
+      </c>
+      <c r="C16" s="46">
+        <v>1</v>
+      </c>
+      <c r="D16" s="47">
+        <v>1.24</v>
+      </c>
+      <c r="E16" s="48">
+        <f t="shared" si="0"/>
+        <v>16.147935929157441</v>
+      </c>
+      <c r="F16" s="49">
+        <v>207.1</v>
+      </c>
+      <c r="G16" s="46">
+        <v>1</v>
+      </c>
+      <c r="H16" s="50">
+        <v>1.048E-2</v>
+      </c>
+      <c r="I16" s="51">
+        <f t="shared" si="1"/>
+        <v>5.0603573153066156E-2</v>
+      </c>
+      <c r="J16" s="48">
+        <f t="shared" si="2"/>
+        <v>16.097332356004376</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="44" t="s">
+        <v>573</v>
+      </c>
+      <c r="B17" s="45">
+        <v>73.13</v>
+      </c>
+      <c r="C17" s="46">
+        <v>1</v>
+      </c>
+      <c r="D17" s="47">
+        <v>1.7250000000000001</v>
+      </c>
+      <c r="E17" s="48">
+        <f t="shared" si="0"/>
+        <v>23.5881307261042</v>
+      </c>
+      <c r="F17" s="49">
+        <v>203.8</v>
+      </c>
+      <c r="G17" s="46">
+        <v>1</v>
+      </c>
+      <c r="H17" s="50">
+        <v>0.22020000000000001</v>
+      </c>
+      <c r="I17" s="51">
+        <f t="shared" si="1"/>
+        <v>1.0804710500490677</v>
+      </c>
+      <c r="J17" s="48">
+        <f t="shared" si="2"/>
+        <v>22.507659676055134</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="44" t="s">
+        <v>574</v>
+      </c>
+      <c r="B18" s="45">
+        <v>75.63</v>
+      </c>
+      <c r="C18" s="46">
+        <v>1</v>
+      </c>
+      <c r="D18" s="47">
+        <v>2.3620000000000001</v>
+      </c>
+      <c r="E18" s="48">
+        <f t="shared" si="0"/>
+        <v>31.230992992198864</v>
+      </c>
+      <c r="F18" s="49">
+        <v>201.8</v>
+      </c>
+      <c r="G18" s="46">
+        <v>1</v>
+      </c>
+      <c r="H18" s="50">
+        <v>8.4159999999999999E-2</v>
+      </c>
+      <c r="I18" s="51">
+        <f t="shared" si="1"/>
+        <v>0.41704658077304257</v>
+      </c>
+      <c r="J18" s="48">
+        <f t="shared" si="2"/>
+        <v>30.813946411425821</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="44" t="s">
+        <v>575</v>
+      </c>
+      <c r="B19" s="45">
+        <v>72.069999999999993</v>
+      </c>
+      <c r="C19" s="46">
+        <v>1</v>
+      </c>
+      <c r="D19" s="47">
+        <v>2.081</v>
+      </c>
+      <c r="E19" s="48">
+        <f t="shared" si="0"/>
+        <v>28.874705147773</v>
+      </c>
+      <c r="F19" s="49">
+        <v>212.3</v>
+      </c>
+      <c r="G19" s="46">
+        <v>1</v>
+      </c>
+      <c r="H19" s="50">
+        <v>0.1186</v>
+      </c>
+      <c r="I19" s="51">
+        <f t="shared" si="1"/>
+        <v>0.55864342910975029</v>
+      </c>
+      <c r="J19" s="48">
+        <f t="shared" si="2"/>
+        <v>28.316061718663249</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="44" t="s">
+        <v>576</v>
+      </c>
+      <c r="B20" s="45">
+        <v>72.760000000000005</v>
+      </c>
+      <c r="C20" s="46">
+        <v>1</v>
+      </c>
+      <c r="D20" s="47">
+        <v>1.927</v>
+      </c>
+      <c r="E20" s="48">
+        <f t="shared" si="0"/>
+        <v>26.484332050577237</v>
+      </c>
+      <c r="F20" s="49">
+        <v>203.8</v>
+      </c>
+      <c r="G20" s="46">
+        <v>1</v>
+      </c>
+      <c r="H20" s="50">
+        <v>0.12870000000000001</v>
+      </c>
+      <c r="I20" s="51">
+        <f t="shared" si="1"/>
+        <v>0.63150147203140339</v>
+      </c>
+      <c r="J20" s="48">
+        <f t="shared" si="2"/>
+        <v>25.852830578545834</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="44" t="s">
+        <v>577</v>
+      </c>
+      <c r="B21" s="45">
+        <v>75.42</v>
+      </c>
+      <c r="C21" s="46">
+        <v>1</v>
+      </c>
+      <c r="D21" s="47">
+        <v>1.8560000000000001</v>
+      </c>
+      <c r="E21" s="48">
+        <f t="shared" si="0"/>
+        <v>24.608857067090955</v>
+      </c>
+      <c r="F21" s="49">
+        <v>202.3</v>
+      </c>
+      <c r="G21" s="46">
+        <v>1</v>
+      </c>
+      <c r="H21" s="50">
+        <v>0.3664</v>
+      </c>
+      <c r="I21" s="51">
+        <f t="shared" si="1"/>
+        <v>1.811171527434503</v>
+      </c>
+      <c r="J21" s="48">
+        <f t="shared" si="2"/>
+        <v>22.797685539656452</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="44"/>
+      <c r="B22" s="45"/>
+      <c r="C22" s="46"/>
+      <c r="D22" s="47"/>
+      <c r="E22" s="48"/>
+      <c r="F22" s="49"/>
+      <c r="G22" s="46"/>
+      <c r="H22" s="50"/>
+      <c r="I22" s="51"/>
+      <c r="J22" s="48"/>
+    </row>
+    <row r="23" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="44" t="s">
+        <v>578</v>
+      </c>
+      <c r="B23" s="45">
+        <v>79.290000000000006</v>
+      </c>
+      <c r="C23" s="46">
+        <v>1</v>
+      </c>
+      <c r="D23" s="47">
+        <v>2.1259999999999999</v>
+      </c>
+      <c r="E23" s="48">
+        <f t="shared" si="0"/>
+        <v>26.812965064951442</v>
+      </c>
+      <c r="F23" s="49">
+        <v>212.3</v>
+      </c>
+      <c r="G23" s="46">
+        <v>1</v>
+      </c>
+      <c r="H23" s="50">
+        <v>0.21440000000000001</v>
+      </c>
+      <c r="I23" s="51">
+        <f t="shared" ref="I23:I30" si="3">(H23*1000/F23)*G23</f>
+        <v>1.0098916627414036</v>
+      </c>
+      <c r="J23" s="48">
+        <f t="shared" ref="J23:J30" si="4">E23-I23</f>
+        <v>25.803073402210039</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="44" t="s">
+        <v>579</v>
+      </c>
+      <c r="B24" s="45">
+        <v>74.98</v>
+      </c>
+      <c r="C24" s="46">
+        <v>1</v>
+      </c>
+      <c r="D24" s="47">
+        <v>2.024</v>
+      </c>
+      <c r="E24" s="48">
+        <f t="shared" si="0"/>
+        <v>26.993865030674844</v>
+      </c>
+      <c r="F24" s="49">
+        <v>200.28</v>
+      </c>
+      <c r="G24" s="46">
+        <v>1</v>
+      </c>
+      <c r="H24" s="50">
+        <v>0.2049</v>
+      </c>
+      <c r="I24" s="51">
+        <f t="shared" si="3"/>
+        <v>1.0230677052127022</v>
+      </c>
+      <c r="J24" s="48">
+        <f t="shared" si="4"/>
+        <v>25.97079732546214</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="44" t="s">
+        <v>580</v>
+      </c>
+      <c r="B25" s="45">
+        <v>79.52</v>
+      </c>
+      <c r="C25" s="46">
+        <v>1</v>
+      </c>
+      <c r="D25" s="47">
+        <v>1.786</v>
+      </c>
+      <c r="E25" s="48">
+        <f t="shared" si="0"/>
+        <v>22.45975855130785</v>
+      </c>
+      <c r="F25" s="49">
+        <v>208.69</v>
+      </c>
+      <c r="G25" s="46">
+        <v>1</v>
+      </c>
+      <c r="H25" s="50">
+        <v>0.1961</v>
+      </c>
+      <c r="I25" s="51">
+        <f t="shared" si="3"/>
+        <v>0.93967128276390821</v>
+      </c>
+      <c r="J25" s="48">
+        <f t="shared" si="4"/>
+        <v>21.520087268543943</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="44" t="s">
+        <v>581</v>
+      </c>
+      <c r="B26" s="45">
+        <v>78.75</v>
+      </c>
+      <c r="C26" s="46">
+        <v>1</v>
+      </c>
+      <c r="D26" s="47">
+        <v>1.7829999999999999</v>
+      </c>
+      <c r="E26" s="48">
+        <f t="shared" si="0"/>
+        <v>22.641269841269843</v>
+      </c>
+      <c r="F26" s="49">
+        <v>203.43</v>
+      </c>
+      <c r="G26" s="46">
+        <v>1</v>
+      </c>
+      <c r="H26" s="50">
+        <v>0.40510000000000002</v>
+      </c>
+      <c r="I26" s="51">
+        <f t="shared" si="3"/>
+        <v>1.9913483753625325</v>
+      </c>
+      <c r="J26" s="48">
+        <f t="shared" si="4"/>
+        <v>20.649921465907312</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="44" t="s">
+        <v>582</v>
+      </c>
+      <c r="B27" s="45">
+        <v>75.040000000000006</v>
+      </c>
+      <c r="C27" s="46">
+        <v>1</v>
+      </c>
+      <c r="D27" s="47">
+        <v>1.595</v>
+      </c>
+      <c r="E27" s="48">
+        <f t="shared" si="0"/>
+        <v>21.255330490405115</v>
+      </c>
+      <c r="F27" s="49">
+        <v>203.09</v>
+      </c>
+      <c r="G27" s="46">
+        <v>1</v>
+      </c>
+      <c r="H27" s="50">
+        <v>0.29580000000000001</v>
+      </c>
+      <c r="I27" s="51">
+        <f t="shared" si="3"/>
+        <v>1.4564971195036684</v>
+      </c>
+      <c r="J27" s="48">
+        <f t="shared" si="4"/>
+        <v>19.798833370901445</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="44" t="s">
+        <v>583</v>
+      </c>
+      <c r="B28" s="45">
+        <v>72.94</v>
+      </c>
+      <c r="C28" s="46">
+        <v>1</v>
+      </c>
+      <c r="D28" s="47">
+        <v>1.7350000000000001</v>
+      </c>
+      <c r="E28" s="48">
+        <f t="shared" si="0"/>
+        <v>23.786673978612558</v>
+      </c>
+      <c r="F28" s="49">
+        <v>201.41</v>
+      </c>
+      <c r="G28" s="46">
+        <v>1</v>
+      </c>
+      <c r="H28" s="50">
+        <v>0.17269999999999999</v>
+      </c>
+      <c r="I28" s="51">
+        <f t="shared" si="3"/>
+        <v>0.85745494265428723</v>
+      </c>
+      <c r="J28" s="48">
+        <f t="shared" si="4"/>
+        <v>22.929219035958273</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="44" t="s">
+        <v>584</v>
+      </c>
+      <c r="B29" s="45">
+        <v>78.959999999999994</v>
+      </c>
+      <c r="C29" s="46">
+        <v>1</v>
+      </c>
+      <c r="D29" s="47">
+        <v>1.601</v>
+      </c>
+      <c r="E29" s="48">
+        <f t="shared" si="0"/>
+        <v>20.276089159067883</v>
+      </c>
+      <c r="F29" s="49">
+        <v>201.06</v>
+      </c>
+      <c r="G29" s="46">
+        <v>1</v>
+      </c>
+      <c r="H29" s="50">
+        <v>7.9960000000000003E-2</v>
+      </c>
+      <c r="I29" s="51">
+        <f t="shared" si="3"/>
+        <v>0.39769223117477376</v>
+      </c>
+      <c r="J29" s="48">
+        <f t="shared" si="4"/>
+        <v>19.87839692789311</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="44" t="s">
+        <v>585</v>
+      </c>
+      <c r="B30" s="45">
+        <v>70.8</v>
+      </c>
+      <c r="C30" s="46">
+        <v>1</v>
+      </c>
+      <c r="D30" s="47">
+        <v>1.4259999999999999</v>
+      </c>
+      <c r="E30" s="48">
+        <f t="shared" si="0"/>
+        <v>20.141242937853107</v>
+      </c>
+      <c r="F30" s="49">
+        <v>203.05</v>
+      </c>
+      <c r="G30" s="46">
+        <v>1</v>
+      </c>
+      <c r="H30" s="50">
+        <v>0.11360000000000001</v>
+      </c>
+      <c r="I30" s="51">
+        <f t="shared" si="3"/>
+        <v>0.55946811130263485</v>
+      </c>
+      <c r="J30" s="48">
+        <f t="shared" si="4"/>
+        <v>19.581774826550472</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="44"/>
+      <c r="B31" s="45"/>
+      <c r="C31" s="46"/>
+      <c r="D31" s="47"/>
+      <c r="E31" s="48"/>
+      <c r="F31" s="49"/>
+      <c r="G31" s="46"/>
+      <c r="H31" s="50"/>
+      <c r="I31" s="51"/>
+      <c r="J31" s="48"/>
+    </row>
+    <row r="32" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="44"/>
+      <c r="B32" s="45"/>
+      <c r="C32" s="46"/>
+      <c r="D32" s="47"/>
+      <c r="E32" s="48"/>
+      <c r="F32" s="49"/>
+      <c r="G32" s="46"/>
+      <c r="H32" s="50"/>
+      <c r="I32" s="51"/>
+      <c r="J32" s="48"/>
+    </row>
+    <row r="33" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="44"/>
+      <c r="B33" s="45"/>
+      <c r="C33" s="46"/>
+      <c r="D33" s="47"/>
+      <c r="E33" s="48"/>
+      <c r="F33" s="49"/>
+      <c r="G33" s="46"/>
+      <c r="H33" s="50"/>
+      <c r="I33" s="51"/>
+      <c r="J33" s="48"/>
+    </row>
+    <row r="34" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="44"/>
+      <c r="B34" s="45"/>
+      <c r="C34" s="46"/>
+      <c r="D34" s="47"/>
+      <c r="E34" s="48"/>
+      <c r="F34" s="49"/>
+      <c r="G34" s="46"/>
+      <c r="H34" s="50"/>
+      <c r="I34" s="51"/>
+      <c r="J34" s="48"/>
+    </row>
+    <row r="35" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="44"/>
+      <c r="B35" s="45"/>
+      <c r="C35" s="46"/>
+      <c r="D35" s="47"/>
+      <c r="E35" s="48"/>
+      <c r="F35" s="49"/>
+      <c r="G35" s="46"/>
+      <c r="H35" s="50"/>
+      <c r="I35" s="51"/>
+      <c r="J35" s="48"/>
+    </row>
+    <row r="36" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="44"/>
+      <c r="B36" s="45"/>
+      <c r="C36" s="46"/>
+      <c r="D36" s="47"/>
+      <c r="E36" s="48"/>
+      <c r="F36" s="49"/>
+      <c r="G36" s="46"/>
+      <c r="H36" s="50"/>
+      <c r="I36" s="51"/>
+      <c r="J36" s="48"/>
+    </row>
+    <row r="37" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="44"/>
+      <c r="B37" s="45"/>
+      <c r="C37" s="46"/>
+      <c r="D37" s="47"/>
+      <c r="E37" s="48"/>
+      <c r="F37" s="49"/>
+      <c r="G37" s="46"/>
+      <c r="H37" s="50"/>
+      <c r="I37" s="51"/>
+      <c r="J37" s="48"/>
+    </row>
+    <row r="38" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="44"/>
+      <c r="B38" s="45"/>
+      <c r="C38" s="46"/>
+      <c r="D38" s="47"/>
+      <c r="E38" s="48"/>
+      <c r="F38" s="49"/>
+      <c r="G38" s="46"/>
+      <c r="H38" s="50"/>
+      <c r="I38" s="51"/>
+      <c r="J38" s="48"/>
+    </row>
+    <row r="39" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="44"/>
+      <c r="B39" s="45"/>
+      <c r="C39" s="46"/>
+      <c r="D39" s="47"/>
+      <c r="E39" s="48"/>
+      <c r="F39" s="49"/>
+      <c r="G39" s="46"/>
+      <c r="H39" s="50"/>
+      <c r="I39" s="51"/>
+      <c r="J39" s="48"/>
+    </row>
+    <row r="40" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="44"/>
+      <c r="B40" s="45"/>
+      <c r="C40" s="46"/>
+      <c r="D40" s="47"/>
+      <c r="E40" s="48"/>
+      <c r="F40" s="49"/>
+      <c r="G40" s="46"/>
+      <c r="H40" s="50"/>
+      <c r="I40" s="51"/>
+      <c r="J40" s="48"/>
+    </row>
+    <row r="41" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="44"/>
+      <c r="B41" s="45"/>
+      <c r="C41" s="46"/>
+      <c r="D41" s="47"/>
+      <c r="E41" s="48"/>
+      <c r="F41" s="49"/>
+      <c r="G41" s="46"/>
+      <c r="H41" s="50"/>
+      <c r="I41" s="51"/>
+      <c r="J41" s="48"/>
+    </row>
+    <row r="42" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="44"/>
+      <c r="B42" s="45"/>
+      <c r="C42" s="46"/>
+      <c r="D42" s="47"/>
+      <c r="E42" s="48"/>
+      <c r="F42" s="49"/>
+      <c r="G42" s="46"/>
+      <c r="H42" s="50"/>
+      <c r="I42" s="51"/>
+      <c r="J42" s="48"/>
+    </row>
+    <row r="43" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="44"/>
+      <c r="B43" s="45"/>
+      <c r="C43" s="46"/>
+      <c r="D43" s="47"/>
+      <c r="E43" s="48"/>
+      <c r="F43" s="49"/>
+      <c r="G43" s="46"/>
+      <c r="H43" s="50"/>
+      <c r="I43" s="51"/>
+      <c r="J43" s="48"/>
+    </row>
+    <row r="44" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="44"/>
+      <c r="B44" s="45"/>
+      <c r="C44" s="46"/>
+      <c r="D44" s="47"/>
+      <c r="E44" s="48"/>
+      <c r="F44" s="49"/>
+      <c r="G44" s="46"/>
+      <c r="H44" s="50"/>
+      <c r="I44" s="51"/>
+      <c r="J44" s="48"/>
+    </row>
+    <row r="45" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="44"/>
+      <c r="B45" s="45"/>
+      <c r="C45" s="46"/>
+      <c r="D45" s="47"/>
+      <c r="E45" s="48"/>
+      <c r="F45" s="49"/>
+      <c r="G45" s="46"/>
+      <c r="H45" s="50"/>
+      <c r="I45" s="51"/>
+      <c r="J45" s="48"/>
+    </row>
+    <row r="46" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="44"/>
+      <c r="B46" s="45"/>
+      <c r="C46" s="46"/>
+      <c r="D46" s="47"/>
+      <c r="E46" s="48"/>
+      <c r="F46" s="49"/>
+      <c r="G46" s="46"/>
+      <c r="H46" s="50"/>
+      <c r="I46" s="51"/>
+      <c r="J46" s="48"/>
+    </row>
+    <row r="47" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="44"/>
+      <c r="B47" s="45"/>
+      <c r="C47" s="46"/>
+      <c r="D47" s="47"/>
+      <c r="E47" s="48"/>
+      <c r="F47" s="49"/>
+      <c r="G47" s="46"/>
+      <c r="H47" s="50"/>
+      <c r="I47" s="51"/>
+      <c r="J47" s="48"/>
+    </row>
+    <row r="48" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="44"/>
+      <c r="B48" s="45"/>
+      <c r="C48" s="46"/>
+      <c r="D48" s="47"/>
+      <c r="E48" s="48"/>
+      <c r="F48" s="49"/>
+      <c r="G48" s="46"/>
+      <c r="H48" s="50"/>
+      <c r="I48" s="51"/>
+      <c r="J48" s="48"/>
+    </row>
+    <row r="49" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="44"/>
+      <c r="B49" s="45"/>
+      <c r="C49" s="46"/>
+      <c r="D49" s="47"/>
+      <c r="E49" s="48"/>
+      <c r="F49" s="49"/>
+      <c r="G49" s="46"/>
+      <c r="H49" s="50"/>
+      <c r="I49" s="51"/>
+      <c r="J49" s="48"/>
+    </row>
+    <row r="50" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="44"/>
+      <c r="B50" s="45"/>
+      <c r="C50" s="46"/>
+      <c r="D50" s="47"/>
+      <c r="E50" s="48"/>
+      <c r="F50" s="49"/>
+      <c r="G50" s="46"/>
+      <c r="H50" s="50"/>
+      <c r="I50" s="51"/>
+      <c r="J50" s="48"/>
+    </row>
+    <row r="51" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="44"/>
+      <c r="B51" s="45"/>
+      <c r="C51" s="46"/>
+      <c r="D51" s="47"/>
+      <c r="E51" s="48"/>
+      <c r="F51" s="49"/>
+      <c r="G51" s="46"/>
+      <c r="H51" s="50"/>
+      <c r="I51" s="51"/>
+      <c r="J51" s="48"/>
+    </row>
+    <row r="52" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="44"/>
+      <c r="B52" s="45"/>
+      <c r="C52" s="46"/>
+      <c r="D52" s="47"/>
+      <c r="E52" s="48"/>
+      <c r="F52" s="49"/>
+      <c r="G52" s="46"/>
+      <c r="H52" s="50"/>
+      <c r="I52" s="51"/>
+      <c r="J52" s="48"/>
+    </row>
+    <row r="53" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="44"/>
+      <c r="B53" s="45"/>
+      <c r="C53" s="46"/>
+      <c r="D53" s="47"/>
+      <c r="E53" s="48"/>
+      <c r="F53" s="49"/>
+      <c r="G53" s="46"/>
+      <c r="H53" s="50"/>
+      <c r="I53" s="51"/>
+      <c r="J53" s="48"/>
+    </row>
+    <row r="54" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="44"/>
+      <c r="B54" s="45"/>
+      <c r="C54" s="46"/>
+      <c r="D54" s="47"/>
+      <c r="E54" s="48"/>
+      <c r="F54" s="49"/>
+      <c r="G54" s="46"/>
+      <c r="H54" s="50"/>
+      <c r="I54" s="51"/>
+      <c r="J54" s="48"/>
+    </row>
+    <row r="55" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="44"/>
+      <c r="B55" s="45"/>
+      <c r="C55" s="46"/>
+      <c r="D55" s="47"/>
+      <c r="E55" s="48"/>
+      <c r="F55" s="49"/>
+      <c r="G55" s="46"/>
+      <c r="H55" s="50"/>
+      <c r="I55" s="51"/>
+      <c r="J55" s="48"/>
+    </row>
+    <row r="56" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="44"/>
+      <c r="B56" s="45"/>
+      <c r="C56" s="46"/>
+      <c r="D56" s="47"/>
+      <c r="E56" s="48"/>
+      <c r="F56" s="49"/>
+      <c r="G56" s="46"/>
+      <c r="H56" s="50"/>
+      <c r="I56" s="51"/>
+      <c r="J56" s="48"/>
+    </row>
+    <row r="57" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="44"/>
+      <c r="B57" s="45"/>
+      <c r="C57" s="46"/>
+      <c r="D57" s="47"/>
+      <c r="E57" s="48"/>
+      <c r="F57" s="49"/>
+      <c r="G57" s="46"/>
+      <c r="H57" s="50"/>
+      <c r="I57" s="51"/>
+      <c r="J57" s="48"/>
+    </row>
+    <row r="58" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="44"/>
+      <c r="B58" s="45"/>
+      <c r="C58" s="46"/>
+      <c r="D58" s="47"/>
+      <c r="E58" s="48"/>
+      <c r="F58" s="49"/>
+      <c r="G58" s="46"/>
+      <c r="H58" s="50"/>
+      <c r="I58" s="51"/>
+      <c r="J58" s="48"/>
+    </row>
+    <row r="59" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="44"/>
+      <c r="B59" s="45"/>
+      <c r="C59" s="46"/>
+      <c r="D59" s="47"/>
+      <c r="E59" s="48"/>
+      <c r="F59" s="49"/>
+      <c r="G59" s="46"/>
+      <c r="H59" s="50"/>
+      <c r="I59" s="51"/>
+      <c r="J59" s="48"/>
+    </row>
+    <row r="60" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="44"/>
+      <c r="B60" s="45"/>
+      <c r="C60" s="46"/>
+      <c r="D60" s="47"/>
+      <c r="E60" s="48"/>
+      <c r="F60" s="49"/>
+      <c r="G60" s="46"/>
+      <c r="H60" s="50"/>
+      <c r="I60" s="51"/>
+      <c r="J60" s="48"/>
+    </row>
+    <row r="61" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="44"/>
+      <c r="B61" s="45"/>
+      <c r="C61" s="46"/>
+      <c r="D61" s="47"/>
+      <c r="E61" s="48"/>
+      <c r="F61" s="49"/>
+      <c r="G61" s="46"/>
+      <c r="H61" s="50"/>
+      <c r="I61" s="51"/>
+      <c r="J61" s="48"/>
+    </row>
+    <row r="62" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="44"/>
+      <c r="B62" s="45"/>
+      <c r="C62" s="46"/>
+      <c r="D62" s="47"/>
+      <c r="E62" s="48"/>
+      <c r="F62" s="49"/>
+      <c r="G62" s="46"/>
+      <c r="H62" s="50"/>
+      <c r="I62" s="51"/>
+      <c r="J62" s="48"/>
+    </row>
+    <row r="63" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="44"/>
+      <c r="B63" s="45"/>
+      <c r="C63" s="46"/>
+      <c r="D63" s="47"/>
+      <c r="E63" s="48"/>
+      <c r="F63" s="49"/>
+      <c r="G63" s="46"/>
+      <c r="H63" s="50"/>
+      <c r="I63" s="51"/>
+      <c r="J63" s="48"/>
+    </row>
+    <row r="64" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="44"/>
+      <c r="B64" s="45"/>
+      <c r="C64" s="46"/>
+      <c r="D64" s="47"/>
+      <c r="E64" s="48"/>
+      <c r="F64" s="49"/>
+      <c r="G64" s="46"/>
+      <c r="H64" s="50"/>
+      <c r="I64" s="51"/>
+      <c r="J64" s="48"/>
+    </row>
+    <row r="65" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="44"/>
+      <c r="B65" s="45"/>
+      <c r="C65" s="46"/>
+      <c r="D65" s="47"/>
+      <c r="E65" s="48"/>
+      <c r="F65" s="49"/>
+      <c r="G65" s="46"/>
+      <c r="H65" s="50"/>
+      <c r="I65" s="51"/>
+      <c r="J65" s="48"/>
+    </row>
+    <row r="66" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A66" s="44"/>
+      <c r="B66" s="45"/>
+      <c r="C66" s="46"/>
+      <c r="D66" s="47"/>
+      <c r="E66" s="48"/>
+      <c r="F66" s="49"/>
+      <c r="G66" s="46"/>
+      <c r="H66" s="50"/>
+      <c r="I66" s="51"/>
+      <c r="J66" s="48"/>
+    </row>
+    <row r="67" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A67" s="44"/>
+      <c r="B67" s="45"/>
+      <c r="C67" s="46"/>
+      <c r="D67" s="47"/>
+      <c r="E67" s="48"/>
+      <c r="F67" s="49"/>
+      <c r="G67" s="46"/>
+      <c r="H67" s="50"/>
+      <c r="I67" s="51"/>
+      <c r="J67" s="48"/>
+    </row>
+    <row r="68" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A68" s="44"/>
+      <c r="B68" s="45"/>
+      <c r="C68" s="46"/>
+      <c r="D68" s="47"/>
+      <c r="E68" s="48"/>
+      <c r="F68" s="49"/>
+      <c r="G68" s="46"/>
+      <c r="H68" s="50"/>
+      <c r="I68" s="51"/>
+      <c r="J68" s="48"/>
+    </row>
+    <row r="69" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A69" s="44"/>
+      <c r="B69" s="45"/>
+      <c r="C69" s="46"/>
+      <c r="D69" s="47"/>
+      <c r="E69" s="48"/>
+      <c r="F69" s="49"/>
+      <c r="G69" s="46"/>
+      <c r="H69" s="50"/>
+      <c r="I69" s="51"/>
+      <c r="J69" s="48"/>
+    </row>
+    <row r="70" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A70" s="44"/>
+      <c r="B70" s="45"/>
+      <c r="C70" s="46"/>
+      <c r="D70" s="47"/>
+      <c r="E70" s="48"/>
+      <c r="F70" s="49"/>
+      <c r="G70" s="46"/>
+      <c r="H70" s="50"/>
+      <c r="I70" s="51"/>
+      <c r="J70" s="48"/>
+    </row>
+    <row r="71" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A71" s="44"/>
+      <c r="B71" s="45"/>
+      <c r="C71" s="46"/>
+      <c r="D71" s="47"/>
+      <c r="E71" s="48"/>
+      <c r="F71" s="49"/>
+      <c r="G71" s="46"/>
+      <c r="H71" s="50"/>
+      <c r="I71" s="51"/>
+      <c r="J71" s="48"/>
+    </row>
+    <row r="72" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A72" s="44"/>
+      <c r="B72" s="45"/>
+      <c r="C72" s="46"/>
+      <c r="D72" s="47"/>
+      <c r="E72" s="48"/>
+      <c r="F72" s="49"/>
+      <c r="G72" s="46"/>
+      <c r="H72" s="50"/>
+      <c r="I72" s="51"/>
+      <c r="J72" s="48"/>
+    </row>
+    <row r="73" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A73" s="44"/>
+      <c r="B73" s="45"/>
+      <c r="C73" s="46"/>
+      <c r="D73" s="47"/>
+      <c r="E73" s="48"/>
+      <c r="F73" s="49"/>
+      <c r="G73" s="46"/>
+      <c r="H73" s="50"/>
+      <c r="I73" s="51"/>
+      <c r="J73" s="48"/>
+    </row>
+    <row r="74" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A74" s="44"/>
+      <c r="B74" s="45"/>
+      <c r="C74" s="46"/>
+      <c r="D74" s="47"/>
+      <c r="E74" s="48"/>
+      <c r="F74" s="49"/>
+      <c r="G74" s="46"/>
+      <c r="H74" s="50"/>
+      <c r="I74" s="51"/>
+      <c r="J74" s="48"/>
+    </row>
+    <row r="75" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A75" s="44"/>
+      <c r="B75" s="45"/>
+      <c r="C75" s="46"/>
+      <c r="D75" s="47"/>
+      <c r="E75" s="48"/>
+      <c r="F75" s="49"/>
+      <c r="G75" s="46"/>
+      <c r="H75" s="50"/>
+      <c r="I75" s="51"/>
+      <c r="J75" s="48"/>
+    </row>
+    <row r="76" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A76" s="44"/>
+      <c r="B76" s="45"/>
+      <c r="C76" s="46"/>
+      <c r="D76" s="47"/>
+      <c r="E76" s="48"/>
+      <c r="F76" s="49"/>
+      <c r="G76" s="46"/>
+      <c r="H76" s="50"/>
+      <c r="I76" s="51"/>
+      <c r="J76" s="48"/>
+    </row>
+    <row r="77" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A77" s="44"/>
+      <c r="B77" s="45"/>
+      <c r="C77" s="46"/>
+      <c r="D77" s="47"/>
+      <c r="E77" s="48"/>
+      <c r="F77" s="49"/>
+      <c r="G77" s="46"/>
+      <c r="H77" s="50"/>
+      <c r="I77" s="51"/>
+      <c r="J77" s="48"/>
+    </row>
+    <row r="78" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A78" s="44"/>
+      <c r="B78" s="45"/>
+      <c r="C78" s="46"/>
+      <c r="D78" s="47"/>
+      <c r="E78" s="48"/>
+      <c r="F78" s="49"/>
+      <c r="G78" s="46"/>
+      <c r="H78" s="50"/>
+      <c r="I78" s="51"/>
+      <c r="J78" s="48"/>
+    </row>
+    <row r="79" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A79" s="44"/>
+      <c r="B79" s="45"/>
+      <c r="C79" s="46"/>
+      <c r="D79" s="47"/>
+      <c r="E79" s="48"/>
+      <c r="F79" s="49"/>
+      <c r="G79" s="46"/>
+      <c r="H79" s="50"/>
+      <c r="I79" s="51"/>
+      <c r="J79" s="48"/>
+    </row>
+    <row r="80" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A80" s="44"/>
+      <c r="B80" s="45"/>
+      <c r="C80" s="46"/>
+      <c r="D80" s="47"/>
+      <c r="E80" s="48"/>
+      <c r="F80" s="49"/>
+      <c r="G80" s="46"/>
+      <c r="H80" s="50"/>
+      <c r="I80" s="51"/>
+      <c r="J80" s="48"/>
+    </row>
+    <row r="81" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A81" s="44"/>
+      <c r="B81" s="45"/>
+      <c r="C81" s="46"/>
+      <c r="D81" s="47"/>
+      <c r="E81" s="48"/>
+      <c r="F81" s="49"/>
+      <c r="G81" s="46"/>
+      <c r="H81" s="50"/>
+      <c r="I81" s="51"/>
+      <c r="J81" s="48"/>
+    </row>
+    <row r="82" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A82" s="44"/>
+      <c r="B82" s="45"/>
+      <c r="C82" s="46"/>
+      <c r="D82" s="47"/>
+      <c r="E82" s="48"/>
+      <c r="F82" s="49"/>
+      <c r="G82" s="46"/>
+      <c r="H82" s="50"/>
+      <c r="I82" s="51"/>
+      <c r="J82" s="48"/>
+    </row>
+    <row r="83" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A83" s="44"/>
+      <c r="B83" s="45"/>
+      <c r="C83" s="46"/>
+      <c r="D83" s="47"/>
+      <c r="E83" s="48"/>
+      <c r="F83" s="49"/>
+      <c r="G83" s="46"/>
+      <c r="H83" s="50"/>
+      <c r="I83" s="51"/>
+      <c r="J83" s="48"/>
+    </row>
+    <row r="84" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A84" s="44"/>
+      <c r="B84" s="45"/>
+      <c r="C84" s="46"/>
+      <c r="D84" s="47"/>
+      <c r="E84" s="48"/>
+      <c r="F84" s="49"/>
+      <c r="G84" s="46"/>
+      <c r="H84" s="50"/>
+      <c r="I84" s="51"/>
+      <c r="J84" s="48"/>
+    </row>
+    <row r="85" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A85" s="44"/>
+      <c r="B85" s="45"/>
+      <c r="C85" s="46"/>
+      <c r="D85" s="47"/>
+      <c r="E85" s="48"/>
+      <c r="F85" s="49"/>
+      <c r="G85" s="46"/>
+      <c r="H85" s="50"/>
+      <c r="I85" s="51"/>
+      <c r="J85" s="48"/>
+    </row>
+    <row r="86" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A86" s="44"/>
+      <c r="B86" s="45"/>
+      <c r="C86" s="46"/>
+      <c r="D86" s="47"/>
+      <c r="E86" s="48"/>
+      <c r="F86" s="49"/>
+      <c r="G86" s="46"/>
+      <c r="H86" s="50"/>
+      <c r="I86" s="51"/>
+      <c r="J86" s="48"/>
+    </row>
+    <row r="87" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A87" s="44"/>
+      <c r="B87" s="45"/>
+      <c r="C87" s="46"/>
+      <c r="D87" s="47"/>
+      <c r="E87" s="48"/>
+      <c r="F87" s="49"/>
+      <c r="G87" s="46"/>
+      <c r="H87" s="50"/>
+      <c r="I87" s="51"/>
+      <c r="J87" s="48"/>
+    </row>
+    <row r="88" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A88" s="44"/>
+      <c r="B88" s="45"/>
+      <c r="C88" s="46"/>
+      <c r="D88" s="47"/>
+      <c r="E88" s="48"/>
+      <c r="F88" s="49"/>
+      <c r="G88" s="46"/>
+      <c r="H88" s="50"/>
+      <c r="I88" s="51"/>
+      <c r="J88" s="48"/>
+    </row>
+    <row r="89" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A89" s="44"/>
+      <c r="B89" s="45"/>
+      <c r="C89" s="46"/>
+      <c r="D89" s="47"/>
+      <c r="E89" s="48"/>
+      <c r="F89" s="49"/>
+      <c r="G89" s="46"/>
+      <c r="H89" s="50"/>
+      <c r="I89" s="51"/>
+      <c r="J89" s="48"/>
+    </row>
+    <row r="90" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A90" s="44"/>
+      <c r="B90" s="45"/>
+      <c r="C90" s="46"/>
+      <c r="D90" s="47"/>
+      <c r="E90" s="48"/>
+      <c r="F90" s="49"/>
+      <c r="G90" s="46"/>
+      <c r="H90" s="50"/>
+      <c r="I90" s="51"/>
+      <c r="J90" s="48"/>
+    </row>
+    <row r="91" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A91" s="44"/>
+      <c r="B91" s="45"/>
+      <c r="C91" s="46"/>
+      <c r="D91" s="47"/>
+      <c r="E91" s="48"/>
+      <c r="F91" s="49"/>
+      <c r="G91" s="46"/>
+      <c r="H91" s="50"/>
+      <c r="I91" s="51"/>
+      <c r="J91" s="48"/>
+    </row>
+    <row r="92" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A92" s="44"/>
+      <c r="B92" s="45"/>
+      <c r="C92" s="46"/>
+      <c r="D92" s="47"/>
+      <c r="E92" s="48"/>
+      <c r="F92" s="49"/>
+      <c r="G92" s="46"/>
+      <c r="H92" s="50"/>
+      <c r="I92" s="51"/>
+      <c r="J92" s="48"/>
+    </row>
+    <row r="93" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A93" s="44"/>
+      <c r="B93" s="45"/>
+      <c r="C93" s="46"/>
+      <c r="D93" s="47"/>
+      <c r="E93" s="48"/>
+      <c r="F93" s="49"/>
+      <c r="G93" s="46"/>
+      <c r="H93" s="50"/>
+      <c r="I93" s="51"/>
+      <c r="J93" s="48"/>
+    </row>
+    <row r="95" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A95" s="77"/>
+    </row>
+  </sheetData>
+  <mergeCells count="24">
+    <mergeCell ref="I11:I12"/>
+    <mergeCell ref="J11:J12"/>
+    <mergeCell ref="B10:E10"/>
+    <mergeCell ref="F10:I10"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="D11:D12"/>
+    <mergeCell ref="E11:E12"/>
+    <mergeCell ref="F11:F12"/>
+    <mergeCell ref="G11:G12"/>
+    <mergeCell ref="H11:H12"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="A1:C3"/>
+    <mergeCell ref="D1:I1"/>
+    <mergeCell ref="D2:I2"/>
+    <mergeCell ref="D3:I3"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="C5:D5"/>
+  </mergeCells>
+  <pageMargins left="0.23611111111111099" right="0.23611111111111099" top="0.196527777777778" bottom="0.196527777777778" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="81" orientation="landscape" horizontalDpi="300" verticalDpi="300"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>